--- a/docs/package/02_Commercials/BrokerVerse_Commercials_and_Pricing.xlsx
+++ b/docs/package/02_Commercials/BrokerVerse_Commercials_and_Pricing.xlsx
@@ -52,13 +52,18 @@
     <definedName name="CR_Large_Max">Inputs!$B$52</definedName>
     <definedName name="CR_Dev_Days">Inputs!$B$53</definedName>
     <definedName name="Env_Setup_Days">Inputs!$B$57</definedName>
-    <definedName name="Env_Monthly_USD">Inputs!$B$58</definedName>
-    <definedName name="Mig_Days_Source">Inputs!$B$59</definedName>
-    <definedName name="Int_Std_Days">Inputs!$B$60</definedName>
-    <definedName name="Int_Cx_Days">Inputs!$B$61</definedName>
-    <definedName name="Report_Days">Inputs!$B$62</definedName>
-    <definedName name="Azure_Factor">Inputs!$B$74</definedName>
-    <definedName name="Local_Factor">Inputs!$B$75</definedName>
+    <definedName name="Mig_Days_Source">Inputs!$B$58</definedName>
+    <definedName name="Int_Std_Days">Inputs!$B$59</definedName>
+    <definedName name="Int_Cx_Days">Inputs!$B$60</definedName>
+    <definedName name="Report_Days">Inputs!$B$61</definedName>
+    <definedName name="NP_Small_USD">Inputs!$B$75</definedName>
+    <definedName name="NP_Med_USD">Inputs!$B$76</definedName>
+    <definedName name="PreProd_Factor">Inputs!$B$77</definedName>
+    <definedName name="PreProd_GoLive_Months">Inputs!$B$78</definedName>
+    <definedName name="PreProd_Rel_Months">Inputs!$B$79</definedName>
+    <definedName name="Major_Rel_Year">Inputs!$B$80</definedName>
+    <definedName name="Azure_Factor">Inputs!$B$88</definedName>
+    <definedName name="Local_Factor">Inputs!$B$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -247,6 +252,7 @@
     <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -258,7 +264,6 @@
     <xf numFmtId="1" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -633,7 +638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -678,7 +683,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="135" customHeight="1">
+    <row r="6" ht="150" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>How to use</t>
@@ -689,7 +694,7 @@
           <t>1. Change drivers only on the Inputs sheet (yellow cells, blue text). Every other sheet is formula driven.
 2. To price a prospect, enter its user count and number of lines of business in Inputs (Calculator section). The calculators on Perpetual Model and Subscription Model update, with the break-even year.
 3. To change the three worked examples, edit the Sample quote scenarios table in Inputs.
-4. Infrastructure is optional and separate. Pick AWS, Azure or Local partner per scenario; the customer may host itself at no fee.
+4. Infrastructure is optional and separate. Pick AWS, Azure or Local partner per scenario; the customer may host itself at no fee. Hosting is priced per environment set (Infrastructure sheet).
 5. Recalculate (F9) if your spreadsheet tool does not recalculate on open.</t>
         </is>
       </c>
@@ -790,37 +795,49 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Validity</t>
+          <t>Environments and hosting</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Prices are valid for 90 days from the quotation date and for contracts signed in that period. Day rates are fixed for 12 months from signing.</t>
+          <t>Small and Medium brokers: Dev, UAT and Production. Large and Enterprise: Dev, SIT, UAT and Production with high availability. Pre-Prod is temporary for every size, created from a production backup for the go-live rehearsal and for each major release, then removed; it is billed per month of use. Each environment is priced on its own line (Inputs and Infrastructure). Hosting fees do not increase yearly: provider price changes are passed through at cost.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Colour key</t>
+          <t>Validity</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Yellow cell with blue text: input. Green: total. Light orange: estimate or assumption. Navy header: column titles.</t>
+          <t>Prices are valid for 90 days from the quotation date and for contracts signed in that period. Day rates are fixed for 12 months from signing.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
+          <t>Colour key</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Yellow cell with blue text: input. Green: total. Light orange: estimate or assumption. Navy header: column titles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
           <t>Sheets</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Inputs, Size Tiers, Perpetual Model, Subscription Model, Infrastructure, Change Requests, Optional Services, Sample Quotes, Market Benchmark, Sources.</t>
         </is>
@@ -1503,7 +1520,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="31">
+      <c r="A18" s="32">
         <f>"BrokerVerse OOTB, "&amp;Inputs!A28&amp;" slab"</f>
         <v/>
       </c>
@@ -1544,7 +1561,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="31">
+      <c r="A19" s="32">
         <f>"BrokerVerse OOTB, "&amp;Inputs!A29&amp;" slab"</f>
         <v/>
       </c>
@@ -1585,7 +1602,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="31">
+      <c r="A20" s="32">
         <f>"BrokerVerse OOTB, "&amp;Inputs!A30&amp;" slab"</f>
         <v/>
       </c>
@@ -1626,7 +1643,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="31">
+      <c r="A21" s="32">
         <f>"BrokerVerse OOTB, "&amp;Inputs!A31&amp;" slab"</f>
         <v/>
       </c>
@@ -3159,7 +3176,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>BrokerVerse documentation: Capacity and Performance; Go-live data set-up; docs/templates</t>
+          <t>BrokerVerse documentation: Capacity and Performance; Go-live data set-up; docs/package/05_Delivery/Upload_Templates</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -3199,7 +3216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N86"/>
+  <dimension ref="A1:N100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3540,9 +3557,9 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>Assumption: cloud list prices are flat; review yearly against FX.</t>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Hosting fees do not escalate yearly: provider price changes are passed through at cost under the Hosting Agreement. Keep at 0%.</t>
         </is>
       </c>
       <c r="E14" s="8" t="n"/>
@@ -4724,20 +4741,20 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>Additional non-production environment: cloud cost per month</t>
-        </is>
-      </c>
-      <c r="B58" s="16" t="n">
-        <v>150</v>
+          <t>Data migration beyond templates: man-days per additional legacy source</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>Estimate: 1 small container, small single-zone database, storage (S3 for compute and database pricing references).</t>
+          <t>Estimate: mapping, extraction scripts, 2 trial loads, reconciliation.</t>
         </is>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -4754,11 +4771,11 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>Data migration beyond templates: man-days per additional legacy source</t>
+          <t>Additional integration, standard (documented API or file)</t>
         </is>
       </c>
       <c r="B59" s="14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
@@ -4767,7 +4784,7 @@
       </c>
       <c r="D59" s="15" t="inlineStr">
         <is>
-          <t>Estimate: mapping, extraction scripts, 2 trial loads, reconciliation.</t>
+          <t>Estimate: e.g. one insurer API, SMS gateway, payment gateway variant.</t>
         </is>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -4784,11 +4801,11 @@
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>Additional integration, standard (documented API or file)</t>
+          <t>Additional integration, complex (no API, two-way, or batch reconciliation)</t>
         </is>
       </c>
       <c r="B60" s="14" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
@@ -4797,7 +4814,7 @@
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>Estimate: e.g. one insurer API, SMS gateway, payment gateway variant.</t>
+          <t>Estimate.</t>
         </is>
       </c>
       <c r="E60" s="8" t="n"/>
@@ -4814,11 +4831,11 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>Additional integration, complex (no API, two-way, or batch reconciliation)</t>
+          <t>New report or document template (typical)</t>
         </is>
       </c>
       <c r="B61" s="14" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
@@ -4827,7 +4844,7 @@
       </c>
       <c r="D61" s="15" t="inlineStr">
         <is>
-          <t>Estimate.</t>
+          <t>Estimate: falls in the Small CR band.</t>
         </is>
       </c>
       <c r="E61" s="8" t="n"/>
@@ -4841,85 +4858,87 @@
       <c r="M61" s="8" t="n"/>
       <c r="N61" s="9" t="n"/>
     </row>
-    <row r="62">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>New report or document template (typical)</t>
-        </is>
-      </c>
-      <c r="B62" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="C62" s="10" t="inlineStr">
-        <is>
-          <t>man-days</t>
-        </is>
-      </c>
-      <c r="D62" s="15" t="inlineStr">
-        <is>
-          <t>Estimate: falls in the Small CR band.</t>
-        </is>
-      </c>
-      <c r="E62" s="8" t="n"/>
-      <c r="F62" s="8" t="n"/>
-      <c r="G62" s="8" t="n"/>
-      <c r="H62" s="8" t="n"/>
-      <c r="I62" s="8" t="n"/>
-      <c r="J62" s="8" t="n"/>
-      <c r="K62" s="8" t="n"/>
-      <c r="L62" s="8" t="n"/>
-      <c r="M62" s="8" t="n"/>
-      <c r="N62" s="9" t="n"/>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Infrastructure: AWS reference cost per month of the Production environment (USD)</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="n"/>
+      <c r="C63" s="7" t="n"/>
+      <c r="D63" s="7" t="n"/>
+      <c r="E63" s="7" t="n"/>
+      <c r="F63" s="7" t="n"/>
+      <c r="G63" s="7" t="n"/>
+      <c r="H63" s="7" t="n"/>
+      <c r="I63" s="7" t="n"/>
+      <c r="J63" s="7" t="n"/>
+      <c r="K63" s="7" t="n"/>
+      <c r="L63" s="7" t="n"/>
+      <c r="M63" s="7" t="n"/>
+      <c r="N63" s="7" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>Infrastructure: AWS reference cost per month (USD, production plus one UAT environment)</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="n"/>
-      <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="n"/>
-      <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="n"/>
-      <c r="G64" s="7" t="n"/>
-      <c r="H64" s="7" t="n"/>
-      <c r="I64" s="7" t="n"/>
-      <c r="J64" s="7" t="n"/>
-      <c r="K64" s="7" t="n"/>
-      <c r="L64" s="7" t="n"/>
-      <c r="M64" s="7" t="n"/>
-      <c r="N64" s="7" t="n"/>
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="G64" s="8" t="n"/>
+      <c r="H64" s="8" t="n"/>
+      <c r="I64" s="8" t="n"/>
+      <c r="J64" s="8" t="n"/>
+      <c r="K64" s="8" t="n"/>
+      <c r="L64" s="8" t="n"/>
+      <c r="M64" s="8" t="n"/>
+      <c r="N64" s="9" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>Small</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>Basis</t>
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>Application containers (API, web, scheduler)</t>
+        </is>
+      </c>
+      <c r="B65" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="C65" s="16" t="n">
+        <v>135</v>
+      </c>
+      <c r="D65" s="16" t="n">
+        <v>180</v>
+      </c>
+      <c r="E65" s="16" t="n">
+        <v>360</v>
+      </c>
+      <c r="F65" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: 2/3/4/8 containers of 1 vCPU, 2 GB (Fargate, Singapore).</t>
         </is>
       </c>
       <c r="G65" s="8" t="n"/>
@@ -4934,24 +4953,24 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>Application containers (API, web, scheduler)</t>
+          <t>Managed PostgreSQL 16 (instance and storage)</t>
         </is>
       </c>
       <c r="B66" s="16" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C66" s="16" t="n">
-        <v>135</v>
+        <v>320</v>
       </c>
       <c r="D66" s="16" t="n">
-        <v>180</v>
+        <v>640</v>
       </c>
       <c r="E66" s="16" t="n">
-        <v>360</v>
+        <v>1280</v>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
-          <t>Estimate: 2/3/4/8 containers of 1 vCPU, 2 GB (Fargate, Singapore).</t>
+          <t>Estimate: db.t4g.medium single-AZ / db.m7g.large Multi-AZ / m7g.xlarge Multi-AZ / m7g.2xlarge Multi-AZ (S20). Large and Enterprise: high availability.</t>
         </is>
       </c>
       <c r="G66" s="8" t="n"/>
@@ -4966,24 +4985,24 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>Managed PostgreSQL 16 (instance and storage)</t>
+          <t>Object storage and backups (documents, snapshots)</t>
         </is>
       </c>
       <c r="B67" s="16" t="n">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="C67" s="16" t="n">
-        <v>320</v>
+        <v>40</v>
       </c>
       <c r="D67" s="16" t="n">
-        <v>640</v>
+        <v>90</v>
       </c>
       <c r="E67" s="16" t="n">
-        <v>1280</v>
+        <v>180</v>
       </c>
       <c r="F67" s="15" t="inlineStr">
         <is>
-          <t>Estimate: db.t4g.medium single-AZ / db.m7g.large Multi-AZ / m7g.xlarge Multi-AZ / m7g.2xlarge Multi-AZ (S20).</t>
+          <t>Estimate: S3 and snapshot storage, growing with policies and uploads.</t>
         </is>
       </c>
       <c r="G67" s="8" t="n"/>
@@ -4998,24 +5017,24 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>Object storage and backups (documents, snapshots)</t>
+          <t>Network (load balancer, CDN, data transfer)</t>
         </is>
       </c>
       <c r="B68" s="16" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C68" s="16" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D68" s="16" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E68" s="16" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>Estimate: S3 and snapshot storage, growing with policies and uploads.</t>
+          <t>Estimate.</t>
         </is>
       </c>
       <c r="G68" s="8" t="n"/>
@@ -5030,20 +5049,20 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>Network (load balancer, CDN, data transfer)</t>
+          <t>Security and monitoring (WAF, logs, alarms, secrets, keys)</t>
         </is>
       </c>
       <c r="B69" s="16" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C69" s="16" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D69" s="16" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E69" s="16" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="F69" s="15" t="inlineStr">
         <is>
@@ -5062,24 +5081,24 @@
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>Security and monitoring (WAF, logs, alarms, secrets, keys)</t>
+          <t>Disaster recovery copy (cross-region backups)</t>
         </is>
       </c>
       <c r="B70" s="16" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="C70" s="16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D70" s="16" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="E70" s="16" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>Estimate.</t>
+          <t>Estimate: Enterprise only; optional for others. Not part of Pre-Prod.</t>
         </is>
       </c>
       <c r="G70" s="8" t="n"/>
@@ -5092,106 +5111,71 @@
       <c r="N70" s="9" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="10" t="inlineStr">
-        <is>
-          <t>UAT environment (scaled down)</t>
-        </is>
-      </c>
-      <c r="B71" s="16" t="n">
-        <v>120</v>
-      </c>
-      <c r="C71" s="16" t="n">
-        <v>200</v>
-      </c>
-      <c r="D71" s="16" t="n">
-        <v>350</v>
-      </c>
-      <c r="E71" s="16" t="n">
-        <v>600</v>
-      </c>
-      <c r="F71" s="15" t="inlineStr">
-        <is>
-          <t>Estimate.</t>
-        </is>
-      </c>
-      <c r="G71" s="8" t="n"/>
-      <c r="H71" s="8" t="n"/>
-      <c r="I71" s="8" t="n"/>
-      <c r="J71" s="8" t="n"/>
-      <c r="K71" s="8" t="n"/>
-      <c r="L71" s="8" t="n"/>
-      <c r="M71" s="8" t="n"/>
-      <c r="N71" s="9" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="10" t="inlineStr">
-        <is>
-          <t>Disaster recovery copy (cross-region backups)</t>
-        </is>
-      </c>
-      <c r="B72" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C72" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="16" t="n">
-        <v>400</v>
-      </c>
-      <c r="F72" s="15" t="inlineStr">
-        <is>
-          <t>Estimate: Enterprise only; optional for others.</t>
-        </is>
-      </c>
-      <c r="G72" s="8" t="n"/>
-      <c r="H72" s="8" t="n"/>
-      <c r="I72" s="8" t="n"/>
-      <c r="J72" s="8" t="n"/>
-      <c r="K72" s="8" t="n"/>
-      <c r="L72" s="8" t="n"/>
-      <c r="M72" s="8" t="n"/>
-      <c r="N72" s="9" t="n"/>
+      <c r="A71" s="18" t="inlineStr">
+        <is>
+          <t>Production reference cost per month (USD)</t>
+        </is>
+      </c>
+      <c r="B71" s="21">
+        <f>SUM(B65:B70)</f>
+        <v/>
+      </c>
+      <c r="C71" s="21">
+        <f>SUM(C65:C70)</f>
+        <v/>
+      </c>
+      <c r="D71" s="21">
+        <f>SUM(D65:D70)</f>
+        <v/>
+      </c>
+      <c r="E71" s="21">
+        <f>SUM(E65:E70)</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="18" t="inlineStr">
-        <is>
-          <t>Total AWS reference cost per month (USD)</t>
-        </is>
-      </c>
-      <c r="B73" s="21">
-        <f>SUM(B66:B72)</f>
-        <v/>
-      </c>
-      <c r="C73" s="21">
-        <f>SUM(C66:C72)</f>
-        <v/>
-      </c>
-      <c r="D73" s="21">
-        <f>SUM(D66:D72)</f>
-        <v/>
-      </c>
-      <c r="E73" s="21">
-        <f>SUM(E66:E72)</f>
-        <v/>
-      </c>
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Infrastructure: non-production environment sizes and Pre-Prod use</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="n"/>
+      <c r="C73" s="7" t="n"/>
+      <c r="D73" s="7" t="n"/>
+      <c r="E73" s="7" t="n"/>
+      <c r="F73" s="7" t="n"/>
+      <c r="G73" s="7" t="n"/>
+      <c r="H73" s="7" t="n"/>
+      <c r="I73" s="7" t="n"/>
+      <c r="J73" s="7" t="n"/>
+      <c r="K73" s="7" t="n"/>
+      <c r="L73" s="7" t="n"/>
+      <c r="M73" s="7" t="n"/>
+      <c r="N73" s="7" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="10" t="inlineStr">
-        <is>
-          <t>Azure cost relative to AWS</t>
-        </is>
-      </c>
-      <c r="B74" s="11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="F74" s="15" t="inlineStr">
-        <is>
-          <t>Assumption: comparable list prices in Southeast Asia (D4s v5 Linux about USD 158 a month, S21); +5% for managed PostgreSQL and WAF differences.</t>
-        </is>
-      </c>
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="n"/>
+      <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="n"/>
       <c r="H74" s="8" t="n"/>
       <c r="I74" s="8" t="n"/>
@@ -5204,17 +5188,24 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>Local partner cloud cost relative to AWS</t>
-        </is>
-      </c>
-      <c r="B75" s="11" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F75" s="15" t="inlineStr">
-        <is>
-          <t>Assumption: Philippine data-centre or partner cloud priced in PHP; lower compute and bandwidth, database run as managed VM. Confirm with a partner quotation.</t>
-        </is>
-      </c>
+          <t>Non-production environment, small: cloud cost per month</t>
+        </is>
+      </c>
+      <c r="B75" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D75" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: 1 container of 1 vCPU, 2 GB; PostgreSQL db.t4g.medium single-AZ, 50 GB; file store; backups 7 to 14 days. Dev in every tier; UAT of Small and Medium brokers.</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="n"/>
+      <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
       <c r="H75" s="8" t="n"/>
       <c r="I75" s="8" t="n"/>
@@ -5224,53 +5215,87 @@
       <c r="M75" s="8" t="n"/>
       <c r="N75" s="9" t="n"/>
     </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>Non-production environment, medium: cloud cost per month</t>
+        </is>
+      </c>
+      <c r="B76" s="16" t="n">
+        <v>300</v>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D76" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: 2 containers of 1 vCPU, 2 GB (the second for the UAT performance test); db.t4g.large single-AZ, 100 GB; file store; load balancer. SIT and UAT of Large and Enterprise brokers.</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="n"/>
+      <c r="F76" s="8" t="n"/>
+      <c r="G76" s="8" t="n"/>
+      <c r="H76" s="8" t="n"/>
+      <c r="I76" s="8" t="n"/>
+      <c r="J76" s="8" t="n"/>
+      <c r="K76" s="8" t="n"/>
+      <c r="L76" s="8" t="n"/>
+      <c r="M76" s="8" t="n"/>
+      <c r="N76" s="9" t="n"/>
+    </row>
     <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>Sample quote scenarios (used by Sample Quotes)</t>
-        </is>
-      </c>
-      <c r="B77" s="7" t="n"/>
-      <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="n"/>
-      <c r="E77" s="7" t="n"/>
-      <c r="F77" s="7" t="n"/>
-      <c r="G77" s="7" t="n"/>
-      <c r="H77" s="7" t="n"/>
-      <c r="I77" s="7" t="n"/>
-      <c r="J77" s="7" t="n"/>
-      <c r="K77" s="7" t="n"/>
-      <c r="L77" s="7" t="n"/>
-      <c r="M77" s="7" t="n"/>
-      <c r="N77" s="7" t="n"/>
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>Pre-Prod cloud cost relative to Production (without the DR copy)</t>
+        </is>
+      </c>
+      <c r="B77" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
+          <t>Assumption: Pre-Prod is restored from a production backup and runs at production topology and size, so the rehearsal measures real timings.</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="n"/>
+      <c r="F77" s="8" t="n"/>
+      <c r="G77" s="8" t="n"/>
+      <c r="H77" s="8" t="n"/>
+      <c r="I77" s="8" t="n"/>
+      <c r="J77" s="8" t="n"/>
+      <c r="K77" s="8" t="n"/>
+      <c r="L77" s="8" t="n"/>
+      <c r="M77" s="8" t="n"/>
+      <c r="N77" s="9" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>Driver</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>Example 1</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t>Example 2</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>Example 3</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr"/>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>Pre-Prod months of use around go-live</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="D78" s="15" t="inlineStr">
+        <is>
+          <t>Assumption: created before the cutover rehearsal and removed after hypercare (1 to 2 months). Billed per month of use.</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="n"/>
+      <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
       <c r="H78" s="8" t="n"/>
       <c r="I78" s="8" t="n"/>
@@ -5283,29 +5308,24 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>Broker profile</t>
-        </is>
-      </c>
-      <c r="B79" s="12" t="inlineStr">
-        <is>
-          <t>Small broker</t>
-        </is>
-      </c>
-      <c r="C79" s="12" t="inlineStr">
-        <is>
-          <t>Medium broker</t>
-        </is>
-      </c>
-      <c r="D79" s="12" t="inlineStr">
-        <is>
-          <t>Large broker</t>
-        </is>
-      </c>
-      <c r="F79" s="10" t="inlineStr">
-        <is>
-          <t>Label only.</t>
-        </is>
-      </c>
+          <t>Pre-Prod months of use per major release</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="D79" s="15" t="inlineStr">
+        <is>
+          <t>Assumption: created from a production backup for the release rehearsal and removed after the release.</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="n"/>
+      <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="n"/>
       <c r="H79" s="8" t="n"/>
       <c r="I79" s="8" t="n"/>
@@ -5318,23 +5338,24 @@
     <row r="80">
       <c r="A80" s="10" t="inlineStr">
         <is>
-          <t>Named users</t>
+          <t>Major releases per year (yearly hosting view only)</t>
         </is>
       </c>
       <c r="B80" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C80" s="14" t="n">
-        <v>60</v>
-      </c>
-      <c r="D80" s="14" t="n">
-        <v>180</v>
-      </c>
-      <c r="F80" s="10" t="inlineStr">
-        <is>
-          <t>Tier follows from the user count.</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>releases</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="inlineStr">
+        <is>
+          <t>Assumption for budgeting. Major releases are announced at least 6 months ahead (Release Notes and Roadmap); the invoice follows the actual months of use.</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="n"/>
+      <c r="F80" s="8" t="n"/>
       <c r="G80" s="8" t="n"/>
       <c r="H80" s="8" t="n"/>
       <c r="I80" s="8" t="n"/>
@@ -5344,98 +5365,67 @@
       <c r="M80" s="8" t="n"/>
       <c r="N80" s="9" t="n"/>
     </row>
-    <row r="81">
-      <c r="A81" s="10" t="inlineStr">
-        <is>
-          <t>Lines of business</t>
-        </is>
-      </c>
-      <c r="B81" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C81" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="D81" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="F81" s="10" t="inlineStr">
-        <is>
-          <t>Motor, fire, marine, casualty, engineering, bonds and so on.</t>
-        </is>
-      </c>
-      <c r="G81" s="8" t="n"/>
-      <c r="H81" s="8" t="n"/>
-      <c r="I81" s="8" t="n"/>
-      <c r="J81" s="8" t="n"/>
-      <c r="K81" s="8" t="n"/>
-      <c r="L81" s="8" t="n"/>
-      <c r="M81" s="8" t="n"/>
-      <c r="N81" s="9" t="n"/>
-    </row>
     <row r="82">
-      <c r="A82" s="10" t="inlineStr">
-        <is>
-          <t>Infrastructure provider (AWS, Azure, Local partner, Customer)</t>
-        </is>
-      </c>
-      <c r="B82" s="12" t="inlineStr">
-        <is>
-          <t>AWS</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="inlineStr">
-        <is>
-          <t>Azure</t>
-        </is>
-      </c>
-      <c r="D82" s="12" t="inlineStr">
-        <is>
-          <t>Local partner</t>
-        </is>
-      </c>
-      <c r="F82" s="10" t="inlineStr">
-        <is>
-          <t>"Customer" means the broker hosts itself: no infrastructure fee.</t>
-        </is>
-      </c>
-      <c r="G82" s="8" t="n"/>
-      <c r="H82" s="8" t="n"/>
-      <c r="I82" s="8" t="n"/>
-      <c r="J82" s="8" t="n"/>
-      <c r="K82" s="8" t="n"/>
-      <c r="L82" s="8" t="n"/>
-      <c r="M82" s="8" t="n"/>
-      <c r="N82" s="9" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="10" t="inlineStr">
-        <is>
-          <t>24x7 Severity 1 support (Yes/No)</t>
-        </is>
-      </c>
-      <c r="B83" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C83" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D83" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F83" s="10" t="inlineStr">
-        <is>
-          <t>Optional.</t>
-        </is>
-      </c>
-      <c r="G83" s="8" t="n"/>
-      <c r="H83" s="8" t="n"/>
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Infrastructure: environment set by tier, AWS reference cost per month (USD)</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="n"/>
+      <c r="C82" s="7" t="n"/>
+      <c r="D82" s="7" t="n"/>
+      <c r="E82" s="7" t="n"/>
+      <c r="F82" s="7" t="n"/>
+      <c r="G82" s="7" t="n"/>
+      <c r="H82" s="7" t="n"/>
+      <c r="I82" s="7" t="n"/>
+      <c r="J82" s="7" t="n"/>
+      <c r="K82" s="7" t="n"/>
+      <c r="L82" s="7" t="n"/>
+      <c r="M82" s="7" t="n"/>
+      <c r="N82" s="7" t="n"/>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>SIT</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>UAT</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>Standing environments</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>Pre-Prod per month of use</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>Environment set and basis</t>
+        </is>
+      </c>
       <c r="I83" s="8" t="n"/>
       <c r="J83" s="8" t="n"/>
       <c r="K83" s="8" t="n"/>
@@ -5444,27 +5434,38 @@
       <c r="N83" s="9" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="10" t="inlineStr">
-        <is>
-          <t>Extra training days</t>
-        </is>
-      </c>
-      <c r="B84" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C84" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D84" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="F84" s="10" t="inlineStr">
-        <is>
-          <t>Beyond the days included for the tier.</t>
-        </is>
-      </c>
-      <c r="G84" s="8" t="n"/>
-      <c r="H84" s="8" t="n"/>
+      <c r="A84" s="18">
+        <f>A28</f>
+        <v/>
+      </c>
+      <c r="B84" s="20">
+        <f>NP_Small_USD</f>
+        <v/>
+      </c>
+      <c r="C84" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="20">
+        <f>NP_Small_USD</f>
+        <v/>
+      </c>
+      <c r="E84" s="20">
+        <f>B71</f>
+        <v/>
+      </c>
+      <c r="F84" s="24">
+        <f>SUM(B84:E84)</f>
+        <v/>
+      </c>
+      <c r="G84" s="21">
+        <f>SUM(B65:B69)*PreProd_Factor</f>
+        <v/>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>Dev, UAT, Production, temporary Pre-Prod. Integration and SIT in Dev, then promoted to UAT for testing.</t>
+        </is>
+      </c>
       <c r="I84" s="8" t="n"/>
       <c r="J84" s="8" t="n"/>
       <c r="K84" s="8" t="n"/>
@@ -5473,27 +5474,38 @@
       <c r="N84" s="9" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="10" t="inlineStr">
-        <is>
-          <t>Extra legacy data sources to migrate</t>
-        </is>
-      </c>
-      <c r="B85" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C85" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F85" s="10" t="inlineStr">
-        <is>
-          <t>Beyond the standard templates.</t>
-        </is>
-      </c>
-      <c r="G85" s="8" t="n"/>
-      <c r="H85" s="8" t="n"/>
+      <c r="A85" s="18">
+        <f>A29</f>
+        <v/>
+      </c>
+      <c r="B85" s="20">
+        <f>NP_Small_USD</f>
+        <v/>
+      </c>
+      <c r="C85" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="20">
+        <f>NP_Small_USD</f>
+        <v/>
+      </c>
+      <c r="E85" s="20">
+        <f>C71</f>
+        <v/>
+      </c>
+      <c r="F85" s="24">
+        <f>SUM(B85:E85)</f>
+        <v/>
+      </c>
+      <c r="G85" s="21">
+        <f>SUM(C65:C69)*PreProd_Factor</f>
+        <v/>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>Dev, UAT, Production, temporary Pre-Prod. As Small.</t>
+        </is>
+      </c>
       <c r="I85" s="8" t="n"/>
       <c r="J85" s="8" t="n"/>
       <c r="K85" s="8" t="n"/>
@@ -5502,27 +5514,39 @@
       <c r="N85" s="9" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="10" t="inlineStr">
-        <is>
-          <t>Additional standard integrations</t>
-        </is>
-      </c>
-      <c r="B86" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C86" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D86" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F86" s="10" t="inlineStr">
-        <is>
-          <t>One-time.</t>
-        </is>
-      </c>
-      <c r="G86" s="8" t="n"/>
-      <c r="H86" s="8" t="n"/>
+      <c r="A86" s="18">
+        <f>A30</f>
+        <v/>
+      </c>
+      <c r="B86" s="20">
+        <f>NP_Small_USD</f>
+        <v/>
+      </c>
+      <c r="C86" s="20">
+        <f>NP_Med_USD</f>
+        <v/>
+      </c>
+      <c r="D86" s="20">
+        <f>NP_Med_USD</f>
+        <v/>
+      </c>
+      <c r="E86" s="20">
+        <f>D71</f>
+        <v/>
+      </c>
+      <c r="F86" s="24">
+        <f>SUM(B86:E86)</f>
+        <v/>
+      </c>
+      <c r="G86" s="21">
+        <f>SUM(D65:D69)*PreProd_Factor</f>
+        <v/>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>Dev, SIT, UAT, Production with high availability, temporary Pre-Prod. SIT and UAT are separate.</t>
+        </is>
+      </c>
       <c r="I86" s="8" t="n"/>
       <c r="J86" s="8" t="n"/>
       <c r="K86" s="8" t="n"/>
@@ -5530,72 +5554,475 @@
       <c r="M86" s="8" t="n"/>
       <c r="N86" s="9" t="n"/>
     </row>
+    <row r="87">
+      <c r="A87" s="18">
+        <f>A31</f>
+        <v/>
+      </c>
+      <c r="B87" s="20">
+        <f>NP_Small_USD</f>
+        <v/>
+      </c>
+      <c r="C87" s="20">
+        <f>NP_Med_USD</f>
+        <v/>
+      </c>
+      <c r="D87" s="20">
+        <f>NP_Med_USD</f>
+        <v/>
+      </c>
+      <c r="E87" s="20">
+        <f>E71</f>
+        <v/>
+      </c>
+      <c r="F87" s="24">
+        <f>SUM(B87:E87)</f>
+        <v/>
+      </c>
+      <c r="G87" s="21">
+        <f>SUM(E65:E69)*PreProd_Factor</f>
+        <v/>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>As Large, with the cross-region DR copy in Production.</t>
+        </is>
+      </c>
+      <c r="I87" s="8" t="n"/>
+      <c r="J87" s="8" t="n"/>
+      <c r="K87" s="8" t="n"/>
+      <c r="L87" s="8" t="n"/>
+      <c r="M87" s="8" t="n"/>
+      <c r="N87" s="9" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>Azure cost relative to AWS</t>
+        </is>
+      </c>
+      <c r="B88" s="11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F88" s="15" t="inlineStr">
+        <is>
+          <t>Assumption: comparable list prices in Southeast Asia (D4s v5 Linux about USD 158 a month, S21); +5% for managed PostgreSQL and WAF differences.</t>
+        </is>
+      </c>
+      <c r="G88" s="8" t="n"/>
+      <c r="H88" s="8" t="n"/>
+      <c r="I88" s="8" t="n"/>
+      <c r="J88" s="8" t="n"/>
+      <c r="K88" s="8" t="n"/>
+      <c r="L88" s="8" t="n"/>
+      <c r="M88" s="8" t="n"/>
+      <c r="N88" s="9" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>Local partner cloud cost relative to AWS</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F89" s="15" t="inlineStr">
+        <is>
+          <t>Assumption: Philippine data-centre or partner cloud priced in PHP; lower compute and bandwidth, database run as managed VM. Confirm with a partner quotation.</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="n"/>
+      <c r="H89" s="8" t="n"/>
+      <c r="I89" s="8" t="n"/>
+      <c r="J89" s="8" t="n"/>
+      <c r="K89" s="8" t="n"/>
+      <c r="L89" s="8" t="n"/>
+      <c r="M89" s="8" t="n"/>
+      <c r="N89" s="9" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>Sample quote scenarios (used by Sample Quotes)</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="n"/>
+      <c r="C91" s="7" t="n"/>
+      <c r="D91" s="7" t="n"/>
+      <c r="E91" s="7" t="n"/>
+      <c r="F91" s="7" t="n"/>
+      <c r="G91" s="7" t="n"/>
+      <c r="H91" s="7" t="n"/>
+      <c r="I91" s="7" t="n"/>
+      <c r="J91" s="7" t="n"/>
+      <c r="K91" s="7" t="n"/>
+      <c r="L91" s="7" t="n"/>
+      <c r="M91" s="7" t="n"/>
+      <c r="N91" s="7" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Example 1</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Example 2</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Example 3</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr"/>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="G92" s="8" t="n"/>
+      <c r="H92" s="8" t="n"/>
+      <c r="I92" s="8" t="n"/>
+      <c r="J92" s="8" t="n"/>
+      <c r="K92" s="8" t="n"/>
+      <c r="L92" s="8" t="n"/>
+      <c r="M92" s="8" t="n"/>
+      <c r="N92" s="9" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>Broker profile</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>Small broker</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>Medium broker</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>Large broker</t>
+        </is>
+      </c>
+      <c r="F93" s="10" t="inlineStr">
+        <is>
+          <t>Label only.</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="n"/>
+      <c r="H93" s="8" t="n"/>
+      <c r="I93" s="8" t="n"/>
+      <c r="J93" s="8" t="n"/>
+      <c r="K93" s="8" t="n"/>
+      <c r="L93" s="8" t="n"/>
+      <c r="M93" s="8" t="n"/>
+      <c r="N93" s="9" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>Named users</t>
+        </is>
+      </c>
+      <c r="B94" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="C94" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="D94" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="F94" s="10" t="inlineStr">
+        <is>
+          <t>Tier follows from the user count.</t>
+        </is>
+      </c>
+      <c r="G94" s="8" t="n"/>
+      <c r="H94" s="8" t="n"/>
+      <c r="I94" s="8" t="n"/>
+      <c r="J94" s="8" t="n"/>
+      <c r="K94" s="8" t="n"/>
+      <c r="L94" s="8" t="n"/>
+      <c r="M94" s="8" t="n"/>
+      <c r="N94" s="9" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>Lines of business</t>
+        </is>
+      </c>
+      <c r="B95" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C95" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="D95" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F95" s="10" t="inlineStr">
+        <is>
+          <t>Motor, fire, marine, casualty, engineering, bonds and so on.</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="n"/>
+      <c r="H95" s="8" t="n"/>
+      <c r="I95" s="8" t="n"/>
+      <c r="J95" s="8" t="n"/>
+      <c r="K95" s="8" t="n"/>
+      <c r="L95" s="8" t="n"/>
+      <c r="M95" s="8" t="n"/>
+      <c r="N95" s="9" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>Infrastructure provider (AWS, Azure, Local partner, Customer)</t>
+        </is>
+      </c>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>Azure</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>Local partner</t>
+        </is>
+      </c>
+      <c r="F96" s="10" t="inlineStr">
+        <is>
+          <t>"Customer" means the broker hosts itself: no infrastructure fee.</t>
+        </is>
+      </c>
+      <c r="G96" s="8" t="n"/>
+      <c r="H96" s="8" t="n"/>
+      <c r="I96" s="8" t="n"/>
+      <c r="J96" s="8" t="n"/>
+      <c r="K96" s="8" t="n"/>
+      <c r="L96" s="8" t="n"/>
+      <c r="M96" s="8" t="n"/>
+      <c r="N96" s="9" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>24x7 Severity 1 support (Yes/No)</t>
+        </is>
+      </c>
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D97" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F97" s="10" t="inlineStr">
+        <is>
+          <t>Optional.</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="n"/>
+      <c r="H97" s="8" t="n"/>
+      <c r="I97" s="8" t="n"/>
+      <c r="J97" s="8" t="n"/>
+      <c r="K97" s="8" t="n"/>
+      <c r="L97" s="8" t="n"/>
+      <c r="M97" s="8" t="n"/>
+      <c r="N97" s="9" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>Extra training days</t>
+        </is>
+      </c>
+      <c r="B98" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D98" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F98" s="10" t="inlineStr">
+        <is>
+          <t>Beyond the days included for the tier.</t>
+        </is>
+      </c>
+      <c r="G98" s="8" t="n"/>
+      <c r="H98" s="8" t="n"/>
+      <c r="I98" s="8" t="n"/>
+      <c r="J98" s="8" t="n"/>
+      <c r="K98" s="8" t="n"/>
+      <c r="L98" s="8" t="n"/>
+      <c r="M98" s="8" t="n"/>
+      <c r="N98" s="9" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>Extra legacy data sources to migrate</t>
+        </is>
+      </c>
+      <c r="B99" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F99" s="10" t="inlineStr">
+        <is>
+          <t>Beyond the standard templates.</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="n"/>
+      <c r="H99" s="8" t="n"/>
+      <c r="I99" s="8" t="n"/>
+      <c r="J99" s="8" t="n"/>
+      <c r="K99" s="8" t="n"/>
+      <c r="L99" s="8" t="n"/>
+      <c r="M99" s="8" t="n"/>
+      <c r="N99" s="9" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>Additional standard integrations</t>
+        </is>
+      </c>
+      <c r="B100" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F100" s="10" t="inlineStr">
+        <is>
+          <t>One-time.</t>
+        </is>
+      </c>
+      <c r="G100" s="8" t="n"/>
+      <c r="H100" s="8" t="n"/>
+      <c r="I100" s="8" t="n"/>
+      <c r="J100" s="8" t="n"/>
+      <c r="K100" s="8" t="n"/>
+      <c r="L100" s="8" t="n"/>
+      <c r="M100" s="8" t="n"/>
+      <c r="N100" s="9" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="58">
+  <mergeCells count="68">
     <mergeCell ref="E36:N36"/>
     <mergeCell ref="D59:N59"/>
+    <mergeCell ref="D79:N79"/>
     <mergeCell ref="D50:N50"/>
-    <mergeCell ref="F86:N86"/>
-    <mergeCell ref="F80:N80"/>
+    <mergeCell ref="H84:N84"/>
     <mergeCell ref="D60:N60"/>
-    <mergeCell ref="F85:N85"/>
+    <mergeCell ref="F95:N95"/>
     <mergeCell ref="D19:N19"/>
+    <mergeCell ref="F94:N94"/>
     <mergeCell ref="D10:N10"/>
+    <mergeCell ref="H87:N87"/>
     <mergeCell ref="F70:N70"/>
-    <mergeCell ref="F79:N79"/>
+    <mergeCell ref="F97:N97"/>
     <mergeCell ref="F66:N66"/>
     <mergeCell ref="D46:N46"/>
-    <mergeCell ref="F75:N75"/>
+    <mergeCell ref="H86:N86"/>
+    <mergeCell ref="D80:N80"/>
     <mergeCell ref="E41:N41"/>
+    <mergeCell ref="F100:N100"/>
     <mergeCell ref="D45:N45"/>
-    <mergeCell ref="F72:N72"/>
     <mergeCell ref="E37:N37"/>
     <mergeCell ref="D6:N6"/>
-    <mergeCell ref="F81:N81"/>
     <mergeCell ref="D52:N52"/>
+    <mergeCell ref="D77:N77"/>
     <mergeCell ref="D11:N11"/>
     <mergeCell ref="D49:N49"/>
     <mergeCell ref="D57:N57"/>
-    <mergeCell ref="F71:N71"/>
+    <mergeCell ref="F93:N93"/>
+    <mergeCell ref="F96:N96"/>
     <mergeCell ref="D13:N13"/>
     <mergeCell ref="F67:N67"/>
+    <mergeCell ref="D76:N76"/>
     <mergeCell ref="E42:N42"/>
     <mergeCell ref="D48:N48"/>
     <mergeCell ref="D17:N17"/>
     <mergeCell ref="D61:N61"/>
+    <mergeCell ref="F92:N92"/>
+    <mergeCell ref="D75:N75"/>
     <mergeCell ref="D53:N53"/>
-    <mergeCell ref="F82:N82"/>
     <mergeCell ref="E39:N39"/>
     <mergeCell ref="D16:N16"/>
     <mergeCell ref="D47:N47"/>
+    <mergeCell ref="F98:N98"/>
     <mergeCell ref="D7:N7"/>
+    <mergeCell ref="D78:N78"/>
+    <mergeCell ref="H83:N83"/>
     <mergeCell ref="E35:N35"/>
+    <mergeCell ref="F88:N88"/>
+    <mergeCell ref="F64:N64"/>
     <mergeCell ref="E38:N38"/>
-    <mergeCell ref="D62:N62"/>
     <mergeCell ref="A32:N32"/>
     <mergeCell ref="D18:N18"/>
     <mergeCell ref="D56:N56"/>
     <mergeCell ref="F69:N69"/>
     <mergeCell ref="D9:N9"/>
-    <mergeCell ref="F78:N78"/>
     <mergeCell ref="D12:N12"/>
     <mergeCell ref="D58:N58"/>
     <mergeCell ref="D8:N8"/>
     <mergeCell ref="F68:N68"/>
     <mergeCell ref="F65:N65"/>
+    <mergeCell ref="D74:N74"/>
+    <mergeCell ref="H85:N85"/>
+    <mergeCell ref="F99:N99"/>
     <mergeCell ref="D15:N15"/>
-    <mergeCell ref="F84:N84"/>
+    <mergeCell ref="F89:N89"/>
     <mergeCell ref="D5:N5"/>
     <mergeCell ref="D51:N51"/>
-    <mergeCell ref="F74:N74"/>
     <mergeCell ref="D14:N14"/>
-    <mergeCell ref="F83:N83"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="B82:D82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B96:D96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"AWS,Azure,Local partner,Customer"</formula1>
     </dataValidation>
-    <dataValidation sqref="B83:D83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B97:D97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5705,11 +6132,11 @@
         <f>Inputs!A28</f>
         <v/>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="25">
         <f>Inputs!B28</f>
         <v/>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <f>IF(Inputs!C28&gt;=100000,"and above",Inputs!C28)</f>
         <v/>
       </c>
@@ -5731,15 +6158,15 @@
         <f>Inputs!E28</f>
         <v/>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="25">
         <f>Inputs!F28</f>
         <v/>
       </c>
-      <c r="I5" s="24">
+      <c r="I5" s="25">
         <f>Inputs!H28</f>
         <v/>
       </c>
-      <c r="J5" s="24">
+      <c r="J5" s="25">
         <f>Inputs!I28</f>
         <v/>
       </c>
@@ -5749,11 +6176,11 @@
         <f>Inputs!A29</f>
         <v/>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="25">
         <f>Inputs!B29</f>
         <v/>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <f>IF(Inputs!C29&gt;=100000,"and above",Inputs!C29)</f>
         <v/>
       </c>
@@ -5775,15 +6202,15 @@
         <f>Inputs!E29</f>
         <v/>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="25">
         <f>Inputs!F29</f>
         <v/>
       </c>
-      <c r="I6" s="24">
+      <c r="I6" s="25">
         <f>Inputs!H29</f>
         <v/>
       </c>
-      <c r="J6" s="24">
+      <c r="J6" s="25">
         <f>Inputs!I29</f>
         <v/>
       </c>
@@ -5793,11 +6220,11 @@
         <f>Inputs!A30</f>
         <v/>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="25">
         <f>Inputs!B30</f>
         <v/>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="25">
         <f>IF(Inputs!C30&gt;=100000,"and above",Inputs!C30)</f>
         <v/>
       </c>
@@ -5819,15 +6246,15 @@
         <f>Inputs!E30</f>
         <v/>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="25">
         <f>Inputs!F30</f>
         <v/>
       </c>
-      <c r="I7" s="24">
+      <c r="I7" s="25">
         <f>Inputs!H30</f>
         <v/>
       </c>
-      <c r="J7" s="24">
+      <c r="J7" s="25">
         <f>Inputs!I30</f>
         <v/>
       </c>
@@ -5837,11 +6264,11 @@
         <f>Inputs!A31</f>
         <v/>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="25">
         <f>Inputs!B31</f>
         <v/>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <f>IF(Inputs!C31&gt;=100000,"and above",Inputs!C31)</f>
         <v/>
       </c>
@@ -5863,15 +6290,15 @@
         <f>Inputs!E31</f>
         <v/>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="25">
         <f>Inputs!F31</f>
         <v/>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="25">
         <f>Inputs!H31</f>
         <v/>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="25">
         <f>Inputs!I31</f>
         <v/>
       </c>
@@ -5893,7 +6320,7 @@
       <c r="J10" s="7" t="n"/>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>Each user is priced at the rate of the slab it falls in. Example: 40 users = 25 users at the Small rate + 15 users at the Medium rate. The broker tier (by total users) sets implementation effort, minimum billable users, included training and infrastructure size.</t>
         </is>
@@ -5972,11 +6399,11 @@
         <f>Inputs!A28</f>
         <v/>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="25">
         <f>Inputs!J28</f>
         <v/>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="27">
         <f>Inputs!M28</f>
         <v/>
       </c>
@@ -5992,7 +6419,7 @@
         <f>'Subscription Model'!C8</f>
         <v/>
       </c>
-      <c r="G15" s="27">
+      <c r="G15" s="28">
         <f>F15/C15</f>
         <v/>
       </c>
@@ -6000,7 +6427,7 @@
         <f>'Perpetual Model'!H9/5</f>
         <v/>
       </c>
-      <c r="I15" s="27">
+      <c r="I15" s="28">
         <f>H15/C15</f>
         <v/>
       </c>
@@ -6014,11 +6441,11 @@
         <f>Inputs!A29</f>
         <v/>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="25">
         <f>Inputs!J29</f>
         <v/>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="27">
         <f>Inputs!M29</f>
         <v/>
       </c>
@@ -6034,7 +6461,7 @@
         <f>'Subscription Model'!C16</f>
         <v/>
       </c>
-      <c r="G16" s="27">
+      <c r="G16" s="28">
         <f>F16/C16</f>
         <v/>
       </c>
@@ -6042,7 +6469,7 @@
         <f>'Perpetual Model'!H17/5</f>
         <v/>
       </c>
-      <c r="I16" s="27">
+      <c r="I16" s="28">
         <f>H16/C16</f>
         <v/>
       </c>
@@ -6056,11 +6483,11 @@
         <f>Inputs!A30</f>
         <v/>
       </c>
-      <c r="B17" s="24">
+      <c r="B17" s="25">
         <f>Inputs!J30</f>
         <v/>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="27">
         <f>Inputs!M30</f>
         <v/>
       </c>
@@ -6076,7 +6503,7 @@
         <f>'Subscription Model'!C24</f>
         <v/>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="28">
         <f>F17/C17</f>
         <v/>
       </c>
@@ -6084,7 +6511,7 @@
         <f>'Perpetual Model'!H25/5</f>
         <v/>
       </c>
-      <c r="I17" s="27">
+      <c r="I17" s="28">
         <f>H17/C17</f>
         <v/>
       </c>
@@ -6098,11 +6525,11 @@
         <f>Inputs!A31</f>
         <v/>
       </c>
-      <c r="B18" s="24">
+      <c r="B18" s="25">
         <f>Inputs!J31</f>
         <v/>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="27">
         <f>Inputs!M31</f>
         <v/>
       </c>
@@ -6118,7 +6545,7 @@
         <f>'Subscription Model'!C32</f>
         <v/>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="28">
         <f>F18/C18</f>
         <v/>
       </c>
@@ -6126,7 +6553,7 @@
         <f>'Perpetual Model'!H33/5</f>
         <v/>
       </c>
-      <c r="I18" s="27">
+      <c r="I18" s="28">
         <f>H18/C18</f>
         <v/>
       </c>
@@ -6243,20 +6670,20 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28">
+      <c r="A5" s="29">
         <f>Inputs!A28&amp;" (reference)"</f>
         <v/>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>Users / lines of business</t>
         </is>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <f>Inputs!J28</f>
         <v/>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <f>Inputs!K28</f>
         <v/>
       </c>
@@ -6379,33 +6806,33 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Total excl. VAT</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr"/>
-      <c r="C9" s="33">
+      <c r="B9" s="33" t="inlineStr"/>
+      <c r="C9" s="24">
         <f>SUM(C6:C8)</f>
         <v/>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="24">
         <f>SUM(D6:D8)</f>
         <v/>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="24">
         <f>SUM(E6:E8)</f>
         <v/>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="24">
         <f>SUM(F6:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="24">
         <f>SUM(G6:G8)</f>
         <v/>
       </c>
-      <c r="H9" s="33">
+      <c r="H9" s="24">
         <f>SUM(H6:H8)</f>
         <v/>
       </c>
@@ -6490,20 +6917,20 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28">
+      <c r="A13" s="29">
         <f>Inputs!A29&amp;" (reference)"</f>
         <v/>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Users / lines of business</t>
         </is>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <f>Inputs!J29</f>
         <v/>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <f>Inputs!K29</f>
         <v/>
       </c>
@@ -6626,33 +7053,33 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="31" t="inlineStr">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>Total excl. VAT</t>
         </is>
       </c>
-      <c r="B17" s="32" t="inlineStr"/>
-      <c r="C17" s="33">
+      <c r="B17" s="33" t="inlineStr"/>
+      <c r="C17" s="24">
         <f>SUM(C14:C16)</f>
         <v/>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="24">
         <f>SUM(D14:D16)</f>
         <v/>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="24">
         <f>SUM(E14:E16)</f>
         <v/>
       </c>
-      <c r="F17" s="33">
+      <c r="F17" s="24">
         <f>SUM(F14:F16)</f>
         <v/>
       </c>
-      <c r="G17" s="33">
+      <c r="G17" s="24">
         <f>SUM(G14:G16)</f>
         <v/>
       </c>
-      <c r="H17" s="33">
+      <c r="H17" s="24">
         <f>SUM(H14:H16)</f>
         <v/>
       </c>
@@ -6737,20 +7164,20 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="28">
+      <c r="A21" s="29">
         <f>Inputs!A30&amp;" (reference)"</f>
         <v/>
       </c>
-      <c r="B21" s="29" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>Users / lines of business</t>
         </is>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <f>Inputs!J30</f>
         <v/>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="31">
         <f>Inputs!K30</f>
         <v/>
       </c>
@@ -6873,33 +7300,33 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="31" t="inlineStr">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>Total excl. VAT</t>
         </is>
       </c>
-      <c r="B25" s="32" t="inlineStr"/>
-      <c r="C25" s="33">
+      <c r="B25" s="33" t="inlineStr"/>
+      <c r="C25" s="24">
         <f>SUM(C22:C24)</f>
         <v/>
       </c>
-      <c r="D25" s="33">
+      <c r="D25" s="24">
         <f>SUM(D22:D24)</f>
         <v/>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="24">
         <f>SUM(E22:E24)</f>
         <v/>
       </c>
-      <c r="F25" s="33">
+      <c r="F25" s="24">
         <f>SUM(F22:F24)</f>
         <v/>
       </c>
-      <c r="G25" s="33">
+      <c r="G25" s="24">
         <f>SUM(G22:G24)</f>
         <v/>
       </c>
-      <c r="H25" s="33">
+      <c r="H25" s="24">
         <f>SUM(H22:H24)</f>
         <v/>
       </c>
@@ -6984,20 +7411,20 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="28">
+      <c r="A29" s="29">
         <f>Inputs!A31&amp;" (reference)"</f>
         <v/>
       </c>
-      <c r="B29" s="29" t="inlineStr">
+      <c r="B29" s="30" t="inlineStr">
         <is>
           <t>Users / lines of business</t>
         </is>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="31">
         <f>Inputs!J31</f>
         <v/>
       </c>
-      <c r="D29" s="30">
+      <c r="D29" s="31">
         <f>Inputs!K31</f>
         <v/>
       </c>
@@ -7120,33 +7547,33 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="31" t="inlineStr">
+      <c r="A33" s="32" t="inlineStr">
         <is>
           <t>Total excl. VAT</t>
         </is>
       </c>
-      <c r="B33" s="32" t="inlineStr"/>
-      <c r="C33" s="33">
+      <c r="B33" s="33" t="inlineStr"/>
+      <c r="C33" s="24">
         <f>SUM(C30:C32)</f>
         <v/>
       </c>
-      <c r="D33" s="33">
+      <c r="D33" s="24">
         <f>SUM(D30:D32)</f>
         <v/>
       </c>
-      <c r="E33" s="33">
+      <c r="E33" s="24">
         <f>SUM(E30:E32)</f>
         <v/>
       </c>
-      <c r="F33" s="33">
+      <c r="F33" s="24">
         <f>SUM(F30:F32)</f>
         <v/>
       </c>
-      <c r="G33" s="33">
+      <c r="G33" s="24">
         <f>SUM(G30:G32)</f>
         <v/>
       </c>
-      <c r="H33" s="33">
+      <c r="H33" s="24">
         <f>SUM(H30:H32)</f>
         <v/>
       </c>
@@ -7314,7 +7741,7 @@
         <f>Inputs!B28&amp;" - "&amp;IF(Inputs!C28&gt;=100000,"above",Inputs!C28)</f>
         <v/>
       </c>
-      <c r="C44" s="24">
+      <c r="C44" s="25">
         <f>MAX(0,MIN($C$39,Inputs!C28)-Inputs!B28+1)</f>
         <v/>
       </c>
@@ -7336,7 +7763,7 @@
         <f>Inputs!B29&amp;" - "&amp;IF(Inputs!C29&gt;=100000,"above",Inputs!C29)</f>
         <v/>
       </c>
-      <c r="C45" s="24">
+      <c r="C45" s="25">
         <f>MAX(0,MIN($C$39,Inputs!C29)-Inputs!B29+1)</f>
         <v/>
       </c>
@@ -7358,7 +7785,7 @@
         <f>Inputs!B30&amp;" - "&amp;IF(Inputs!C30&gt;=100000,"above",Inputs!C30)</f>
         <v/>
       </c>
-      <c r="C46" s="24">
+      <c r="C46" s="25">
         <f>MAX(0,MIN($C$39,Inputs!C30)-Inputs!B30+1)</f>
         <v/>
       </c>
@@ -7380,7 +7807,7 @@
         <f>Inputs!B31&amp;" - "&amp;IF(Inputs!C31&gt;=100000,"above",Inputs!C31)</f>
         <v/>
       </c>
-      <c r="C47" s="24">
+      <c r="C47" s="25">
         <f>MAX(0,MIN($C$39,Inputs!C31)-Inputs!B31+1)</f>
         <v/>
       </c>
@@ -7399,7 +7826,7 @@
           <t>Perpetual licence fee</t>
         </is>
       </c>
-      <c r="E48" s="33">
+      <c r="E48" s="24">
         <f>SUM(E44:E47)</f>
         <v/>
       </c>
@@ -7437,7 +7864,7 @@
           <t>Implementation man-days (before rounding)</t>
         </is>
       </c>
-      <c r="E51" s="24">
+      <c r="E51" s="25">
         <f>INDEX(Inputs!$G$28:$G$31,MATCH($C$39,Inputs!$B$28:$B$31,1))+MAX(0,$C$40-INDEX(Inputs!$H$28:$H$31,MATCH($C$39,Inputs!$B$28:$B$31,1)))*Days_per_LOB</f>
         <v/>
       </c>
@@ -7587,32 +8014,32 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="31" t="inlineStr">
+      <c r="A57" s="32" t="inlineStr">
         <is>
           <t>Total excl. VAT</t>
         </is>
       </c>
-      <c r="C57" s="33">
+      <c r="C57" s="24">
         <f>SUM(C54:C56)</f>
         <v/>
       </c>
-      <c r="D57" s="33">
+      <c r="D57" s="24">
         <f>SUM(D54:D56)</f>
         <v/>
       </c>
-      <c r="E57" s="33">
+      <c r="E57" s="24">
         <f>SUM(E54:E56)</f>
         <v/>
       </c>
-      <c r="F57" s="33">
+      <c r="F57" s="24">
         <f>SUM(F54:F56)</f>
         <v/>
       </c>
-      <c r="G57" s="33">
+      <c r="G57" s="24">
         <f>SUM(G54:G56)</f>
         <v/>
       </c>
-      <c r="H57" s="33">
+      <c r="H57" s="24">
         <f>SUM(H54:H56)</f>
         <v/>
       </c>
@@ -7788,20 +8215,20 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28">
+      <c r="A5" s="29">
         <f>Inputs!A28&amp;" (reference)"</f>
         <v/>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>Users / billable users</t>
         </is>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <f>Inputs!J28</f>
         <v/>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <f>MAX($C$5,INDEX(Inputs!$F$28:$F$31,MATCH($C$5,Inputs!$B$28:$B$31,1)))</f>
         <v/>
       </c>
@@ -7913,33 +8340,33 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Total excl. VAT</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr"/>
-      <c r="C9" s="33">
+      <c r="B9" s="33" t="inlineStr"/>
+      <c r="C9" s="24">
         <f>C7+C8</f>
         <v/>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="24">
         <f>D7+D8</f>
         <v/>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="24">
         <f>E7+E8</f>
         <v/>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="24">
         <f>F7+F8</f>
         <v/>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="24">
         <f>G7+G8</f>
         <v/>
       </c>
-      <c r="H9" s="33">
+      <c r="H9" s="24">
         <f>H7+H8</f>
         <v/>
       </c>
@@ -8019,20 +8446,20 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="28">
+      <c r="A13" s="29">
         <f>Inputs!A29&amp;" (reference)"</f>
         <v/>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Users / billable users</t>
         </is>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <f>Inputs!J29</f>
         <v/>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <f>MAX($C$13,INDEX(Inputs!$F$28:$F$31,MATCH($C$13,Inputs!$B$28:$B$31,1)))</f>
         <v/>
       </c>
@@ -8144,33 +8571,33 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="31" t="inlineStr">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>Total excl. VAT</t>
         </is>
       </c>
-      <c r="B17" s="32" t="inlineStr"/>
-      <c r="C17" s="33">
+      <c r="B17" s="33" t="inlineStr"/>
+      <c r="C17" s="24">
         <f>C15+C16</f>
         <v/>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="24">
         <f>D15+D16</f>
         <v/>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="24">
         <f>E15+E16</f>
         <v/>
       </c>
-      <c r="F17" s="33">
+      <c r="F17" s="24">
         <f>F15+F16</f>
         <v/>
       </c>
-      <c r="G17" s="33">
+      <c r="G17" s="24">
         <f>G15+G16</f>
         <v/>
       </c>
-      <c r="H17" s="33">
+      <c r="H17" s="24">
         <f>H15+H16</f>
         <v/>
       </c>
@@ -8250,20 +8677,20 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="28">
+      <c r="A21" s="29">
         <f>Inputs!A30&amp;" (reference)"</f>
         <v/>
       </c>
-      <c r="B21" s="29" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>Users / billable users</t>
         </is>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <f>Inputs!J30</f>
         <v/>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="31">
         <f>MAX($C$21,INDEX(Inputs!$F$28:$F$31,MATCH($C$21,Inputs!$B$28:$B$31,1)))</f>
         <v/>
       </c>
@@ -8375,33 +8802,33 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="31" t="inlineStr">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>Total excl. VAT</t>
         </is>
       </c>
-      <c r="B25" s="32" t="inlineStr"/>
-      <c r="C25" s="33">
+      <c r="B25" s="33" t="inlineStr"/>
+      <c r="C25" s="24">
         <f>C23+C24</f>
         <v/>
       </c>
-      <c r="D25" s="33">
+      <c r="D25" s="24">
         <f>D23+D24</f>
         <v/>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="24">
         <f>E23+E24</f>
         <v/>
       </c>
-      <c r="F25" s="33">
+      <c r="F25" s="24">
         <f>F23+F24</f>
         <v/>
       </c>
-      <c r="G25" s="33">
+      <c r="G25" s="24">
         <f>G23+G24</f>
         <v/>
       </c>
-      <c r="H25" s="33">
+      <c r="H25" s="24">
         <f>H23+H24</f>
         <v/>
       </c>
@@ -8481,20 +8908,20 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="28">
+      <c r="A29" s="29">
         <f>Inputs!A31&amp;" (reference)"</f>
         <v/>
       </c>
-      <c r="B29" s="29" t="inlineStr">
+      <c r="B29" s="30" t="inlineStr">
         <is>
           <t>Users / billable users</t>
         </is>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="31">
         <f>Inputs!J31</f>
         <v/>
       </c>
-      <c r="D29" s="30">
+      <c r="D29" s="31">
         <f>MAX($C$29,INDEX(Inputs!$F$28:$F$31,MATCH($C$29,Inputs!$B$28:$B$31,1)))</f>
         <v/>
       </c>
@@ -8606,33 +9033,33 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="31" t="inlineStr">
+      <c r="A33" s="32" t="inlineStr">
         <is>
           <t>Total excl. VAT</t>
         </is>
       </c>
-      <c r="B33" s="32" t="inlineStr"/>
-      <c r="C33" s="33">
+      <c r="B33" s="33" t="inlineStr"/>
+      <c r="C33" s="24">
         <f>C31+C32</f>
         <v/>
       </c>
-      <c r="D33" s="33">
+      <c r="D33" s="24">
         <f>D31+D32</f>
         <v/>
       </c>
-      <c r="E33" s="33">
+      <c r="E33" s="24">
         <f>E31+E32</f>
         <v/>
       </c>
-      <c r="F33" s="33">
+      <c r="F33" s="24">
         <f>F31+F32</f>
         <v/>
       </c>
-      <c r="G33" s="33">
+      <c r="G33" s="24">
         <f>G31+G32</f>
         <v/>
       </c>
-      <c r="H33" s="33">
+      <c r="H33" s="24">
         <f>H31+H32</f>
         <v/>
       </c>
@@ -8770,7 +9197,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="28">
+      <c r="A40" s="29">
         <f>Inputs!A28</f>
         <v/>
       </c>
@@ -8809,7 +9236,7 @@
         <f>SUM('Perpetual Model'!$C$9:G9)</f>
         <v/>
       </c>
-      <c r="H41" s="31">
+      <c r="H41" s="32">
         <f>IF(MIN(C43:G43)=99,"Beyond Year 5","Year "&amp;MIN(C43:G43))</f>
         <v/>
       </c>
@@ -8873,7 +9300,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="28">
+      <c r="A45" s="29">
         <f>Inputs!A29</f>
         <v/>
       </c>
@@ -8912,7 +9339,7 @@
         <f>SUM('Perpetual Model'!$C$17:G17)</f>
         <v/>
       </c>
-      <c r="H46" s="31">
+      <c r="H46" s="32">
         <f>IF(MIN(C48:G48)=99,"Beyond Year 5","Year "&amp;MIN(C48:G48))</f>
         <v/>
       </c>
@@ -8976,7 +9403,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="28">
+      <c r="A50" s="29">
         <f>Inputs!A30</f>
         <v/>
       </c>
@@ -9015,7 +9442,7 @@
         <f>SUM('Perpetual Model'!$C$25:G25)</f>
         <v/>
       </c>
-      <c r="H51" s="31">
+      <c r="H51" s="32">
         <f>IF(MIN(C53:G53)=99,"Beyond Year 5","Year "&amp;MIN(C53:G53))</f>
         <v/>
       </c>
@@ -9079,7 +9506,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="28">
+      <c r="A55" s="29">
         <f>Inputs!A31</f>
         <v/>
       </c>
@@ -9118,7 +9545,7 @@
         <f>SUM('Perpetual Model'!$C$33:G33)</f>
         <v/>
       </c>
-      <c r="H56" s="31">
+      <c r="H56" s="32">
         <f>IF(MIN(C58:G58)=99,"Beyond Year 5","Year "&amp;MIN(C58:G58))</f>
         <v/>
       </c>
@@ -9224,7 +9651,7 @@
           <t>Billable users (minimum for tier applies)</t>
         </is>
       </c>
-      <c r="C64" s="24">
+      <c r="C64" s="25">
         <f>MAX(C62,INDEX(Inputs!$F$28:$F$31,MATCH(C62,Inputs!$B$28:$B$31,1)))</f>
         <v/>
       </c>
@@ -9265,7 +9692,7 @@
         <f>Inputs!B28&amp;" - "&amp;IF(Inputs!C28&gt;=100000,"above",Inputs!C28)</f>
         <v/>
       </c>
-      <c r="C67" s="24">
+      <c r="C67" s="25">
         <f>MAX(0,MIN($C$64,Inputs!C28)-Inputs!B28+1)</f>
         <v/>
       </c>
@@ -9287,7 +9714,7 @@
         <f>Inputs!B29&amp;" - "&amp;IF(Inputs!C29&gt;=100000,"above",Inputs!C29)</f>
         <v/>
       </c>
-      <c r="C68" s="24">
+      <c r="C68" s="25">
         <f>MAX(0,MIN($C$64,Inputs!C29)-Inputs!B29+1)</f>
         <v/>
       </c>
@@ -9309,7 +9736,7 @@
         <f>Inputs!B30&amp;" - "&amp;IF(Inputs!C30&gt;=100000,"above",Inputs!C30)</f>
         <v/>
       </c>
-      <c r="C69" s="24">
+      <c r="C69" s="25">
         <f>MAX(0,MIN($C$64,Inputs!C30)-Inputs!B30+1)</f>
         <v/>
       </c>
@@ -9331,7 +9758,7 @@
         <f>Inputs!B31&amp;" - "&amp;IF(Inputs!C31&gt;=100000,"above",Inputs!C31)</f>
         <v/>
       </c>
-      <c r="C70" s="24">
+      <c r="C70" s="25">
         <f>MAX(0,MIN($C$64,Inputs!C31)-Inputs!B31+1)</f>
         <v/>
       </c>
@@ -9350,7 +9777,7 @@
           <t>Monthly subscription, Year 1</t>
         </is>
       </c>
-      <c r="E71" s="33">
+      <c r="E71" s="24">
         <f>SUM(E67:E70)</f>
         <v/>
       </c>
@@ -9491,32 +9918,32 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="31" t="inlineStr">
+      <c r="A78" s="32" t="inlineStr">
         <is>
           <t>Total excl. VAT</t>
         </is>
       </c>
-      <c r="C78" s="33">
+      <c r="C78" s="24">
         <f>C76+C77</f>
         <v/>
       </c>
-      <c r="D78" s="33">
+      <c r="D78" s="24">
         <f>D76+D77</f>
         <v/>
       </c>
-      <c r="E78" s="33">
+      <c r="E78" s="24">
         <f>E76+E77</f>
         <v/>
       </c>
-      <c r="F78" s="33">
+      <c r="F78" s="24">
         <f>F76+F77</f>
         <v/>
       </c>
-      <c r="G78" s="33">
+      <c r="G78" s="24">
         <f>G76+G77</f>
         <v/>
       </c>
-      <c r="H78" s="33">
+      <c r="H78" s="24">
         <f>H76+H77</f>
         <v/>
       </c>
@@ -9621,7 +10048,7 @@
         <f>SUM('Perpetual Model'!$C$57:G57)</f>
         <v/>
       </c>
-      <c r="H82" s="31">
+      <c r="H82" s="32">
         <f>IF(MIN(C84:G84)=99,"Beyond Year 5","Break-even Year "&amp;MIN(C84:G84))</f>
         <v/>
       </c>
@@ -9659,23 +10086,23 @@
           <t>Helper</t>
         </is>
       </c>
-      <c r="C84" s="24">
+      <c r="C84" s="25">
         <f>IF(C83&gt;=C82,1,99)</f>
         <v/>
       </c>
-      <c r="D84" s="24">
+      <c r="D84" s="25">
         <f>IF(D83&gt;=D82,2,99)</f>
         <v/>
       </c>
-      <c r="E84" s="24">
+      <c r="E84" s="25">
         <f>IF(E83&gt;=E82,3,99)</f>
         <v/>
       </c>
-      <c r="F84" s="24">
+      <c r="F84" s="25">
         <f>IF(F83&gt;=F82,4,99)</f>
         <v/>
       </c>
-      <c r="G84" s="24">
+      <c r="G84" s="25">
         <f>IF(G83&gt;=G82,5,99)</f>
         <v/>
       </c>
@@ -9701,35 +10128,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="44" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Infrastructure (optional and separate)</t>
+          <t>Infrastructure (optional and separate): hosting per environment set</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Indicative monthly cost by provider and tier, with margin. Production plus one UAT environment. The customer may host BrokerVerse itself at no fee.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="45" customHeight="1">
+          <t>Price per month by provider, tier and environment, with margin. Standing environments run all the time; Pre-Prod is temporary and billed per month of use. The customer may host BrokerVerse itself at no fee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Provider</t>
@@ -9742,41 +10173,61 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Cloud cost per month (USD)</t>
+          <t>Environment set</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Cloud cost per month (PHP)</t>
+          <t>Dev per month (PHP)</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Margin (PHP)</t>
+          <t>SIT per month (PHP)</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Price per month (PHP)</t>
+          <t>UAT per month (PHP)</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Price per year, Year 1 (PHP)</t>
+          <t>Production per month (PHP)</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Price per month (USD)</t>
+          <t>Standing environments per month (PHP)</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>Pre-Prod per month of use (PHP)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Hosting Year 1 (PHP, incl. Pre-Prod at go-live)</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Hosting each later year (PHP, incl. Pre-Prod per major release)</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Standing per month (USD)</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="18" t="inlineStr">
         <is>
           <t>AWS</t>
@@ -9786,37 +10237,54 @@
         <f>Inputs!A28</f>
         <v/>
       </c>
-      <c r="C5" s="26">
-        <f>Inputs!B73*1</f>
-        <v/>
-      </c>
-      <c r="D5" s="20">
-        <f>C5*FX</f>
-        <v/>
-      </c>
-      <c r="E5" s="20">
-        <f>D5*Infra_Margin</f>
-        <v/>
-      </c>
-      <c r="F5" s="33">
-        <f>ROUND(D5+E5,-3)</f>
-        <v/>
-      </c>
-      <c r="G5" s="20">
-        <f>F5*12</f>
-        <v/>
-      </c>
-      <c r="H5" s="20">
-        <f>F5/FX</f>
-        <v/>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Dev, UAT, Production + Pre-Prod when used</t>
+        </is>
+      </c>
+      <c r="D5" s="27">
+        <f>ROUND(Inputs!B84*1*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="E5" s="27">
+        <f>ROUND(Inputs!C84*1*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="F5" s="27">
+        <f>ROUND(Inputs!D84*1*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="G5" s="27">
+        <f>ROUND(Inputs!E84*1*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="H5" s="24">
+        <f>SUM(D5:G5)</f>
+        <v/>
+      </c>
+      <c r="I5" s="24">
+        <f>ROUND(Inputs!G84*1*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="J5" s="20">
+        <f>H5*12+I5*PreProd_GoLive_Months</f>
+        <v/>
+      </c>
+      <c r="K5" s="20">
+        <f>H5*12+I5*PreProd_Rel_Months*Major_Rel_Year</f>
+        <v/>
+      </c>
+      <c r="L5" s="20">
+        <f>H5/FX</f>
+        <v/>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>Singapore region (ap-southeast-1); a Manila Local Zone exists for latency-sensitive parts (S22).</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>AWS</t>
@@ -9826,33 +10294,50 @@
         <f>Inputs!A29</f>
         <v/>
       </c>
-      <c r="C6" s="26">
-        <f>Inputs!C73*1</f>
-        <v/>
-      </c>
-      <c r="D6" s="20">
-        <f>C6*FX</f>
-        <v/>
-      </c>
-      <c r="E6" s="20">
-        <f>D6*Infra_Margin</f>
-        <v/>
-      </c>
-      <c r="F6" s="33">
-        <f>ROUND(D6+E6,-3)</f>
-        <v/>
-      </c>
-      <c r="G6" s="20">
-        <f>F6*12</f>
-        <v/>
-      </c>
-      <c r="H6" s="20">
-        <f>F6/FX</f>
-        <v/>
-      </c>
-      <c r="I6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Dev, UAT, Production + Pre-Prod when used</t>
+        </is>
+      </c>
+      <c r="D6" s="27">
+        <f>ROUND(Inputs!B85*1*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="E6" s="27">
+        <f>ROUND(Inputs!C85*1*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="F6" s="27">
+        <f>ROUND(Inputs!D85*1*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="G6" s="27">
+        <f>ROUND(Inputs!E85*1*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="H6" s="24">
+        <f>SUM(D6:G6)</f>
+        <v/>
+      </c>
+      <c r="I6" s="24">
+        <f>ROUND(Inputs!G85*1*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="J6" s="20">
+        <f>H6*12+I6*PreProd_GoLive_Months</f>
+        <v/>
+      </c>
+      <c r="K6" s="20">
+        <f>H6*12+I6*PreProd_Rel_Months*Major_Rel_Year</f>
+        <v/>
+      </c>
+      <c r="L6" s="20">
+        <f>H6/FX</f>
+        <v/>
+      </c>
+      <c r="M6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
           <t>AWS</t>
@@ -9862,33 +10347,50 @@
         <f>Inputs!A30</f>
         <v/>
       </c>
-      <c r="C7" s="26">
-        <f>Inputs!D73*1</f>
-        <v/>
-      </c>
-      <c r="D7" s="20">
-        <f>C7*FX</f>
-        <v/>
-      </c>
-      <c r="E7" s="20">
-        <f>D7*Infra_Margin</f>
-        <v/>
-      </c>
-      <c r="F7" s="33">
-        <f>ROUND(D7+E7,-3)</f>
-        <v/>
-      </c>
-      <c r="G7" s="20">
-        <f>F7*12</f>
-        <v/>
-      </c>
-      <c r="H7" s="20">
-        <f>F7/FX</f>
-        <v/>
-      </c>
-      <c r="I7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Dev, SIT, UAT, Production (HA) + Pre-Prod when used</t>
+        </is>
+      </c>
+      <c r="D7" s="27">
+        <f>ROUND(Inputs!B86*1*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="E7" s="27">
+        <f>ROUND(Inputs!C86*1*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="F7" s="27">
+        <f>ROUND(Inputs!D86*1*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="G7" s="27">
+        <f>ROUND(Inputs!E86*1*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="H7" s="24">
+        <f>SUM(D7:G7)</f>
+        <v/>
+      </c>
+      <c r="I7" s="24">
+        <f>ROUND(Inputs!G86*1*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="J7" s="20">
+        <f>H7*12+I7*PreProd_GoLive_Months</f>
+        <v/>
+      </c>
+      <c r="K7" s="20">
+        <f>H7*12+I7*PreProd_Rel_Months*Major_Rel_Year</f>
+        <v/>
+      </c>
+      <c r="L7" s="20">
+        <f>H7/FX</f>
+        <v/>
+      </c>
+      <c r="M7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>AWS</t>
@@ -9898,33 +10400,50 @@
         <f>Inputs!A31</f>
         <v/>
       </c>
-      <c r="C8" s="26">
-        <f>Inputs!E73*1</f>
-        <v/>
-      </c>
-      <c r="D8" s="20">
-        <f>C8*FX</f>
-        <v/>
-      </c>
-      <c r="E8" s="20">
-        <f>D8*Infra_Margin</f>
-        <v/>
-      </c>
-      <c r="F8" s="33">
-        <f>ROUND(D8+E8,-3)</f>
-        <v/>
-      </c>
-      <c r="G8" s="20">
-        <f>F8*12</f>
-        <v/>
-      </c>
-      <c r="H8" s="20">
-        <f>F8/FX</f>
-        <v/>
-      </c>
-      <c r="I8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Dev, SIT, UAT, Production (HA, DR copy) + Pre-Prod when used</t>
+        </is>
+      </c>
+      <c r="D8" s="27">
+        <f>ROUND(Inputs!B87*1*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="E8" s="27">
+        <f>ROUND(Inputs!C87*1*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="F8" s="27">
+        <f>ROUND(Inputs!D87*1*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="G8" s="27">
+        <f>ROUND(Inputs!E87*1*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="H8" s="24">
+        <f>SUM(D8:G8)</f>
+        <v/>
+      </c>
+      <c r="I8" s="24">
+        <f>ROUND(Inputs!G87*1*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="J8" s="20">
+        <f>H8*12+I8*PreProd_GoLive_Months</f>
+        <v/>
+      </c>
+      <c r="K8" s="20">
+        <f>H8*12+I8*PreProd_Rel_Months*Major_Rel_Year</f>
+        <v/>
+      </c>
+      <c r="L8" s="20">
+        <f>H8/FX</f>
+        <v/>
+      </c>
+      <c r="M8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="18" t="inlineStr">
         <is>
           <t>Azure</t>
@@ -9934,37 +10453,54 @@
         <f>Inputs!A28</f>
         <v/>
       </c>
-      <c r="C9" s="26">
-        <f>Inputs!B73*Azure_Factor</f>
-        <v/>
-      </c>
-      <c r="D9" s="20">
-        <f>C9*FX</f>
-        <v/>
-      </c>
-      <c r="E9" s="20">
-        <f>D9*Infra_Margin</f>
-        <v/>
-      </c>
-      <c r="F9" s="33">
-        <f>ROUND(D9+E9,-3)</f>
-        <v/>
-      </c>
-      <c r="G9" s="20">
-        <f>F9*12</f>
-        <v/>
-      </c>
-      <c r="H9" s="20">
-        <f>F9/FX</f>
-        <v/>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Dev, UAT, Production + Pre-Prod when used</t>
+        </is>
+      </c>
+      <c r="D9" s="27">
+        <f>ROUND(Inputs!B84*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="E9" s="27">
+        <f>ROUND(Inputs!C84*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="F9" s="27">
+        <f>ROUND(Inputs!D84*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="G9" s="27">
+        <f>ROUND(Inputs!E84*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="H9" s="24">
+        <f>SUM(D9:G9)</f>
+        <v/>
+      </c>
+      <c r="I9" s="24">
+        <f>ROUND(Inputs!G84*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="J9" s="20">
+        <f>H9*12+I9*PreProd_GoLive_Months</f>
+        <v/>
+      </c>
+      <c r="K9" s="20">
+        <f>H9*12+I9*PreProd_Rel_Months*Major_Rel_Year</f>
+        <v/>
+      </c>
+      <c r="L9" s="20">
+        <f>H9/FX</f>
+        <v/>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>Southeast Asia region (Singapore).</t>
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Azure</t>
@@ -9974,33 +10510,50 @@
         <f>Inputs!A29</f>
         <v/>
       </c>
-      <c r="C10" s="26">
-        <f>Inputs!C73*Azure_Factor</f>
-        <v/>
-      </c>
-      <c r="D10" s="20">
-        <f>C10*FX</f>
-        <v/>
-      </c>
-      <c r="E10" s="20">
-        <f>D10*Infra_Margin</f>
-        <v/>
-      </c>
-      <c r="F10" s="33">
-        <f>ROUND(D10+E10,-3)</f>
-        <v/>
-      </c>
-      <c r="G10" s="20">
-        <f>F10*12</f>
-        <v/>
-      </c>
-      <c r="H10" s="20">
-        <f>F10/FX</f>
-        <v/>
-      </c>
-      <c r="I10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Dev, UAT, Production + Pre-Prod when used</t>
+        </is>
+      </c>
+      <c r="D10" s="27">
+        <f>ROUND(Inputs!B85*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="E10" s="27">
+        <f>ROUND(Inputs!C85*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="F10" s="27">
+        <f>ROUND(Inputs!D85*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="G10" s="27">
+        <f>ROUND(Inputs!E85*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="H10" s="24">
+        <f>SUM(D10:G10)</f>
+        <v/>
+      </c>
+      <c r="I10" s="24">
+        <f>ROUND(Inputs!G85*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="J10" s="20">
+        <f>H10*12+I10*PreProd_GoLive_Months</f>
+        <v/>
+      </c>
+      <c r="K10" s="20">
+        <f>H10*12+I10*PreProd_Rel_Months*Major_Rel_Year</f>
+        <v/>
+      </c>
+      <c r="L10" s="20">
+        <f>H10/FX</f>
+        <v/>
+      </c>
+      <c r="M10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Azure</t>
@@ -10010,33 +10563,50 @@
         <f>Inputs!A30</f>
         <v/>
       </c>
-      <c r="C11" s="26">
-        <f>Inputs!D73*Azure_Factor</f>
-        <v/>
-      </c>
-      <c r="D11" s="20">
-        <f>C11*FX</f>
-        <v/>
-      </c>
-      <c r="E11" s="20">
-        <f>D11*Infra_Margin</f>
-        <v/>
-      </c>
-      <c r="F11" s="33">
-        <f>ROUND(D11+E11,-3)</f>
-        <v/>
-      </c>
-      <c r="G11" s="20">
-        <f>F11*12</f>
-        <v/>
-      </c>
-      <c r="H11" s="20">
-        <f>F11/FX</f>
-        <v/>
-      </c>
-      <c r="I11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Dev, SIT, UAT, Production (HA) + Pre-Prod when used</t>
+        </is>
+      </c>
+      <c r="D11" s="27">
+        <f>ROUND(Inputs!B86*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="E11" s="27">
+        <f>ROUND(Inputs!C86*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="F11" s="27">
+        <f>ROUND(Inputs!D86*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="G11" s="27">
+        <f>ROUND(Inputs!E86*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="H11" s="24">
+        <f>SUM(D11:G11)</f>
+        <v/>
+      </c>
+      <c r="I11" s="24">
+        <f>ROUND(Inputs!G86*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="J11" s="20">
+        <f>H11*12+I11*PreProd_GoLive_Months</f>
+        <v/>
+      </c>
+      <c r="K11" s="20">
+        <f>H11*12+I11*PreProd_Rel_Months*Major_Rel_Year</f>
+        <v/>
+      </c>
+      <c r="L11" s="20">
+        <f>H11/FX</f>
+        <v/>
+      </c>
+      <c r="M11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Azure</t>
@@ -10046,33 +10616,50 @@
         <f>Inputs!A31</f>
         <v/>
       </c>
-      <c r="C12" s="26">
-        <f>Inputs!E73*Azure_Factor</f>
-        <v/>
-      </c>
-      <c r="D12" s="20">
-        <f>C12*FX</f>
-        <v/>
-      </c>
-      <c r="E12" s="20">
-        <f>D12*Infra_Margin</f>
-        <v/>
-      </c>
-      <c r="F12" s="33">
-        <f>ROUND(D12+E12,-3)</f>
-        <v/>
-      </c>
-      <c r="G12" s="20">
-        <f>F12*12</f>
-        <v/>
-      </c>
-      <c r="H12" s="20">
-        <f>F12/FX</f>
-        <v/>
-      </c>
-      <c r="I12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Dev, SIT, UAT, Production (HA, DR copy) + Pre-Prod when used</t>
+        </is>
+      </c>
+      <c r="D12" s="27">
+        <f>ROUND(Inputs!B87*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="E12" s="27">
+        <f>ROUND(Inputs!C87*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="F12" s="27">
+        <f>ROUND(Inputs!D87*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="G12" s="27">
+        <f>ROUND(Inputs!E87*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="H12" s="24">
+        <f>SUM(D12:G12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="24">
+        <f>ROUND(Inputs!G87*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="J12" s="20">
+        <f>H12*12+I12*PreProd_GoLive_Months</f>
+        <v/>
+      </c>
+      <c r="K12" s="20">
+        <f>H12*12+I12*PreProd_Rel_Months*Major_Rel_Year</f>
+        <v/>
+      </c>
+      <c r="L12" s="20">
+        <f>H12/FX</f>
+        <v/>
+      </c>
+      <c r="M12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
         <is>
           <t>Local partner</t>
@@ -10082,37 +10669,54 @@
         <f>Inputs!A28</f>
         <v/>
       </c>
-      <c r="C13" s="26">
-        <f>Inputs!B73*Local_Factor</f>
-        <v/>
-      </c>
-      <c r="D13" s="20">
-        <f>C13*FX</f>
-        <v/>
-      </c>
-      <c r="E13" s="20">
-        <f>D13*Infra_Margin</f>
-        <v/>
-      </c>
-      <c r="F13" s="33">
-        <f>ROUND(D13+E13,-3)</f>
-        <v/>
-      </c>
-      <c r="G13" s="20">
-        <f>F13*12</f>
-        <v/>
-      </c>
-      <c r="H13" s="20">
-        <f>F13/FX</f>
-        <v/>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Dev, UAT, Production + Pre-Prod when used</t>
+        </is>
+      </c>
+      <c r="D13" s="27">
+        <f>ROUND(Inputs!B84*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="E13" s="27">
+        <f>ROUND(Inputs!C84*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="F13" s="27">
+        <f>ROUND(Inputs!D84*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="G13" s="27">
+        <f>ROUND(Inputs!E84*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="H13" s="24">
+        <f>SUM(D13:G13)</f>
+        <v/>
+      </c>
+      <c r="I13" s="24">
+        <f>ROUND(Inputs!G84*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="J13" s="20">
+        <f>H13*12+I13*PreProd_GoLive_Months</f>
+        <v/>
+      </c>
+      <c r="K13" s="20">
+        <f>H13*12+I13*PreProd_Rel_Months*Major_Rel_Year</f>
+        <v/>
+      </c>
+      <c r="L13" s="20">
+        <f>H13/FX</f>
+        <v/>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>Philippine data centre or partner cloud; data stays in the Philippines.</t>
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Local partner</t>
@@ -10122,33 +10726,50 @@
         <f>Inputs!A29</f>
         <v/>
       </c>
-      <c r="C14" s="26">
-        <f>Inputs!C73*Local_Factor</f>
-        <v/>
-      </c>
-      <c r="D14" s="20">
-        <f>C14*FX</f>
-        <v/>
-      </c>
-      <c r="E14" s="20">
-        <f>D14*Infra_Margin</f>
-        <v/>
-      </c>
-      <c r="F14" s="33">
-        <f>ROUND(D14+E14,-3)</f>
-        <v/>
-      </c>
-      <c r="G14" s="20">
-        <f>F14*12</f>
-        <v/>
-      </c>
-      <c r="H14" s="20">
-        <f>F14/FX</f>
-        <v/>
-      </c>
-      <c r="I14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Dev, UAT, Production + Pre-Prod when used</t>
+        </is>
+      </c>
+      <c r="D14" s="27">
+        <f>ROUND(Inputs!B85*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="E14" s="27">
+        <f>ROUND(Inputs!C85*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="F14" s="27">
+        <f>ROUND(Inputs!D85*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="G14" s="27">
+        <f>ROUND(Inputs!E85*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="H14" s="24">
+        <f>SUM(D14:G14)</f>
+        <v/>
+      </c>
+      <c r="I14" s="24">
+        <f>ROUND(Inputs!G85*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="J14" s="20">
+        <f>H14*12+I14*PreProd_GoLive_Months</f>
+        <v/>
+      </c>
+      <c r="K14" s="20">
+        <f>H14*12+I14*PreProd_Rel_Months*Major_Rel_Year</f>
+        <v/>
+      </c>
+      <c r="L14" s="20">
+        <f>H14/FX</f>
+        <v/>
+      </c>
+      <c r="M14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Local partner</t>
@@ -10158,33 +10779,50 @@
         <f>Inputs!A30</f>
         <v/>
       </c>
-      <c r="C15" s="26">
-        <f>Inputs!D73*Local_Factor</f>
-        <v/>
-      </c>
-      <c r="D15" s="20">
-        <f>C15*FX</f>
-        <v/>
-      </c>
-      <c r="E15" s="20">
-        <f>D15*Infra_Margin</f>
-        <v/>
-      </c>
-      <c r="F15" s="33">
-        <f>ROUND(D15+E15,-3)</f>
-        <v/>
-      </c>
-      <c r="G15" s="20">
-        <f>F15*12</f>
-        <v/>
-      </c>
-      <c r="H15" s="20">
-        <f>F15/FX</f>
-        <v/>
-      </c>
-      <c r="I15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16">
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Dev, SIT, UAT, Production (HA) + Pre-Prod when used</t>
+        </is>
+      </c>
+      <c r="D15" s="27">
+        <f>ROUND(Inputs!B86*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="E15" s="27">
+        <f>ROUND(Inputs!C86*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="F15" s="27">
+        <f>ROUND(Inputs!D86*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="G15" s="27">
+        <f>ROUND(Inputs!E86*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="H15" s="24">
+        <f>SUM(D15:G15)</f>
+        <v/>
+      </c>
+      <c r="I15" s="24">
+        <f>ROUND(Inputs!G86*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="J15" s="20">
+        <f>H15*12+I15*PreProd_GoLive_Months</f>
+        <v/>
+      </c>
+      <c r="K15" s="20">
+        <f>H15*12+I15*PreProd_Rel_Months*Major_Rel_Year</f>
+        <v/>
+      </c>
+      <c r="L15" s="20">
+        <f>H15/FX</f>
+        <v/>
+      </c>
+      <c r="M15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Local partner</t>
@@ -10194,33 +10832,50 @@
         <f>Inputs!A31</f>
         <v/>
       </c>
-      <c r="C16" s="26">
-        <f>Inputs!E73*Local_Factor</f>
-        <v/>
-      </c>
-      <c r="D16" s="20">
-        <f>C16*FX</f>
-        <v/>
-      </c>
-      <c r="E16" s="20">
-        <f>D16*Infra_Margin</f>
-        <v/>
-      </c>
-      <c r="F16" s="33">
-        <f>ROUND(D16+E16,-3)</f>
-        <v/>
-      </c>
-      <c r="G16" s="20">
-        <f>F16*12</f>
-        <v/>
-      </c>
-      <c r="H16" s="20">
-        <f>F16/FX</f>
-        <v/>
-      </c>
-      <c r="I16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Dev, SIT, UAT, Production (HA, DR copy) + Pre-Prod when used</t>
+        </is>
+      </c>
+      <c r="D16" s="27">
+        <f>ROUND(Inputs!B87*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="E16" s="27">
+        <f>ROUND(Inputs!C87*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="F16" s="27">
+        <f>ROUND(Inputs!D87*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="G16" s="27">
+        <f>ROUND(Inputs!E87*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="H16" s="24">
+        <f>SUM(D16:G16)</f>
+        <v/>
+      </c>
+      <c r="I16" s="24">
+        <f>ROUND(Inputs!G87*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <v/>
+      </c>
+      <c r="J16" s="20">
+        <f>H16*12+I16*PreProd_GoLive_Months</f>
+        <v/>
+      </c>
+      <c r="K16" s="20">
+        <f>H16*12+I16*PreProd_Rel_Months*Major_Rel_Year</f>
+        <v/>
+      </c>
+      <c r="L16" s="20">
+        <f>H16/FX</f>
+        <v/>
+      </c>
+      <c r="M16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Customer</t>
@@ -10230,8 +10885,10 @@
         <f>Inputs!A28</f>
         <v/>
       </c>
-      <c r="C17" s="20" t="n">
-        <v>0</v>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Dev, UAT, Production + Pre-Prod when used</t>
+        </is>
       </c>
       <c r="D17" s="20" t="n">
         <v>0</v>
@@ -10248,13 +10905,25 @@
       <c r="H17" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>Broker hosts itself (cloud account or own data centre). Deployment guide supplied; set-up support at day rates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
+      <c r="I17" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>Broker hosts itself (cloud account or own data centre) with the same environment set. Deployment guide supplied; set-up support at day rates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Customer</t>
@@ -10264,8 +10933,10 @@
         <f>Inputs!A29</f>
         <v/>
       </c>
-      <c r="C18" s="20" t="n">
-        <v>0</v>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Dev, UAT, Production + Pre-Prod when used</t>
+        </is>
       </c>
       <c r="D18" s="20" t="n">
         <v>0</v>
@@ -10282,9 +10953,21 @@
       <c r="H18" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19">
+      <c r="I18" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Customer</t>
@@ -10294,8 +10977,10 @@
         <f>Inputs!A30</f>
         <v/>
       </c>
-      <c r="C19" s="20" t="n">
-        <v>0</v>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Dev, SIT, UAT, Production (HA) + Pre-Prod when used</t>
+        </is>
       </c>
       <c r="D19" s="20" t="n">
         <v>0</v>
@@ -10312,9 +10997,21 @@
       <c r="H19" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20">
+      <c r="I19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
           <t>Customer</t>
@@ -10324,8 +11021,10 @@
         <f>Inputs!A31</f>
         <v/>
       </c>
-      <c r="C20" s="20" t="n">
-        <v>0</v>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Dev, SIT, UAT, Production (HA, DR copy) + Pre-Prod when used</t>
+        </is>
       </c>
       <c r="D20" s="20" t="n">
         <v>0</v>
@@ -10342,12 +11041,24 @@
       <c r="H20" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="5" t="inlineStr"/>
+      <c r="I20" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>What the infrastructure price covers</t>
+          <t>Environment model and what the price covers</t>
         </is>
       </c>
       <c r="B22" s="7" t="n"/>
@@ -10358,49 +11069,69 @@
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="7" t="n"/>
       <c r="I22" s="7" t="n"/>
+      <c r="J22" s="7" t="n"/>
+      <c r="K22" s="7" t="n"/>
+      <c r="L22" s="7" t="n"/>
+      <c r="M22" s="7" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="25" t="inlineStr">
-        <is>
-          <t>Covers: cloud resources for production and one UAT environment, daily backups, monitoring and alarms, operating system and database patching, TLS certificates.</t>
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>Environment model: Small and Medium brokers have Dev, UAT and Production. Integration and system testing are done in Dev and the release is promoted to UAT for testing, then to Production. Large and Enterprise brokers have Dev, SIT, UAT and Production, with SIT and UAT separate and Production highly available.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>Pre-Prod is temporary for every size: created from a production backup (masked when used by people without production access) for the go-live rehearsal and for each major release, then removed. It is billed per month of use at the Pre-Prod rate: by default 2 months around go-live and 1 month per major release (Inputs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>Covers: cloud resources of each environment, daily backups, monitoring and alarms, operating system and database patching, TLS certificates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t>Reference sizing: the BrokerVerse capacity document sizes 200 named users (80 concurrent) at 2 API containers of 1 vCPU, 2 GB and Amazon RDS for PostgreSQL 16 db.m7g.large Multi-AZ, 100 GB gp3 storage.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
-        <is>
-          <t>Excludes: e-mail sending service charges above normal volumes, SMS, payment gateway fees, domain names, extra environments (see Optional Services) and disaster-recovery copies for tiers other than Enterprise.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="25" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>Excludes: e-mail sending service charges above normal volumes, SMS, payment gateway fees, domain names, extra environments such as a training environment (see Optional Services) and disaster-recovery copies for tiers other than Enterprise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>All cloud figures are estimates from public on-demand list prices, rounded up. Confirm with the provider pricing calculator and a partner quotation before a binding offer. Reserved instances or savings plans can lower cost 20% to 40% for a 1 to 3 year commitment.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="25" t="inlineStr">
-        <is>
-          <t>Billing: monthly in advance in PHP. The margin line covers FX movement between USD cloud billing and PHP invoicing, and the operations effort.</t>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>Billing: monthly in advance in PHP from the handover of each environment; Pre-Prod monthly for each month or part month of use. Hosting fees do not increase yearly; provider price changes are passed through at cost (Hosting Agreement). The margin covers FX movement between USD cloud billing and PHP invoicing, and the operations effort.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="A24:I24"/>
+  <mergeCells count="7">
+    <mergeCell ref="A23:M23"/>
+    <mergeCell ref="A27:M27"/>
+    <mergeCell ref="A26:M26"/>
+    <mergeCell ref="A29:M29"/>
+    <mergeCell ref="A25:M25"/>
+    <mergeCell ref="A24:M24"/>
+    <mergeCell ref="A28:M28"/>
   </mergeCells>
   <printOptions gridLines="0"/>
   <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10565,12 +11296,12 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Blended rate</t>
         </is>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="24">
         <f>Blended</f>
         <v/>
       </c>
@@ -10598,35 +11329,35 @@
       <c r="H11" s="7" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>1. The broker raises the CR with the business need and examples. iorta TechNXT replies with an impact note within 5 business days (Small) or 10 (Medium, Large).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>2. Developer man-days are estimated from the screens, APIs, reports, database changes and jobs affected.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>3. Business analysis = development x BA %; testing = development x QA %; project management = (BA + development + testing) x PM %; contingency on the total. Days are rounded up to the half day.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="26" t="inlineStr">
         <is>
           <t>4. Cost = days by role x role day rate. The band decides the approval route and the payment terms: Small, billed on delivery; Medium, 50% on approval and 50% on UAT sign-off; Large, 30% / 50% / 20% like a project.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>5. CRs change the OOTB version for that customer only. The changed code is covered by AMC or subscription support only when merged into the product line; otherwise support of the change is billed at day rates.</t>
         </is>
@@ -11122,19 +11853,19 @@
           <t>CR price excl. VAT (PHP)</t>
         </is>
       </c>
-      <c r="B39" s="33">
+      <c r="B39" s="24">
         <f>SUM(B34:B38)</f>
         <v/>
       </c>
-      <c r="C39" s="33">
+      <c r="C39" s="24">
         <f>SUM(C34:C38)</f>
         <v/>
       </c>
-      <c r="D39" s="33">
+      <c r="D39" s="24">
         <f>SUM(D34:D38)</f>
         <v/>
       </c>
-      <c r="E39" s="33">
+      <c r="E39" s="24">
         <f>SUM(E34:E38)</f>
         <v/>
       </c>
@@ -11211,7 +11942,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Priced on request in addition to either model. PHP, exclusive of VAT. Recurring items escalate 5% a year.</t>
+          <t>Priced on request in addition to either model. PHP, exclusive of VAT. 24x7 support escalates 5% a year; hosted environments do not.</t>
         </is>
       </c>
     </row>
@@ -11266,7 +11997,7 @@
         <f>C5/FX</f>
         <v/>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <f>Env_Setup_Days</f>
         <v/>
       </c>
@@ -11288,17 +12019,17 @@
         </is>
       </c>
       <c r="C6" s="34">
-        <f>ROUND(Env_Monthly_USD*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(NP_Small_USD*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="D6" s="20">
         <f>C6/FX</f>
         <v/>
       </c>
-      <c r="E6" s="24" t="inlineStr"/>
+      <c r="E6" s="25" t="inlineStr"/>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Cloud cost plus infrastructure margin. Customer-hosted: set-up fee only.</t>
+          <t>Small non-production size (as Dev) on AWS, cloud cost plus infrastructure margin; no yearly increase. Customer-hosted: set-up fee only.</t>
         </is>
       </c>
     </row>
@@ -11321,7 +12052,7 @@
         <f>C7/FX</f>
         <v/>
       </c>
-      <c r="E7" s="24" t="inlineStr"/>
+      <c r="E7" s="25" t="inlineStr"/>
       <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Up to 15 participants per session; customer provides the room and PCs.</t>
@@ -11347,13 +12078,13 @@
         <f>C8/FX</f>
         <v/>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <f>Mig_Days_Source</f>
         <v/>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Standard: data loaded by the broker with the BrokerVerse upload templates (docs/templates), with guidance. This item covers extraction and transformation from a legacy system.</t>
+          <t>Standard: data loaded by the broker with the BrokerVerse upload templates (docs/package/05_Delivery/Upload_Templates), with guidance. This item covers extraction and transformation from a legacy system.</t>
         </is>
       </c>
     </row>
@@ -11376,7 +12107,7 @@
         <f>C9/FX</f>
         <v/>
       </c>
-      <c r="E9" s="24" t="inlineStr"/>
+      <c r="E9" s="25" t="inlineStr"/>
       <c r="F9" s="5" t="inlineStr">
         <is>
           <t>For volume or data-quality work beyond the estimate.</t>
@@ -11402,7 +12133,7 @@
         <f>C10/FX</f>
         <v/>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="25">
         <f>Int_Std_Days</f>
         <v/>
       </c>
@@ -11431,7 +12162,7 @@
         <f>C11/FX</f>
         <v/>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="25">
         <f>Int_Cx_Days</f>
         <v/>
       </c>
@@ -11460,7 +12191,7 @@
         <f>C12/FX</f>
         <v/>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="25">
         <f>Days_per_LOB</f>
         <v/>
       </c>
@@ -11489,7 +12220,7 @@
         <f>C13/FX</f>
         <v/>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="25">
         <f>Report_Days</f>
         <v/>
       </c>
@@ -11518,7 +12249,7 @@
         <f>C14/FX</f>
         <v/>
       </c>
-      <c r="E14" s="24" t="inlineStr"/>
+      <c r="E14" s="25" t="inlineStr"/>
       <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Outside Metro Manila: travel, lodging and meals at cost.</t>
@@ -11622,30 +12353,30 @@
       <c r="F20" s="7" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t>Configuration of the company, branches, users and roles, insurers, commission rates, chart of accounts, banks and the included lines of business.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="25" t="inlineStr">
-        <is>
-          <t>Data load using the standard upload templates (about 40 templates in docs/templates), with the broker supplying clean data.</t>
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>Data load using the standard upload templates (about 50 templates in docs/package/05_Delivery/Upload_Templates), with the broker supplying clean data.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t>Training days included for the tier (train-the-trainer), UAT support, go-live support and 4 weeks of hypercare.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
-        <is>
-          <t>One production and one UAT environment when iorta TechNXT hosts; deployment guidance when the broker hosts.</t>
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>Set-up of the environment set of the tier (Dev, UAT and Production; SIT as well for Large and Enterprise) and of Pre-Prod for the go-live rehearsal; hosting is billed separately. Deployment guidance when the broker hosts.</t>
         </is>
       </c>
     </row>
@@ -11705,7 +12436,7 @@
     </row>
     <row r="4">
       <c r="A4" s="6">
-        <f>"Example 1: "&amp;Inputs!$B$79&amp;", "&amp;Inputs!$B$80&amp;" users, "&amp;Inputs!$B$81&amp;" lines of business, tier "&amp;INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))&amp;", hosting: "&amp;Inputs!$B$82</f>
+        <f>"Example 1: "&amp;Inputs!$B$93&amp;", "&amp;Inputs!$B$94&amp;" users, "&amp;Inputs!$B$95&amp;" lines of business, tier "&amp;INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))&amp;", hosting: "&amp;Inputs!$B$96</f>
         <v/>
       </c>
       <c r="B4" s="7" t="n"/>
@@ -11772,7 +12503,7 @@
         </is>
       </c>
       <c r="B7" s="20">
-        <f>ROUND((INDEX(Inputs!$G$28:$G$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))+MAX(0,Inputs!$B$81-INDEX(Inputs!$H$28:$H$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1)))*Days_per_LOB)*Blended/Round_To,0)*Round_To</f>
+        <f>ROUND((INDEX(Inputs!$G$28:$G$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))+MAX(0,Inputs!$B$95-INDEX(Inputs!$H$28:$H$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1)))*Days_per_LOB)*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="C7" s="20" t="n">
@@ -11803,7 +12534,7 @@
         </is>
       </c>
       <c r="B8" s="20">
-        <f>MAX(0,MIN(Inputs!$B$80,Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$D$28+MAX(0,MIN(Inputs!$B$80,Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$D$29+MAX(0,MIN(Inputs!$B$80,Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$D$30+MAX(0,MIN(Inputs!$B$80,Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$D$31</f>
+        <f>MAX(0,MIN(Inputs!$B$94,Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$D$28+MAX(0,MIN(Inputs!$B$94,Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$D$29+MAX(0,MIN(Inputs!$B$94,Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$D$30+MAX(0,MIN(Inputs!$B$94,Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$D$31</f>
         <v/>
       </c>
       <c r="C8" s="20" t="n">
@@ -11937,27 +12668,27 @@
     </row>
     <row r="13">
       <c r="A13" s="10">
-        <f>"Subscription ("&amp;MAX(Inputs!$B$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1)))&amp;" billable users)"</f>
+        <f>"Subscription ("&amp;MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1)))&amp;" billable users)"</f>
         <v/>
       </c>
       <c r="B13" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$B$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(1-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(1-1)</f>
         <v/>
       </c>
       <c r="C13" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$B$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(2-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(2-1)</f>
         <v/>
       </c>
       <c r="D13" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$B$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(3-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(3-1)</f>
         <v/>
       </c>
       <c r="E13" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$B$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(4-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(4-1)</f>
         <v/>
       </c>
       <c r="F13" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$B$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(5-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(5-1)</f>
         <v/>
       </c>
       <c r="G13" s="34">
@@ -12013,27 +12744,27 @@
     </row>
     <row r="16">
       <c r="A16" s="10">
-        <f>"Infrastructure: "&amp;Inputs!$B$82</f>
+        <f>"Hosting, environment set and Pre-Prod: "&amp;Inputs!$B$96</f>
         <v/>
       </c>
       <c r="B16" s="20">
-        <f>SUMIFS(Infrastructure!$F$5:$F$20,Infrastructure!$A$5:$A$20,Inputs!$B$82,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1)))*12*(1+Infra_Esc)^(1-1)</f>
+        <f>(SUMIFS(Infrastructure!$J$5:$J$20,Infrastructure!$A$5:$A$20,Inputs!$B$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(1-1)</f>
         <v/>
       </c>
       <c r="C16" s="20">
-        <f>SUMIFS(Infrastructure!$F$5:$F$20,Infrastructure!$A$5:$A$20,Inputs!$B$82,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1)))*12*(1+Infra_Esc)^(2-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$B$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(2-1)</f>
         <v/>
       </c>
       <c r="D16" s="20">
-        <f>SUMIFS(Infrastructure!$F$5:$F$20,Infrastructure!$A$5:$A$20,Inputs!$B$82,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1)))*12*(1+Infra_Esc)^(3-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$B$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(3-1)</f>
         <v/>
       </c>
       <c r="E16" s="20">
-        <f>SUMIFS(Infrastructure!$F$5:$F$20,Infrastructure!$A$5:$A$20,Inputs!$B$82,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1)))*12*(1+Infra_Esc)^(4-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$B$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(4-1)</f>
         <v/>
       </c>
       <c r="F16" s="20">
-        <f>SUMIFS(Infrastructure!$F$5:$F$20,Infrastructure!$A$5:$A$20,Inputs!$B$82,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1)))*12*(1+Infra_Esc)^(5-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$B$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(5-1)</f>
         <v/>
       </c>
       <c r="G16" s="34">
@@ -12052,23 +12783,23 @@
         </is>
       </c>
       <c r="B17" s="20">
-        <f>IF(Inputs!$B$83="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))*(1+Esc)^(1-1),0)</f>
+        <f>IF(Inputs!$B$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(1-1),0)</f>
         <v/>
       </c>
       <c r="C17" s="20">
-        <f>IF(Inputs!$B$83="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))*(1+Esc)^(2-1),0)</f>
+        <f>IF(Inputs!$B$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(2-1),0)</f>
         <v/>
       </c>
       <c r="D17" s="20">
-        <f>IF(Inputs!$B$83="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))*(1+Esc)^(3-1),0)</f>
+        <f>IF(Inputs!$B$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(3-1),0)</f>
         <v/>
       </c>
       <c r="E17" s="20">
-        <f>IF(Inputs!$B$83="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))*(1+Esc)^(4-1),0)</f>
+        <f>IF(Inputs!$B$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(4-1),0)</f>
         <v/>
       </c>
       <c r="F17" s="20">
-        <f>IF(Inputs!$B$83="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$80,Inputs!$B$28:$B$31,1))*(1+Esc)^(5-1),0)</f>
+        <f>IF(Inputs!$B$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(5-1),0)</f>
         <v/>
       </c>
       <c r="G17" s="34">
@@ -12087,7 +12818,7 @@
         </is>
       </c>
       <c r="B18" s="20">
-        <f>Inputs!$B$84*Rate_Trainer+ROUND(Mig_Days_Source*Blended/Round_To,0)*Round_To*Inputs!$B$85+ROUND(Int_Std_Days*Blended/Round_To,0)*Round_To*Inputs!$B$86</f>
+        <f>Inputs!$B$98*Rate_Trainer+ROUND(Mig_Days_Source*Blended/Round_To,0)*Round_To*Inputs!$B$99+ROUND(Int_Std_Days*Blended/Round_To,0)*Round_To*Inputs!$B$100</f>
         <v/>
       </c>
       <c r="C18" s="20" t="n">
@@ -12154,28 +12885,28 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="31" t="inlineStr">
+      <c r="A21" s="32" t="inlineStr">
         <is>
           <t>Perpetual with options, excl. VAT</t>
         </is>
       </c>
-      <c r="B21" s="33">
+      <c r="B21" s="24">
         <f>B10+B19</f>
         <v/>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="24">
         <f>C10+C19</f>
         <v/>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="24">
         <f>D10+D19</f>
         <v/>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="24">
         <f>E10+E19</f>
         <v/>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="24">
         <f>F10+F19</f>
         <v/>
       </c>
@@ -12189,28 +12920,28 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="31" t="inlineStr">
+      <c r="A22" s="32" t="inlineStr">
         <is>
           <t>Subscription with options, excl. VAT</t>
         </is>
       </c>
-      <c r="B22" s="33">
+      <c r="B22" s="24">
         <f>B14+B19</f>
         <v/>
       </c>
-      <c r="C22" s="33">
+      <c r="C22" s="24">
         <f>C14+C19</f>
         <v/>
       </c>
-      <c r="D22" s="33">
+      <c r="D22" s="24">
         <f>D14+D19</f>
         <v/>
       </c>
-      <c r="E22" s="33">
+      <c r="E22" s="24">
         <f>E14+E19</f>
         <v/>
       </c>
-      <c r="F22" s="33">
+      <c r="F22" s="24">
         <f>F14+F19</f>
         <v/>
       </c>
@@ -12329,7 +13060,7 @@
     </row>
     <row r="27">
       <c r="A27" s="6">
-        <f>"Example 2: "&amp;Inputs!$C$79&amp;", "&amp;Inputs!$C$80&amp;" users, "&amp;Inputs!$C$81&amp;" lines of business, tier "&amp;INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))&amp;", hosting: "&amp;Inputs!$C$82</f>
+        <f>"Example 2: "&amp;Inputs!$C$93&amp;", "&amp;Inputs!$C$94&amp;" users, "&amp;Inputs!$C$95&amp;" lines of business, tier "&amp;INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))&amp;", hosting: "&amp;Inputs!$C$96</f>
         <v/>
       </c>
       <c r="B27" s="7" t="n"/>
@@ -12396,7 +13127,7 @@
         </is>
       </c>
       <c r="B30" s="20">
-        <f>ROUND((INDEX(Inputs!$G$28:$G$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))+MAX(0,Inputs!$C$81-INDEX(Inputs!$H$28:$H$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1)))*Days_per_LOB)*Blended/Round_To,0)*Round_To</f>
+        <f>ROUND((INDEX(Inputs!$G$28:$G$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))+MAX(0,Inputs!$C$95-INDEX(Inputs!$H$28:$H$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1)))*Days_per_LOB)*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="C30" s="20" t="n">
@@ -12427,7 +13158,7 @@
         </is>
       </c>
       <c r="B31" s="20">
-        <f>MAX(0,MIN(Inputs!$C$80,Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$D$28+MAX(0,MIN(Inputs!$C$80,Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$D$29+MAX(0,MIN(Inputs!$C$80,Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$D$30+MAX(0,MIN(Inputs!$C$80,Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$D$31</f>
+        <f>MAX(0,MIN(Inputs!$C$94,Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$D$28+MAX(0,MIN(Inputs!$C$94,Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$D$29+MAX(0,MIN(Inputs!$C$94,Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$D$30+MAX(0,MIN(Inputs!$C$94,Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$D$31</f>
         <v/>
       </c>
       <c r="C31" s="20" t="n">
@@ -12561,27 +13292,27 @@
     </row>
     <row r="36">
       <c r="A36" s="10">
-        <f>"Subscription ("&amp;MAX(Inputs!$C$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1)))&amp;" billable users)"</f>
+        <f>"Subscription ("&amp;MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1)))&amp;" billable users)"</f>
         <v/>
       </c>
       <c r="B36" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$C$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(1-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(1-1)</f>
         <v/>
       </c>
       <c r="C36" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$C$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(2-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(2-1)</f>
         <v/>
       </c>
       <c r="D36" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$C$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(3-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(3-1)</f>
         <v/>
       </c>
       <c r="E36" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$C$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(4-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(4-1)</f>
         <v/>
       </c>
       <c r="F36" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$C$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(5-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(5-1)</f>
         <v/>
       </c>
       <c r="G36" s="34">
@@ -12637,27 +13368,27 @@
     </row>
     <row r="39">
       <c r="A39" s="10">
-        <f>"Infrastructure: "&amp;Inputs!$C$82</f>
+        <f>"Hosting, environment set and Pre-Prod: "&amp;Inputs!$C$96</f>
         <v/>
       </c>
       <c r="B39" s="20">
-        <f>SUMIFS(Infrastructure!$F$5:$F$20,Infrastructure!$A$5:$A$20,Inputs!$C$82,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1)))*12*(1+Infra_Esc)^(1-1)</f>
+        <f>(SUMIFS(Infrastructure!$J$5:$J$20,Infrastructure!$A$5:$A$20,Inputs!$C$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(1-1)</f>
         <v/>
       </c>
       <c r="C39" s="20">
-        <f>SUMIFS(Infrastructure!$F$5:$F$20,Infrastructure!$A$5:$A$20,Inputs!$C$82,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1)))*12*(1+Infra_Esc)^(2-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$C$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(2-1)</f>
         <v/>
       </c>
       <c r="D39" s="20">
-        <f>SUMIFS(Infrastructure!$F$5:$F$20,Infrastructure!$A$5:$A$20,Inputs!$C$82,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1)))*12*(1+Infra_Esc)^(3-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$C$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(3-1)</f>
         <v/>
       </c>
       <c r="E39" s="20">
-        <f>SUMIFS(Infrastructure!$F$5:$F$20,Infrastructure!$A$5:$A$20,Inputs!$C$82,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1)))*12*(1+Infra_Esc)^(4-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$C$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(4-1)</f>
         <v/>
       </c>
       <c r="F39" s="20">
-        <f>SUMIFS(Infrastructure!$F$5:$F$20,Infrastructure!$A$5:$A$20,Inputs!$C$82,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1)))*12*(1+Infra_Esc)^(5-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$C$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(5-1)</f>
         <v/>
       </c>
       <c r="G39" s="34">
@@ -12676,23 +13407,23 @@
         </is>
       </c>
       <c r="B40" s="20">
-        <f>IF(Inputs!$C$83="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))*(1+Esc)^(1-1),0)</f>
+        <f>IF(Inputs!$C$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(1-1),0)</f>
         <v/>
       </c>
       <c r="C40" s="20">
-        <f>IF(Inputs!$C$83="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))*(1+Esc)^(2-1),0)</f>
+        <f>IF(Inputs!$C$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(2-1),0)</f>
         <v/>
       </c>
       <c r="D40" s="20">
-        <f>IF(Inputs!$C$83="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))*(1+Esc)^(3-1),0)</f>
+        <f>IF(Inputs!$C$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(3-1),0)</f>
         <v/>
       </c>
       <c r="E40" s="20">
-        <f>IF(Inputs!$C$83="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))*(1+Esc)^(4-1),0)</f>
+        <f>IF(Inputs!$C$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(4-1),0)</f>
         <v/>
       </c>
       <c r="F40" s="20">
-        <f>IF(Inputs!$C$83="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$80,Inputs!$B$28:$B$31,1))*(1+Esc)^(5-1),0)</f>
+        <f>IF(Inputs!$C$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(5-1),0)</f>
         <v/>
       </c>
       <c r="G40" s="34">
@@ -12711,7 +13442,7 @@
         </is>
       </c>
       <c r="B41" s="20">
-        <f>Inputs!$C$84*Rate_Trainer+ROUND(Mig_Days_Source*Blended/Round_To,0)*Round_To*Inputs!$C$85+ROUND(Int_Std_Days*Blended/Round_To,0)*Round_To*Inputs!$C$86</f>
+        <f>Inputs!$C$98*Rate_Trainer+ROUND(Mig_Days_Source*Blended/Round_To,0)*Round_To*Inputs!$C$99+ROUND(Int_Std_Days*Blended/Round_To,0)*Round_To*Inputs!$C$100</f>
         <v/>
       </c>
       <c r="C41" s="20" t="n">
@@ -12778,28 +13509,28 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="31" t="inlineStr">
+      <c r="A44" s="32" t="inlineStr">
         <is>
           <t>Perpetual with options, excl. VAT</t>
         </is>
       </c>
-      <c r="B44" s="33">
+      <c r="B44" s="24">
         <f>B33+B42</f>
         <v/>
       </c>
-      <c r="C44" s="33">
+      <c r="C44" s="24">
         <f>C33+C42</f>
         <v/>
       </c>
-      <c r="D44" s="33">
+      <c r="D44" s="24">
         <f>D33+D42</f>
         <v/>
       </c>
-      <c r="E44" s="33">
+      <c r="E44" s="24">
         <f>E33+E42</f>
         <v/>
       </c>
-      <c r="F44" s="33">
+      <c r="F44" s="24">
         <f>F33+F42</f>
         <v/>
       </c>
@@ -12813,28 +13544,28 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="31" t="inlineStr">
+      <c r="A45" s="32" t="inlineStr">
         <is>
           <t>Subscription with options, excl. VAT</t>
         </is>
       </c>
-      <c r="B45" s="33">
+      <c r="B45" s="24">
         <f>B37+B42</f>
         <v/>
       </c>
-      <c r="C45" s="33">
+      <c r="C45" s="24">
         <f>C37+C42</f>
         <v/>
       </c>
-      <c r="D45" s="33">
+      <c r="D45" s="24">
         <f>D37+D42</f>
         <v/>
       </c>
-      <c r="E45" s="33">
+      <c r="E45" s="24">
         <f>E37+E42</f>
         <v/>
       </c>
-      <c r="F45" s="33">
+      <c r="F45" s="24">
         <f>F37+F42</f>
         <v/>
       </c>
@@ -12953,7 +13684,7 @@
     </row>
     <row r="50">
       <c r="A50" s="6">
-        <f>"Example 3: "&amp;Inputs!$D$79&amp;", "&amp;Inputs!$D$80&amp;" users, "&amp;Inputs!$D$81&amp;" lines of business, tier "&amp;INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))&amp;", hosting: "&amp;Inputs!$D$82</f>
+        <f>"Example 3: "&amp;Inputs!$D$93&amp;", "&amp;Inputs!$D$94&amp;" users, "&amp;Inputs!$D$95&amp;" lines of business, tier "&amp;INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))&amp;", hosting: "&amp;Inputs!$D$96</f>
         <v/>
       </c>
       <c r="B50" s="7" t="n"/>
@@ -13020,7 +13751,7 @@
         </is>
       </c>
       <c r="B53" s="20">
-        <f>ROUND((INDEX(Inputs!$G$28:$G$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))+MAX(0,Inputs!$D$81-INDEX(Inputs!$H$28:$H$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1)))*Days_per_LOB)*Blended/Round_To,0)*Round_To</f>
+        <f>ROUND((INDEX(Inputs!$G$28:$G$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))+MAX(0,Inputs!$D$95-INDEX(Inputs!$H$28:$H$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1)))*Days_per_LOB)*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="C53" s="20" t="n">
@@ -13051,7 +13782,7 @@
         </is>
       </c>
       <c r="B54" s="20">
-        <f>MAX(0,MIN(Inputs!$D$80,Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$D$28+MAX(0,MIN(Inputs!$D$80,Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$D$29+MAX(0,MIN(Inputs!$D$80,Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$D$30+MAX(0,MIN(Inputs!$D$80,Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$D$31</f>
+        <f>MAX(0,MIN(Inputs!$D$94,Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$D$28+MAX(0,MIN(Inputs!$D$94,Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$D$29+MAX(0,MIN(Inputs!$D$94,Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$D$30+MAX(0,MIN(Inputs!$D$94,Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$D$31</f>
         <v/>
       </c>
       <c r="C54" s="20" t="n">
@@ -13185,27 +13916,27 @@
     </row>
     <row r="59">
       <c r="A59" s="10">
-        <f>"Subscription ("&amp;MAX(Inputs!$D$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1)))&amp;" billable users)"</f>
+        <f>"Subscription ("&amp;MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1)))&amp;" billable users)"</f>
         <v/>
       </c>
       <c r="B59" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$D$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(1-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(1-1)</f>
         <v/>
       </c>
       <c r="C59" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$D$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(2-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(2-1)</f>
         <v/>
       </c>
       <c r="D59" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$D$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(3-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(3-1)</f>
         <v/>
       </c>
       <c r="E59" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$D$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(4-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(4-1)</f>
         <v/>
       </c>
       <c r="F59" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$D$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$80,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(5-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(5-1)</f>
         <v/>
       </c>
       <c r="G59" s="34">
@@ -13261,27 +13992,27 @@
     </row>
     <row r="62">
       <c r="A62" s="10">
-        <f>"Infrastructure: "&amp;Inputs!$D$82</f>
+        <f>"Hosting, environment set and Pre-Prod: "&amp;Inputs!$D$96</f>
         <v/>
       </c>
       <c r="B62" s="20">
-        <f>SUMIFS(Infrastructure!$F$5:$F$20,Infrastructure!$A$5:$A$20,Inputs!$D$82,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1)))*12*(1+Infra_Esc)^(1-1)</f>
+        <f>(SUMIFS(Infrastructure!$J$5:$J$20,Infrastructure!$A$5:$A$20,Inputs!$D$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(1-1)</f>
         <v/>
       </c>
       <c r="C62" s="20">
-        <f>SUMIFS(Infrastructure!$F$5:$F$20,Infrastructure!$A$5:$A$20,Inputs!$D$82,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1)))*12*(1+Infra_Esc)^(2-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$D$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(2-1)</f>
         <v/>
       </c>
       <c r="D62" s="20">
-        <f>SUMIFS(Infrastructure!$F$5:$F$20,Infrastructure!$A$5:$A$20,Inputs!$D$82,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1)))*12*(1+Infra_Esc)^(3-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$D$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(3-1)</f>
         <v/>
       </c>
       <c r="E62" s="20">
-        <f>SUMIFS(Infrastructure!$F$5:$F$20,Infrastructure!$A$5:$A$20,Inputs!$D$82,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1)))*12*(1+Infra_Esc)^(4-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$D$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(4-1)</f>
         <v/>
       </c>
       <c r="F62" s="20">
-        <f>SUMIFS(Infrastructure!$F$5:$F$20,Infrastructure!$A$5:$A$20,Inputs!$D$82,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1)))*12*(1+Infra_Esc)^(5-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$D$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(5-1)</f>
         <v/>
       </c>
       <c r="G62" s="34">
@@ -13300,23 +14031,23 @@
         </is>
       </c>
       <c r="B63" s="20">
-        <f>IF(Inputs!$D$83="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))*(1+Esc)^(1-1),0)</f>
+        <f>IF(Inputs!$D$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(1-1),0)</f>
         <v/>
       </c>
       <c r="C63" s="20">
-        <f>IF(Inputs!$D$83="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))*(1+Esc)^(2-1),0)</f>
+        <f>IF(Inputs!$D$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(2-1),0)</f>
         <v/>
       </c>
       <c r="D63" s="20">
-        <f>IF(Inputs!$D$83="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))*(1+Esc)^(3-1),0)</f>
+        <f>IF(Inputs!$D$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(3-1),0)</f>
         <v/>
       </c>
       <c r="E63" s="20">
-        <f>IF(Inputs!$D$83="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))*(1+Esc)^(4-1),0)</f>
+        <f>IF(Inputs!$D$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(4-1),0)</f>
         <v/>
       </c>
       <c r="F63" s="20">
-        <f>IF(Inputs!$D$83="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$80,Inputs!$B$28:$B$31,1))*(1+Esc)^(5-1),0)</f>
+        <f>IF(Inputs!$D$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(5-1),0)</f>
         <v/>
       </c>
       <c r="G63" s="34">
@@ -13335,7 +14066,7 @@
         </is>
       </c>
       <c r="B64" s="20">
-        <f>Inputs!$D$84*Rate_Trainer+ROUND(Mig_Days_Source*Blended/Round_To,0)*Round_To*Inputs!$D$85+ROUND(Int_Std_Days*Blended/Round_To,0)*Round_To*Inputs!$D$86</f>
+        <f>Inputs!$D$98*Rate_Trainer+ROUND(Mig_Days_Source*Blended/Round_To,0)*Round_To*Inputs!$D$99+ROUND(Int_Std_Days*Blended/Round_To,0)*Round_To*Inputs!$D$100</f>
         <v/>
       </c>
       <c r="C64" s="20" t="n">
@@ -13402,28 +14133,28 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="31" t="inlineStr">
+      <c r="A67" s="32" t="inlineStr">
         <is>
           <t>Perpetual with options, excl. VAT</t>
         </is>
       </c>
-      <c r="B67" s="33">
+      <c r="B67" s="24">
         <f>B56+B65</f>
         <v/>
       </c>
-      <c r="C67" s="33">
+      <c r="C67" s="24">
         <f>C56+C65</f>
         <v/>
       </c>
-      <c r="D67" s="33">
+      <c r="D67" s="24">
         <f>D56+D65</f>
         <v/>
       </c>
-      <c r="E67" s="33">
+      <c r="E67" s="24">
         <f>E56+E65</f>
         <v/>
       </c>
-      <c r="F67" s="33">
+      <c r="F67" s="24">
         <f>F56+F65</f>
         <v/>
       </c>
@@ -13437,28 +14168,28 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="31" t="inlineStr">
+      <c r="A68" s="32" t="inlineStr">
         <is>
           <t>Subscription with options, excl. VAT</t>
         </is>
       </c>
-      <c r="B68" s="33">
+      <c r="B68" s="24">
         <f>B60+B65</f>
         <v/>
       </c>
-      <c r="C68" s="33">
+      <c r="C68" s="24">
         <f>C60+C65</f>
         <v/>
       </c>
-      <c r="D68" s="33">
+      <c r="D68" s="24">
         <f>D60+D65</f>
         <v/>
       </c>
-      <c r="E68" s="33">
+      <c r="E68" s="24">
         <f>E60+E65</f>
         <v/>
       </c>
-      <c r="F68" s="33">
+      <c r="F68" s="24">
         <f>F60+F65</f>
         <v/>
       </c>

--- a/docs/package/02_Commercials/BrokerVerse_Commercials_and_Pricing.xlsx
+++ b/docs/package/02_Commercials/BrokerVerse_Commercials_and_Pricing.xlsx
@@ -56,14 +56,20 @@
     <definedName name="Int_Std_Days">Inputs!$B$59</definedName>
     <definedName name="Int_Cx_Days">Inputs!$B$60</definedName>
     <definedName name="Report_Days">Inputs!$B$61</definedName>
-    <definedName name="NP_Small_USD">Inputs!$B$75</definedName>
-    <definedName name="NP_Med_USD">Inputs!$B$76</definedName>
-    <definedName name="PreProd_Factor">Inputs!$B$77</definedName>
-    <definedName name="PreProd_GoLive_Months">Inputs!$B$78</definedName>
-    <definedName name="PreProd_Rel_Months">Inputs!$B$79</definedName>
-    <definedName name="Major_Rel_Year">Inputs!$B$80</definedName>
-    <definedName name="Azure_Factor">Inputs!$B$88</definedName>
-    <definedName name="Local_Factor">Inputs!$B$89</definedName>
+    <definedName name="Conn_Golive_Days">Inputs!$B$62</definedName>
+    <definedName name="AML_Act_Days">Inputs!$B$63</definedName>
+    <definedName name="IC_Act_Days">Inputs!$B$64</definedName>
+    <definedName name="BIR_Act_Days">Inputs!$B$65</definedName>
+    <definedName name="Dealer_Prog_Days">Inputs!$B$66</definedName>
+    <definedName name="Brand_Pack_Days">Inputs!$B$67</definedName>
+    <definedName name="NP_Small_USD">Inputs!$B$81</definedName>
+    <definedName name="NP_Med_USD">Inputs!$B$82</definedName>
+    <definedName name="PreProd_Factor">Inputs!$B$83</definedName>
+    <definedName name="PreProd_GoLive_Months">Inputs!$B$84</definedName>
+    <definedName name="PreProd_Rel_Months">Inputs!$B$85</definedName>
+    <definedName name="Major_Rel_Year">Inputs!$B$86</definedName>
+    <definedName name="Azure_Factor">Inputs!$B$94</definedName>
+    <definedName name="Local_Factor">Inputs!$B$95</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3216,7 +3222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N100"/>
+  <dimension ref="A1:N106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4784,7 +4790,7 @@
       </c>
       <c r="D59" s="15" t="inlineStr">
         <is>
-          <t>Estimate: e.g. one insurer API, SMS gateway, payment gateway variant.</t>
+          <t>Estimate: a new kind of interface not covered by the delivered connectors, e.g. a payment gateway variant or an accounting package feed.</t>
         </is>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -4858,57 +4864,87 @@
       <c r="M61" s="8" t="n"/>
       <c r="N61" s="9" t="n"/>
     </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>Go-live of a delivered connector with one partner (to confirm by management)</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="D62" s="15" t="inlineStr">
+        <is>
+          <t>Assumption: SMS gateway, CTPL provider, one insurer API mapping, one bank file layout or the BIR EIS: configuration, credentials check, live test, support of the partner acceptance. To confirm by management.</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="n"/>
+      <c r="F62" s="8" t="n"/>
+      <c r="G62" s="8" t="n"/>
+      <c r="H62" s="8" t="n"/>
+      <c r="I62" s="8" t="n"/>
+      <c r="J62" s="8" t="n"/>
+      <c r="K62" s="8" t="n"/>
+      <c r="L62" s="8" t="n"/>
+      <c r="M62" s="8" t="n"/>
+      <c r="N62" s="9" t="n"/>
+    </row>
     <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>Infrastructure: AWS reference cost per month of the Production environment (USD)</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="n"/>
-      <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="n"/>
-      <c r="E63" s="7" t="n"/>
-      <c r="F63" s="7" t="n"/>
-      <c r="G63" s="7" t="n"/>
-      <c r="H63" s="7" t="n"/>
-      <c r="I63" s="7" t="n"/>
-      <c r="J63" s="7" t="n"/>
-      <c r="K63" s="7" t="n"/>
-      <c r="L63" s="7" t="n"/>
-      <c r="M63" s="7" t="n"/>
-      <c r="N63" s="7" t="n"/>
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>Activation of the AML/CFT toolkit (to confirm by management)</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="D63" s="15" t="inlineStr">
+        <is>
+          <t>Assumption: risk factors and rules workshop with the compliance officer, settings, first list loads, provider set-up, AMLC test file. To confirm by management.</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="n"/>
+      <c r="F63" s="8" t="n"/>
+      <c r="G63" s="8" t="n"/>
+      <c r="H63" s="8" t="n"/>
+      <c r="I63" s="8" t="n"/>
+      <c r="J63" s="8" t="n"/>
+      <c r="K63" s="8" t="n"/>
+      <c r="L63" s="8" t="n"/>
+      <c r="M63" s="8" t="n"/>
+      <c r="N63" s="9" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>Small</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>Basis</t>
-        </is>
-      </c>
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>Activation of the IC compliance registers (to confirm by management)</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="D64" s="15" t="inlineStr">
+        <is>
+          <t>Assumption: licence and fit and proper register load, insurer certificates, complaints and breach settings, IC statement account mapping to the broker chart. To confirm by management.</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="n"/>
+      <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
       <c r="H64" s="8" t="n"/>
       <c r="I64" s="8" t="n"/>
@@ -4921,26 +4957,24 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>Application containers (API, web, scheduler)</t>
-        </is>
-      </c>
-      <c r="B65" s="16" t="n">
-        <v>90</v>
-      </c>
-      <c r="C65" s="16" t="n">
-        <v>135</v>
-      </c>
-      <c r="D65" s="16" t="n">
-        <v>180</v>
-      </c>
-      <c r="E65" s="16" t="n">
-        <v>360</v>
-      </c>
-      <c r="F65" s="15" t="inlineStr">
-        <is>
-          <t>Estimate: 2/3/4/8 containers of 1 vCPU, 2 GB (Fargate, Singapore).</t>
-        </is>
-      </c>
+          <t>Activation of the BIR pack (to confirm by management)</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="D65" s="15" t="inlineStr">
+        <is>
+          <t>Assumption: BIR and EOPT invoice settings with the tax adviser, ATC mapping, DAT file dry run, CAS books pack. To confirm by management.</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="n"/>
+      <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
       <c r="H65" s="8" t="n"/>
       <c r="I65" s="8" t="n"/>
@@ -4953,26 +4987,24 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>Managed PostgreSQL 16 (instance and storage)</t>
-        </is>
-      </c>
-      <c r="B66" s="16" t="n">
-        <v>85</v>
-      </c>
-      <c r="C66" s="16" t="n">
-        <v>320</v>
-      </c>
-      <c r="D66" s="16" t="n">
-        <v>640</v>
-      </c>
-      <c r="E66" s="16" t="n">
-        <v>1280</v>
-      </c>
-      <c r="F66" s="15" t="inlineStr">
-        <is>
-          <t>Estimate: db.t4g.medium single-AZ / db.m7g.large Multi-AZ / m7g.xlarge Multi-AZ / m7g.2xlarge Multi-AZ (S20). Large and Enterprise: high availability.</t>
-        </is>
-      </c>
+          <t>Set-up of one dealer programme (to confirm by management)</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="D66" s="15" t="inlineStr">
+        <is>
+          <t>Assumption: channels, rates, subsidy, bank letter and the first upload. To confirm by management.</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="n"/>
+      <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
       <c r="H66" s="8" t="n"/>
       <c r="I66" s="8" t="n"/>
@@ -4985,26 +5017,24 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>Object storage and backups (documents, snapshots)</t>
-        </is>
-      </c>
-      <c r="B67" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="C67" s="16" t="n">
-        <v>40</v>
-      </c>
-      <c r="D67" s="16" t="n">
-        <v>90</v>
-      </c>
-      <c r="E67" s="16" t="n">
-        <v>180</v>
-      </c>
-      <c r="F67" s="15" t="inlineStr">
-        <is>
-          <t>Estimate: S3 and snapshot storage, growing with policies and uploads.</t>
-        </is>
-      </c>
+          <t>Client brand pack (to confirm by management)</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="D67" s="15" t="inlineStr">
+        <is>
+          <t>Assumption: theme, sign-in picture, document and e-mail branding, e-signature mapping, exported pack. To confirm by management.</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="n"/>
+      <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
       <c r="H67" s="8" t="n"/>
       <c r="I67" s="8" t="n"/>
@@ -5014,91 +5044,55 @@
       <c r="M67" s="8" t="n"/>
       <c r="N67" s="9" t="n"/>
     </row>
-    <row r="68">
-      <c r="A68" s="10" t="inlineStr">
-        <is>
-          <t>Network (load balancer, CDN, data transfer)</t>
-        </is>
-      </c>
-      <c r="B68" s="16" t="n">
-        <v>45</v>
-      </c>
-      <c r="C68" s="16" t="n">
-        <v>70</v>
-      </c>
-      <c r="D68" s="16" t="n">
-        <v>120</v>
-      </c>
-      <c r="E68" s="16" t="n">
-        <v>220</v>
-      </c>
-      <c r="F68" s="15" t="inlineStr">
-        <is>
-          <t>Estimate.</t>
-        </is>
-      </c>
-      <c r="G68" s="8" t="n"/>
-      <c r="H68" s="8" t="n"/>
-      <c r="I68" s="8" t="n"/>
-      <c r="J68" s="8" t="n"/>
-      <c r="K68" s="8" t="n"/>
-      <c r="L68" s="8" t="n"/>
-      <c r="M68" s="8" t="n"/>
-      <c r="N68" s="9" t="n"/>
-    </row>
     <row r="69">
-      <c r="A69" s="10" t="inlineStr">
-        <is>
-          <t>Security and monitoring (WAF, logs, alarms, secrets, keys)</t>
-        </is>
-      </c>
-      <c r="B69" s="16" t="n">
-        <v>35</v>
-      </c>
-      <c r="C69" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="D69" s="16" t="n">
-        <v>110</v>
-      </c>
-      <c r="E69" s="16" t="n">
-        <v>200</v>
-      </c>
-      <c r="F69" s="15" t="inlineStr">
-        <is>
-          <t>Estimate.</t>
-        </is>
-      </c>
-      <c r="G69" s="8" t="n"/>
-      <c r="H69" s="8" t="n"/>
-      <c r="I69" s="8" t="n"/>
-      <c r="J69" s="8" t="n"/>
-      <c r="K69" s="8" t="n"/>
-      <c r="L69" s="8" t="n"/>
-      <c r="M69" s="8" t="n"/>
-      <c r="N69" s="9" t="n"/>
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Infrastructure: AWS reference cost per month of the Production environment (USD)</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="n"/>
+      <c r="C69" s="7" t="n"/>
+      <c r="D69" s="7" t="n"/>
+      <c r="E69" s="7" t="n"/>
+      <c r="F69" s="7" t="n"/>
+      <c r="G69" s="7" t="n"/>
+      <c r="H69" s="7" t="n"/>
+      <c r="I69" s="7" t="n"/>
+      <c r="J69" s="7" t="n"/>
+      <c r="K69" s="7" t="n"/>
+      <c r="L69" s="7" t="n"/>
+      <c r="M69" s="7" t="n"/>
+      <c r="N69" s="7" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="10" t="inlineStr">
-        <is>
-          <t>Disaster recovery copy (cross-region backups)</t>
-        </is>
-      </c>
-      <c r="B70" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C70" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="16" t="n">
-        <v>400</v>
-      </c>
-      <c r="F70" s="15" t="inlineStr">
-        <is>
-          <t>Estimate: Enterprise only; optional for others. Not part of Pre-Prod.</t>
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Basis</t>
         </is>
       </c>
       <c r="G70" s="8" t="n"/>
@@ -5111,71 +5105,124 @@
       <c r="N70" s="9" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="18" t="inlineStr">
-        <is>
-          <t>Production reference cost per month (USD)</t>
-        </is>
-      </c>
-      <c r="B71" s="21">
-        <f>SUM(B65:B70)</f>
-        <v/>
-      </c>
-      <c r="C71" s="21">
-        <f>SUM(C65:C70)</f>
-        <v/>
-      </c>
-      <c r="D71" s="21">
-        <f>SUM(D65:D70)</f>
-        <v/>
-      </c>
-      <c r="E71" s="21">
-        <f>SUM(E65:E70)</f>
-        <v/>
-      </c>
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>Application containers (API, web, scheduler)</t>
+        </is>
+      </c>
+      <c r="B71" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="C71" s="16" t="n">
+        <v>135</v>
+      </c>
+      <c r="D71" s="16" t="n">
+        <v>180</v>
+      </c>
+      <c r="E71" s="16" t="n">
+        <v>360</v>
+      </c>
+      <c r="F71" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: 2/3/4/8 containers of 1 vCPU, 2 GB (Fargate, Singapore).</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="n"/>
+      <c r="H71" s="8" t="n"/>
+      <c r="I71" s="8" t="n"/>
+      <c r="J71" s="8" t="n"/>
+      <c r="K71" s="8" t="n"/>
+      <c r="L71" s="8" t="n"/>
+      <c r="M71" s="8" t="n"/>
+      <c r="N71" s="9" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>Managed PostgreSQL 16 (instance and storage)</t>
+        </is>
+      </c>
+      <c r="B72" s="16" t="n">
+        <v>85</v>
+      </c>
+      <c r="C72" s="16" t="n">
+        <v>320</v>
+      </c>
+      <c r="D72" s="16" t="n">
+        <v>640</v>
+      </c>
+      <c r="E72" s="16" t="n">
+        <v>1280</v>
+      </c>
+      <c r="F72" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: db.t4g.medium single-AZ / db.m7g.large Multi-AZ / m7g.xlarge Multi-AZ / m7g.2xlarge Multi-AZ (S20). Large and Enterprise: high availability.</t>
+        </is>
+      </c>
+      <c r="G72" s="8" t="n"/>
+      <c r="H72" s="8" t="n"/>
+      <c r="I72" s="8" t="n"/>
+      <c r="J72" s="8" t="n"/>
+      <c r="K72" s="8" t="n"/>
+      <c r="L72" s="8" t="n"/>
+      <c r="M72" s="8" t="n"/>
+      <c r="N72" s="9" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="6" t="inlineStr">
-        <is>
-          <t>Infrastructure: non-production environment sizes and Pre-Prod use</t>
-        </is>
-      </c>
-      <c r="B73" s="7" t="n"/>
-      <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="n"/>
-      <c r="E73" s="7" t="n"/>
-      <c r="F73" s="7" t="n"/>
-      <c r="G73" s="7" t="n"/>
-      <c r="H73" s="7" t="n"/>
-      <c r="I73" s="7" t="n"/>
-      <c r="J73" s="7" t="n"/>
-      <c r="K73" s="7" t="n"/>
-      <c r="L73" s="7" t="n"/>
-      <c r="M73" s="7" t="n"/>
-      <c r="N73" s="7" t="n"/>
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>Object storage and backups (documents, snapshots)</t>
+        </is>
+      </c>
+      <c r="B73" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="C73" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="D73" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="E73" s="16" t="n">
+        <v>180</v>
+      </c>
+      <c r="F73" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: S3 and snapshot storage, growing with policies and uploads.</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="n"/>
+      <c r="H73" s="8" t="n"/>
+      <c r="I73" s="8" t="n"/>
+      <c r="J73" s="8" t="n"/>
+      <c r="K73" s="8" t="n"/>
+      <c r="L73" s="8" t="n"/>
+      <c r="M73" s="8" t="n"/>
+      <c r="N73" s="9" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>Driver</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>Basis</t>
-        </is>
-      </c>
-      <c r="E74" s="8" t="n"/>
-      <c r="F74" s="8" t="n"/>
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>Network (load balancer, CDN, data transfer)</t>
+        </is>
+      </c>
+      <c r="B74" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="C74" s="16" t="n">
+        <v>70</v>
+      </c>
+      <c r="D74" s="16" t="n">
+        <v>120</v>
+      </c>
+      <c r="E74" s="16" t="n">
+        <v>220</v>
+      </c>
+      <c r="F74" s="15" t="inlineStr">
+        <is>
+          <t>Estimate.</t>
+        </is>
+      </c>
       <c r="G74" s="8" t="n"/>
       <c r="H74" s="8" t="n"/>
       <c r="I74" s="8" t="n"/>
@@ -5188,24 +5235,26 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>Non-production environment, small: cloud cost per month</t>
+          <t>Security and monitoring (WAF, logs, alarms, secrets, keys)</t>
         </is>
       </c>
       <c r="B75" s="16" t="n">
-        <v>150</v>
-      </c>
-      <c r="C75" s="10" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D75" s="15" t="inlineStr">
-        <is>
-          <t>Estimate: 1 container of 1 vCPU, 2 GB; PostgreSQL db.t4g.medium single-AZ, 50 GB; file store; backups 7 to 14 days. Dev in every tier; UAT of Small and Medium brokers.</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="n"/>
-      <c r="F75" s="8" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="C75" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="D75" s="16" t="n">
+        <v>110</v>
+      </c>
+      <c r="E75" s="16" t="n">
+        <v>200</v>
+      </c>
+      <c r="F75" s="15" t="inlineStr">
+        <is>
+          <t>Estimate.</t>
+        </is>
+      </c>
       <c r="G75" s="8" t="n"/>
       <c r="H75" s="8" t="n"/>
       <c r="I75" s="8" t="n"/>
@@ -5218,24 +5267,26 @@
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>Non-production environment, medium: cloud cost per month</t>
+          <t>Disaster recovery copy (cross-region backups)</t>
         </is>
       </c>
       <c r="B76" s="16" t="n">
-        <v>300</v>
-      </c>
-      <c r="C76" s="10" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D76" s="15" t="inlineStr">
-        <is>
-          <t>Estimate: 2 containers of 1 vCPU, 2 GB (the second for the UAT performance test); db.t4g.large single-AZ, 100 GB; file store; load balancer. SIT and UAT of Large and Enterprise brokers.</t>
-        </is>
-      </c>
-      <c r="E76" s="8" t="n"/>
-      <c r="F76" s="8" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="C76" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="16" t="n">
+        <v>400</v>
+      </c>
+      <c r="F76" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: Enterprise only; optional for others. Not part of Pre-Prod.</t>
+        </is>
+      </c>
       <c r="G76" s="8" t="n"/>
       <c r="H76" s="8" t="n"/>
       <c r="I76" s="8" t="n"/>
@@ -5246,112 +5297,67 @@
       <c r="N76" s="9" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="10" t="inlineStr">
-        <is>
-          <t>Pre-Prod cloud cost relative to Production (without the DR copy)</t>
-        </is>
-      </c>
-      <c r="B77" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C77" s="10" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D77" s="15" t="inlineStr">
-        <is>
-          <t>Assumption: Pre-Prod is restored from a production backup and runs at production topology and size, so the rehearsal measures real timings.</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="n"/>
-      <c r="F77" s="8" t="n"/>
-      <c r="G77" s="8" t="n"/>
-      <c r="H77" s="8" t="n"/>
-      <c r="I77" s="8" t="n"/>
-      <c r="J77" s="8" t="n"/>
-      <c r="K77" s="8" t="n"/>
-      <c r="L77" s="8" t="n"/>
-      <c r="M77" s="8" t="n"/>
-      <c r="N77" s="9" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="10" t="inlineStr">
-        <is>
-          <t>Pre-Prod months of use around go-live</t>
-        </is>
-      </c>
-      <c r="B78" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C78" s="10" t="inlineStr">
-        <is>
-          <t>months</t>
-        </is>
-      </c>
-      <c r="D78" s="15" t="inlineStr">
-        <is>
-          <t>Assumption: created before the cutover rehearsal and removed after hypercare (1 to 2 months). Billed per month of use.</t>
-        </is>
-      </c>
-      <c r="E78" s="8" t="n"/>
-      <c r="F78" s="8" t="n"/>
-      <c r="G78" s="8" t="n"/>
-      <c r="H78" s="8" t="n"/>
-      <c r="I78" s="8" t="n"/>
-      <c r="J78" s="8" t="n"/>
-      <c r="K78" s="8" t="n"/>
-      <c r="L78" s="8" t="n"/>
-      <c r="M78" s="8" t="n"/>
-      <c r="N78" s="9" t="n"/>
+      <c r="A77" s="18" t="inlineStr">
+        <is>
+          <t>Production reference cost per month (USD)</t>
+        </is>
+      </c>
+      <c r="B77" s="21">
+        <f>SUM(B71:B76)</f>
+        <v/>
+      </c>
+      <c r="C77" s="21">
+        <f>SUM(C71:C76)</f>
+        <v/>
+      </c>
+      <c r="D77" s="21">
+        <f>SUM(D71:D76)</f>
+        <v/>
+      </c>
+      <c r="E77" s="21">
+        <f>SUM(E71:E76)</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>Pre-Prod months of use per major release</t>
-        </is>
-      </c>
-      <c r="B79" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C79" s="10" t="inlineStr">
-        <is>
-          <t>months</t>
-        </is>
-      </c>
-      <c r="D79" s="15" t="inlineStr">
-        <is>
-          <t>Assumption: created from a production backup for the release rehearsal and removed after the release.</t>
-        </is>
-      </c>
-      <c r="E79" s="8" t="n"/>
-      <c r="F79" s="8" t="n"/>
-      <c r="G79" s="8" t="n"/>
-      <c r="H79" s="8" t="n"/>
-      <c r="I79" s="8" t="n"/>
-      <c r="J79" s="8" t="n"/>
-      <c r="K79" s="8" t="n"/>
-      <c r="L79" s="8" t="n"/>
-      <c r="M79" s="8" t="n"/>
-      <c r="N79" s="9" t="n"/>
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Infrastructure: non-production environment sizes and Pre-Prod use</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="n"/>
+      <c r="C79" s="7" t="n"/>
+      <c r="D79" s="7" t="n"/>
+      <c r="E79" s="7" t="n"/>
+      <c r="F79" s="7" t="n"/>
+      <c r="G79" s="7" t="n"/>
+      <c r="H79" s="7" t="n"/>
+      <c r="I79" s="7" t="n"/>
+      <c r="J79" s="7" t="n"/>
+      <c r="K79" s="7" t="n"/>
+      <c r="L79" s="7" t="n"/>
+      <c r="M79" s="7" t="n"/>
+      <c r="N79" s="7" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="10" t="inlineStr">
-        <is>
-          <t>Major releases per year (yearly hosting view only)</t>
-        </is>
-      </c>
-      <c r="B80" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C80" s="10" t="inlineStr">
-        <is>
-          <t>releases</t>
-        </is>
-      </c>
-      <c r="D80" s="15" t="inlineStr">
-        <is>
-          <t>Assumption for budgeting. Major releases are announced at least 6 months ahead (Release Notes and Roadmap); the invoice follows the actual months of use.</t>
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Basis</t>
         </is>
       </c>
       <c r="E80" s="8" t="n"/>
@@ -5365,67 +5371,89 @@
       <c r="M80" s="8" t="n"/>
       <c r="N80" s="9" t="n"/>
     </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>Non-production environment, small: cloud cost per month</t>
+        </is>
+      </c>
+      <c r="B81" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D81" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: 1 container of 1 vCPU, 2 GB; PostgreSQL db.t4g.medium single-AZ, 50 GB; file store; backups 7 to 14 days. Dev in every tier; UAT of Small and Medium brokers.</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="n"/>
+      <c r="F81" s="8" t="n"/>
+      <c r="G81" s="8" t="n"/>
+      <c r="H81" s="8" t="n"/>
+      <c r="I81" s="8" t="n"/>
+      <c r="J81" s="8" t="n"/>
+      <c r="K81" s="8" t="n"/>
+      <c r="L81" s="8" t="n"/>
+      <c r="M81" s="8" t="n"/>
+      <c r="N81" s="9" t="n"/>
+    </row>
     <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>Infrastructure: environment set by tier, AWS reference cost per month (USD)</t>
-        </is>
-      </c>
-      <c r="B82" s="7" t="n"/>
-      <c r="C82" s="7" t="n"/>
-      <c r="D82" s="7" t="n"/>
-      <c r="E82" s="7" t="n"/>
-      <c r="F82" s="7" t="n"/>
-      <c r="G82" s="7" t="n"/>
-      <c r="H82" s="7" t="n"/>
-      <c r="I82" s="7" t="n"/>
-      <c r="J82" s="7" t="n"/>
-      <c r="K82" s="7" t="n"/>
-      <c r="L82" s="7" t="n"/>
-      <c r="M82" s="7" t="n"/>
-      <c r="N82" s="7" t="n"/>
-    </row>
-    <row r="83" ht="30" customHeight="1">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>Tier</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>Dev</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>SIT</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>UAT</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>Production</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>Standing environments</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>Pre-Prod per month of use</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr">
-        <is>
-          <t>Environment set and basis</t>
-        </is>
-      </c>
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>Non-production environment, medium: cloud cost per month</t>
+        </is>
+      </c>
+      <c r="B82" s="16" t="n">
+        <v>300</v>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D82" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: 2 containers of 1 vCPU, 2 GB (the second for the UAT performance test); db.t4g.large single-AZ, 100 GB; file store; load balancer. SIT and UAT of Large and Enterprise brokers.</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="n"/>
+      <c r="F82" s="8" t="n"/>
+      <c r="G82" s="8" t="n"/>
+      <c r="H82" s="8" t="n"/>
+      <c r="I82" s="8" t="n"/>
+      <c r="J82" s="8" t="n"/>
+      <c r="K82" s="8" t="n"/>
+      <c r="L82" s="8" t="n"/>
+      <c r="M82" s="8" t="n"/>
+      <c r="N82" s="9" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>Pre-Prod cloud cost relative to Production (without the DR copy)</t>
+        </is>
+      </c>
+      <c r="B83" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D83" s="15" t="inlineStr">
+        <is>
+          <t>Assumption: Pre-Prod is restored from a production backup and runs at production topology and size, so the rehearsal measures real timings.</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="n"/>
+      <c r="F83" s="8" t="n"/>
+      <c r="G83" s="8" t="n"/>
+      <c r="H83" s="8" t="n"/>
       <c r="I83" s="8" t="n"/>
       <c r="J83" s="8" t="n"/>
       <c r="K83" s="8" t="n"/>
@@ -5434,38 +5462,28 @@
       <c r="N83" s="9" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="18">
-        <f>A28</f>
-        <v/>
-      </c>
-      <c r="B84" s="20">
-        <f>NP_Small_USD</f>
-        <v/>
-      </c>
-      <c r="C84" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="20">
-        <f>NP_Small_USD</f>
-        <v/>
-      </c>
-      <c r="E84" s="20">
-        <f>B71</f>
-        <v/>
-      </c>
-      <c r="F84" s="24">
-        <f>SUM(B84:E84)</f>
-        <v/>
-      </c>
-      <c r="G84" s="21">
-        <f>SUM(B65:B69)*PreProd_Factor</f>
-        <v/>
-      </c>
-      <c r="H84" s="5" t="inlineStr">
-        <is>
-          <t>Dev, UAT, Production, temporary Pre-Prod. Integration and SIT in Dev, then promoted to UAT for testing.</t>
-        </is>
-      </c>
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>Pre-Prod months of use around go-live</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="D84" s="15" t="inlineStr">
+        <is>
+          <t>Assumption: created before the cutover rehearsal and removed after hypercare (1 to 2 months). Billed per month of use.</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="n"/>
+      <c r="F84" s="8" t="n"/>
+      <c r="G84" s="8" t="n"/>
+      <c r="H84" s="8" t="n"/>
       <c r="I84" s="8" t="n"/>
       <c r="J84" s="8" t="n"/>
       <c r="K84" s="8" t="n"/>
@@ -5474,38 +5492,28 @@
       <c r="N84" s="9" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="18">
-        <f>A29</f>
-        <v/>
-      </c>
-      <c r="B85" s="20">
-        <f>NP_Small_USD</f>
-        <v/>
-      </c>
-      <c r="C85" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="20">
-        <f>NP_Small_USD</f>
-        <v/>
-      </c>
-      <c r="E85" s="20">
-        <f>C71</f>
-        <v/>
-      </c>
-      <c r="F85" s="24">
-        <f>SUM(B85:E85)</f>
-        <v/>
-      </c>
-      <c r="G85" s="21">
-        <f>SUM(C65:C69)*PreProd_Factor</f>
-        <v/>
-      </c>
-      <c r="H85" s="5" t="inlineStr">
-        <is>
-          <t>Dev, UAT, Production, temporary Pre-Prod. As Small.</t>
-        </is>
-      </c>
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>Pre-Prod months of use per major release</t>
+        </is>
+      </c>
+      <c r="B85" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="inlineStr">
+        <is>
+          <t>Assumption: created from a production backup for the release rehearsal and removed after the release.</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="n"/>
+      <c r="F85" s="8" t="n"/>
+      <c r="G85" s="8" t="n"/>
+      <c r="H85" s="8" t="n"/>
       <c r="I85" s="8" t="n"/>
       <c r="J85" s="8" t="n"/>
       <c r="K85" s="8" t="n"/>
@@ -5514,39 +5522,28 @@
       <c r="N85" s="9" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="18">
-        <f>A30</f>
-        <v/>
-      </c>
-      <c r="B86" s="20">
-        <f>NP_Small_USD</f>
-        <v/>
-      </c>
-      <c r="C86" s="20">
-        <f>NP_Med_USD</f>
-        <v/>
-      </c>
-      <c r="D86" s="20">
-        <f>NP_Med_USD</f>
-        <v/>
-      </c>
-      <c r="E86" s="20">
-        <f>D71</f>
-        <v/>
-      </c>
-      <c r="F86" s="24">
-        <f>SUM(B86:E86)</f>
-        <v/>
-      </c>
-      <c r="G86" s="21">
-        <f>SUM(D65:D69)*PreProd_Factor</f>
-        <v/>
-      </c>
-      <c r="H86" s="5" t="inlineStr">
-        <is>
-          <t>Dev, SIT, UAT, Production with high availability, temporary Pre-Prod. SIT and UAT are separate.</t>
-        </is>
-      </c>
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>Major releases per year (yearly hosting view only)</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>releases</t>
+        </is>
+      </c>
+      <c r="D86" s="15" t="inlineStr">
+        <is>
+          <t>Assumption for budgeting. Major releases are announced at least 6 months ahead (Release Notes and Roadmap); the invoice follows the actual months of use.</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="n"/>
+      <c r="F86" s="8" t="n"/>
+      <c r="G86" s="8" t="n"/>
+      <c r="H86" s="8" t="n"/>
       <c r="I86" s="8" t="n"/>
       <c r="J86" s="8" t="n"/>
       <c r="K86" s="8" t="n"/>
@@ -5554,86 +5551,67 @@
       <c r="M86" s="8" t="n"/>
       <c r="N86" s="9" t="n"/>
     </row>
-    <row r="87">
-      <c r="A87" s="18">
-        <f>A31</f>
-        <v/>
-      </c>
-      <c r="B87" s="20">
-        <f>NP_Small_USD</f>
-        <v/>
-      </c>
-      <c r="C87" s="20">
-        <f>NP_Med_USD</f>
-        <v/>
-      </c>
-      <c r="D87" s="20">
-        <f>NP_Med_USD</f>
-        <v/>
-      </c>
-      <c r="E87" s="20">
-        <f>E71</f>
-        <v/>
-      </c>
-      <c r="F87" s="24">
-        <f>SUM(B87:E87)</f>
-        <v/>
-      </c>
-      <c r="G87" s="21">
-        <f>SUM(E65:E69)*PreProd_Factor</f>
-        <v/>
-      </c>
-      <c r="H87" s="5" t="inlineStr">
-        <is>
-          <t>As Large, with the cross-region DR copy in Production.</t>
-        </is>
-      </c>
-      <c r="I87" s="8" t="n"/>
-      <c r="J87" s="8" t="n"/>
-      <c r="K87" s="8" t="n"/>
-      <c r="L87" s="8" t="n"/>
-      <c r="M87" s="8" t="n"/>
-      <c r="N87" s="9" t="n"/>
-    </row>
     <row r="88">
-      <c r="A88" s="10" t="inlineStr">
-        <is>
-          <t>Azure cost relative to AWS</t>
-        </is>
-      </c>
-      <c r="B88" s="11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="F88" s="15" t="inlineStr">
-        <is>
-          <t>Assumption: comparable list prices in Southeast Asia (D4s v5 Linux about USD 158 a month, S21); +5% for managed PostgreSQL and WAF differences.</t>
-        </is>
-      </c>
-      <c r="G88" s="8" t="n"/>
-      <c r="H88" s="8" t="n"/>
-      <c r="I88" s="8" t="n"/>
-      <c r="J88" s="8" t="n"/>
-      <c r="K88" s="8" t="n"/>
-      <c r="L88" s="8" t="n"/>
-      <c r="M88" s="8" t="n"/>
-      <c r="N88" s="9" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="10" t="inlineStr">
-        <is>
-          <t>Local partner cloud cost relative to AWS</t>
-        </is>
-      </c>
-      <c r="B89" s="11" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F89" s="15" t="inlineStr">
-        <is>
-          <t>Assumption: Philippine data-centre or partner cloud priced in PHP; lower compute and bandwidth, database run as managed VM. Confirm with a partner quotation.</t>
-        </is>
-      </c>
-      <c r="G89" s="8" t="n"/>
-      <c r="H89" s="8" t="n"/>
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>Infrastructure: environment set by tier, AWS reference cost per month (USD)</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="n"/>
+      <c r="C88" s="7" t="n"/>
+      <c r="D88" s="7" t="n"/>
+      <c r="E88" s="7" t="n"/>
+      <c r="F88" s="7" t="n"/>
+      <c r="G88" s="7" t="n"/>
+      <c r="H88" s="7" t="n"/>
+      <c r="I88" s="7" t="n"/>
+      <c r="J88" s="7" t="n"/>
+      <c r="K88" s="7" t="n"/>
+      <c r="L88" s="7" t="n"/>
+      <c r="M88" s="7" t="n"/>
+      <c r="N88" s="7" t="n"/>
+    </row>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>SIT</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>UAT</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>Standing environments</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>Pre-Prod per month of use</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>Environment set and basis</t>
+        </is>
+      </c>
       <c r="I89" s="8" t="n"/>
       <c r="J89" s="8" t="n"/>
       <c r="K89" s="8" t="n"/>
@@ -5641,55 +5619,120 @@
       <c r="M89" s="8" t="n"/>
       <c r="N89" s="9" t="n"/>
     </row>
+    <row r="90">
+      <c r="A90" s="18">
+        <f>A28</f>
+        <v/>
+      </c>
+      <c r="B90" s="20">
+        <f>NP_Small_USD</f>
+        <v/>
+      </c>
+      <c r="C90" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="20">
+        <f>NP_Small_USD</f>
+        <v/>
+      </c>
+      <c r="E90" s="20">
+        <f>B77</f>
+        <v/>
+      </c>
+      <c r="F90" s="24">
+        <f>SUM(B90:E90)</f>
+        <v/>
+      </c>
+      <c r="G90" s="21">
+        <f>SUM(B71:B75)*PreProd_Factor</f>
+        <v/>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>Dev, UAT, Production, temporary Pre-Prod. Integration and SIT in Dev, then promoted to UAT for testing.</t>
+        </is>
+      </c>
+      <c r="I90" s="8" t="n"/>
+      <c r="J90" s="8" t="n"/>
+      <c r="K90" s="8" t="n"/>
+      <c r="L90" s="8" t="n"/>
+      <c r="M90" s="8" t="n"/>
+      <c r="N90" s="9" t="n"/>
+    </row>
     <row r="91">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>Sample quote scenarios (used by Sample Quotes)</t>
-        </is>
-      </c>
-      <c r="B91" s="7" t="n"/>
-      <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="n"/>
-      <c r="E91" s="7" t="n"/>
-      <c r="F91" s="7" t="n"/>
-      <c r="G91" s="7" t="n"/>
-      <c r="H91" s="7" t="n"/>
-      <c r="I91" s="7" t="n"/>
-      <c r="J91" s="7" t="n"/>
-      <c r="K91" s="7" t="n"/>
-      <c r="L91" s="7" t="n"/>
-      <c r="M91" s="7" t="n"/>
-      <c r="N91" s="7" t="n"/>
+      <c r="A91" s="18">
+        <f>A29</f>
+        <v/>
+      </c>
+      <c r="B91" s="20">
+        <f>NP_Small_USD</f>
+        <v/>
+      </c>
+      <c r="C91" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="20">
+        <f>NP_Small_USD</f>
+        <v/>
+      </c>
+      <c r="E91" s="20">
+        <f>C77</f>
+        <v/>
+      </c>
+      <c r="F91" s="24">
+        <f>SUM(B91:E91)</f>
+        <v/>
+      </c>
+      <c r="G91" s="21">
+        <f>SUM(C71:C75)*PreProd_Factor</f>
+        <v/>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>Dev, UAT, Production, temporary Pre-Prod. As Small.</t>
+        </is>
+      </c>
+      <c r="I91" s="8" t="n"/>
+      <c r="J91" s="8" t="n"/>
+      <c r="K91" s="8" t="n"/>
+      <c r="L91" s="8" t="n"/>
+      <c r="M91" s="8" t="n"/>
+      <c r="N91" s="9" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>Driver</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>Example 1</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="inlineStr">
-        <is>
-          <t>Example 2</t>
-        </is>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>Example 3</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr"/>
-      <c r="F92" s="3" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="G92" s="8" t="n"/>
-      <c r="H92" s="8" t="n"/>
+      <c r="A92" s="18">
+        <f>A30</f>
+        <v/>
+      </c>
+      <c r="B92" s="20">
+        <f>NP_Small_USD</f>
+        <v/>
+      </c>
+      <c r="C92" s="20">
+        <f>NP_Med_USD</f>
+        <v/>
+      </c>
+      <c r="D92" s="20">
+        <f>NP_Med_USD</f>
+        <v/>
+      </c>
+      <c r="E92" s="20">
+        <f>D77</f>
+        <v/>
+      </c>
+      <c r="F92" s="24">
+        <f>SUM(B92:E92)</f>
+        <v/>
+      </c>
+      <c r="G92" s="21">
+        <f>SUM(D71:D75)*PreProd_Factor</f>
+        <v/>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>Dev, SIT, UAT, Production with high availability, temporary Pre-Prod. SIT and UAT are separate.</t>
+        </is>
+      </c>
       <c r="I92" s="8" t="n"/>
       <c r="J92" s="8" t="n"/>
       <c r="K92" s="8" t="n"/>
@@ -5698,33 +5741,39 @@
       <c r="N92" s="9" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="10" t="inlineStr">
-        <is>
-          <t>Broker profile</t>
-        </is>
-      </c>
-      <c r="B93" s="12" t="inlineStr">
-        <is>
-          <t>Small broker</t>
-        </is>
-      </c>
-      <c r="C93" s="12" t="inlineStr">
-        <is>
-          <t>Medium broker</t>
-        </is>
-      </c>
-      <c r="D93" s="12" t="inlineStr">
-        <is>
-          <t>Large broker</t>
-        </is>
-      </c>
-      <c r="F93" s="10" t="inlineStr">
-        <is>
-          <t>Label only.</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="n"/>
-      <c r="H93" s="8" t="n"/>
+      <c r="A93" s="18">
+        <f>A31</f>
+        <v/>
+      </c>
+      <c r="B93" s="20">
+        <f>NP_Small_USD</f>
+        <v/>
+      </c>
+      <c r="C93" s="20">
+        <f>NP_Med_USD</f>
+        <v/>
+      </c>
+      <c r="D93" s="20">
+        <f>NP_Med_USD</f>
+        <v/>
+      </c>
+      <c r="E93" s="20">
+        <f>E77</f>
+        <v/>
+      </c>
+      <c r="F93" s="24">
+        <f>SUM(B93:E93)</f>
+        <v/>
+      </c>
+      <c r="G93" s="21">
+        <f>SUM(E71:E75)*PreProd_Factor</f>
+        <v/>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>As Large, with the cross-region DR copy in Production.</t>
+        </is>
+      </c>
       <c r="I93" s="8" t="n"/>
       <c r="J93" s="8" t="n"/>
       <c r="K93" s="8" t="n"/>
@@ -5735,21 +5784,15 @@
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>Named users</t>
-        </is>
-      </c>
-      <c r="B94" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C94" s="14" t="n">
-        <v>60</v>
-      </c>
-      <c r="D94" s="14" t="n">
-        <v>180</v>
-      </c>
-      <c r="F94" s="10" t="inlineStr">
-        <is>
-          <t>Tier follows from the user count.</t>
+          <t>Azure cost relative to AWS</t>
+        </is>
+      </c>
+      <c r="B94" s="11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F94" s="15" t="inlineStr">
+        <is>
+          <t>Assumption: comparable list prices in Southeast Asia (D4s v5 Linux about USD 158 a month, S21); +5% for managed PostgreSQL and WAF differences.</t>
         </is>
       </c>
       <c r="G94" s="8" t="n"/>
@@ -5764,21 +5807,15 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>Lines of business</t>
-        </is>
-      </c>
-      <c r="B95" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C95" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="D95" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="F95" s="10" t="inlineStr">
-        <is>
-          <t>Motor, fire, marine, casualty, engineering, bonds and so on.</t>
+          <t>Local partner cloud cost relative to AWS</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F95" s="15" t="inlineStr">
+        <is>
+          <t>Assumption: Philippine data-centre or partner cloud priced in PHP; lower compute and bandwidth, database run as managed VM. Confirm with a partner quotation.</t>
         </is>
       </c>
       <c r="G95" s="8" t="n"/>
@@ -5790,94 +5827,51 @@
       <c r="M95" s="8" t="n"/>
       <c r="N95" s="9" t="n"/>
     </row>
-    <row r="96">
-      <c r="A96" s="10" t="inlineStr">
-        <is>
-          <t>Infrastructure provider (AWS, Azure, Local partner, Customer)</t>
-        </is>
-      </c>
-      <c r="B96" s="12" t="inlineStr">
-        <is>
-          <t>AWS</t>
-        </is>
-      </c>
-      <c r="C96" s="12" t="inlineStr">
-        <is>
-          <t>Azure</t>
-        </is>
-      </c>
-      <c r="D96" s="12" t="inlineStr">
-        <is>
-          <t>Local partner</t>
-        </is>
-      </c>
-      <c r="F96" s="10" t="inlineStr">
-        <is>
-          <t>"Customer" means the broker hosts itself: no infrastructure fee.</t>
-        </is>
-      </c>
-      <c r="G96" s="8" t="n"/>
-      <c r="H96" s="8" t="n"/>
-      <c r="I96" s="8" t="n"/>
-      <c r="J96" s="8" t="n"/>
-      <c r="K96" s="8" t="n"/>
-      <c r="L96" s="8" t="n"/>
-      <c r="M96" s="8" t="n"/>
-      <c r="N96" s="9" t="n"/>
-    </row>
     <row r="97">
-      <c r="A97" s="10" t="inlineStr">
-        <is>
-          <t>24x7 Severity 1 support (Yes/No)</t>
-        </is>
-      </c>
-      <c r="B97" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C97" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D97" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F97" s="10" t="inlineStr">
-        <is>
-          <t>Optional.</t>
-        </is>
-      </c>
-      <c r="G97" s="8" t="n"/>
-      <c r="H97" s="8" t="n"/>
-      <c r="I97" s="8" t="n"/>
-      <c r="J97" s="8" t="n"/>
-      <c r="K97" s="8" t="n"/>
-      <c r="L97" s="8" t="n"/>
-      <c r="M97" s="8" t="n"/>
-      <c r="N97" s="9" t="n"/>
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>Sample quote scenarios (used by Sample Quotes)</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="n"/>
+      <c r="C97" s="7" t="n"/>
+      <c r="D97" s="7" t="n"/>
+      <c r="E97" s="7" t="n"/>
+      <c r="F97" s="7" t="n"/>
+      <c r="G97" s="7" t="n"/>
+      <c r="H97" s="7" t="n"/>
+      <c r="I97" s="7" t="n"/>
+      <c r="J97" s="7" t="n"/>
+      <c r="K97" s="7" t="n"/>
+      <c r="L97" s="7" t="n"/>
+      <c r="M97" s="7" t="n"/>
+      <c r="N97" s="7" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="10" t="inlineStr">
-        <is>
-          <t>Extra training days</t>
-        </is>
-      </c>
-      <c r="B98" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C98" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D98" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="F98" s="10" t="inlineStr">
-        <is>
-          <t>Beyond the days included for the tier.</t>
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Example 1</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Example 2</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Example 3</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr"/>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
       <c r="G98" s="8" t="n"/>
@@ -5892,21 +5886,27 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>Extra legacy data sources to migrate</t>
-        </is>
-      </c>
-      <c r="B99" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C99" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D99" s="14" t="n">
-        <v>2</v>
+          <t>Broker profile</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="inlineStr">
+        <is>
+          <t>Small broker</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>Medium broker</t>
+        </is>
+      </c>
+      <c r="D99" s="12" t="inlineStr">
+        <is>
+          <t>Large broker</t>
+        </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>Beyond the standard templates.</t>
+          <t>Label only.</t>
         </is>
       </c>
       <c r="G99" s="8" t="n"/>
@@ -5921,21 +5921,21 @@
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>Additional standard integrations</t>
+          <t>Named users</t>
         </is>
       </c>
       <c r="B100" s="14" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C100" s="14" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D100" s="14" t="n">
-        <v>2</v>
+        <v>180</v>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>One-time.</t>
+          <t>Tier follows from the user count.</t>
         </is>
       </c>
       <c r="G100" s="8" t="n"/>
@@ -5947,82 +5947,274 @@
       <c r="M100" s="8" t="n"/>
       <c r="N100" s="9" t="n"/>
     </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>Lines of business</t>
+        </is>
+      </c>
+      <c r="B101" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C101" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="D101" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F101" s="10" t="inlineStr">
+        <is>
+          <t>Motor, fire, marine, casualty, engineering, bonds and so on.</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="n"/>
+      <c r="H101" s="8" t="n"/>
+      <c r="I101" s="8" t="n"/>
+      <c r="J101" s="8" t="n"/>
+      <c r="K101" s="8" t="n"/>
+      <c r="L101" s="8" t="n"/>
+      <c r="M101" s="8" t="n"/>
+      <c r="N101" s="9" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>Infrastructure provider (AWS, Azure, Local partner, Customer)</t>
+        </is>
+      </c>
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>Azure</t>
+        </is>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>Local partner</t>
+        </is>
+      </c>
+      <c r="F102" s="10" t="inlineStr">
+        <is>
+          <t>"Customer" means the broker hosts itself: no infrastructure fee.</t>
+        </is>
+      </c>
+      <c r="G102" s="8" t="n"/>
+      <c r="H102" s="8" t="n"/>
+      <c r="I102" s="8" t="n"/>
+      <c r="J102" s="8" t="n"/>
+      <c r="K102" s="8" t="n"/>
+      <c r="L102" s="8" t="n"/>
+      <c r="M102" s="8" t="n"/>
+      <c r="N102" s="9" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>24x7 Severity 1 support (Yes/No)</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F103" s="10" t="inlineStr">
+        <is>
+          <t>Optional.</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="n"/>
+      <c r="H103" s="8" t="n"/>
+      <c r="I103" s="8" t="n"/>
+      <c r="J103" s="8" t="n"/>
+      <c r="K103" s="8" t="n"/>
+      <c r="L103" s="8" t="n"/>
+      <c r="M103" s="8" t="n"/>
+      <c r="N103" s="9" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t>Extra training days</t>
+        </is>
+      </c>
+      <c r="B104" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D104" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F104" s="10" t="inlineStr">
+        <is>
+          <t>Beyond the days included for the tier.</t>
+        </is>
+      </c>
+      <c r="G104" s="8" t="n"/>
+      <c r="H104" s="8" t="n"/>
+      <c r="I104" s="8" t="n"/>
+      <c r="J104" s="8" t="n"/>
+      <c r="K104" s="8" t="n"/>
+      <c r="L104" s="8" t="n"/>
+      <c r="M104" s="8" t="n"/>
+      <c r="N104" s="9" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>Extra legacy data sources to migrate</t>
+        </is>
+      </c>
+      <c r="B105" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F105" s="10" t="inlineStr">
+        <is>
+          <t>Beyond the standard templates.</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="n"/>
+      <c r="H105" s="8" t="n"/>
+      <c r="I105" s="8" t="n"/>
+      <c r="J105" s="8" t="n"/>
+      <c r="K105" s="8" t="n"/>
+      <c r="L105" s="8" t="n"/>
+      <c r="M105" s="8" t="n"/>
+      <c r="N105" s="9" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <t>Additional standard integrations</t>
+        </is>
+      </c>
+      <c r="B106" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C106" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F106" s="10" t="inlineStr">
+        <is>
+          <t>One-time.</t>
+        </is>
+      </c>
+      <c r="G106" s="8" t="n"/>
+      <c r="H106" s="8" t="n"/>
+      <c r="I106" s="8" t="n"/>
+      <c r="J106" s="8" t="n"/>
+      <c r="K106" s="8" t="n"/>
+      <c r="L106" s="8" t="n"/>
+      <c r="M106" s="8" t="n"/>
+      <c r="N106" s="9" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="68">
+  <mergeCells count="74">
     <mergeCell ref="E36:N36"/>
     <mergeCell ref="D59:N59"/>
-    <mergeCell ref="D79:N79"/>
     <mergeCell ref="D50:N50"/>
-    <mergeCell ref="H84:N84"/>
+    <mergeCell ref="F104:N104"/>
     <mergeCell ref="D60:N60"/>
+    <mergeCell ref="F76:N76"/>
     <mergeCell ref="F95:N95"/>
     <mergeCell ref="D19:N19"/>
+    <mergeCell ref="D63:N63"/>
     <mergeCell ref="F94:N94"/>
     <mergeCell ref="D10:N10"/>
-    <mergeCell ref="H87:N87"/>
+    <mergeCell ref="F101:N101"/>
     <mergeCell ref="F70:N70"/>
-    <mergeCell ref="F97:N97"/>
-    <mergeCell ref="F66:N66"/>
+    <mergeCell ref="D81:N81"/>
     <mergeCell ref="D46:N46"/>
-    <mergeCell ref="H86:N86"/>
+    <mergeCell ref="D84:N84"/>
+    <mergeCell ref="F75:N75"/>
+    <mergeCell ref="F106:N106"/>
     <mergeCell ref="D80:N80"/>
     <mergeCell ref="E41:N41"/>
+    <mergeCell ref="D65:N65"/>
+    <mergeCell ref="D45:N45"/>
     <mergeCell ref="F100:N100"/>
-    <mergeCell ref="D45:N45"/>
+    <mergeCell ref="F72:N72"/>
     <mergeCell ref="E37:N37"/>
     <mergeCell ref="D6:N6"/>
     <mergeCell ref="D52:N52"/>
-    <mergeCell ref="D77:N77"/>
+    <mergeCell ref="H92:N92"/>
+    <mergeCell ref="D86:N86"/>
     <mergeCell ref="D11:N11"/>
     <mergeCell ref="D49:N49"/>
     <mergeCell ref="D57:N57"/>
-    <mergeCell ref="F93:N93"/>
-    <mergeCell ref="F96:N96"/>
+    <mergeCell ref="H91:N91"/>
+    <mergeCell ref="F102:N102"/>
+    <mergeCell ref="F71:N71"/>
     <mergeCell ref="D13:N13"/>
-    <mergeCell ref="F67:N67"/>
-    <mergeCell ref="D76:N76"/>
+    <mergeCell ref="F105:N105"/>
     <mergeCell ref="E42:N42"/>
     <mergeCell ref="D48:N48"/>
     <mergeCell ref="D17:N17"/>
     <mergeCell ref="D61:N61"/>
-    <mergeCell ref="F92:N92"/>
-    <mergeCell ref="D75:N75"/>
     <mergeCell ref="D53:N53"/>
+    <mergeCell ref="D66:N66"/>
+    <mergeCell ref="H93:N93"/>
     <mergeCell ref="E39:N39"/>
     <mergeCell ref="D16:N16"/>
     <mergeCell ref="D47:N47"/>
     <mergeCell ref="F98:N98"/>
     <mergeCell ref="D7:N7"/>
-    <mergeCell ref="D78:N78"/>
-    <mergeCell ref="H83:N83"/>
     <mergeCell ref="E35:N35"/>
-    <mergeCell ref="F88:N88"/>
-    <mergeCell ref="F64:N64"/>
     <mergeCell ref="E38:N38"/>
+    <mergeCell ref="D62:N62"/>
     <mergeCell ref="A32:N32"/>
+    <mergeCell ref="F73:N73"/>
     <mergeCell ref="D18:N18"/>
     <mergeCell ref="D56:N56"/>
-    <mergeCell ref="F69:N69"/>
+    <mergeCell ref="H89:N89"/>
     <mergeCell ref="D9:N9"/>
     <mergeCell ref="D12:N12"/>
     <mergeCell ref="D58:N58"/>
     <mergeCell ref="D8:N8"/>
-    <mergeCell ref="F68:N68"/>
-    <mergeCell ref="F65:N65"/>
-    <mergeCell ref="D74:N74"/>
-    <mergeCell ref="H85:N85"/>
+    <mergeCell ref="D83:N83"/>
+    <mergeCell ref="F103:N103"/>
+    <mergeCell ref="D64:N64"/>
+    <mergeCell ref="D15:N15"/>
+    <mergeCell ref="D82:N82"/>
     <mergeCell ref="F99:N99"/>
-    <mergeCell ref="D15:N15"/>
-    <mergeCell ref="F89:N89"/>
+    <mergeCell ref="D67:N67"/>
     <mergeCell ref="D5:N5"/>
     <mergeCell ref="D51:N51"/>
+    <mergeCell ref="F74:N74"/>
     <mergeCell ref="D14:N14"/>
+    <mergeCell ref="D85:N85"/>
+    <mergeCell ref="H90:N90"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="B96:D96" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B102:D102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"AWS,Azure,Local partner,Customer"</formula1>
     </dataValidation>
-    <dataValidation sqref="B97:D97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B103:D103" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10243,19 +10435,19 @@
         </is>
       </c>
       <c r="D5" s="27">
-        <f>ROUND(Inputs!B84*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!B90*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="E5" s="27">
-        <f>ROUND(Inputs!C84*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!C90*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="F5" s="27">
-        <f>ROUND(Inputs!D84*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!D90*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="G5" s="27">
-        <f>ROUND(Inputs!E84*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!E90*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="H5" s="24">
@@ -10263,7 +10455,7 @@
         <v/>
       </c>
       <c r="I5" s="24">
-        <f>ROUND(Inputs!G84*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!G90*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="J5" s="20">
@@ -10300,19 +10492,19 @@
         </is>
       </c>
       <c r="D6" s="27">
-        <f>ROUND(Inputs!B85*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!B91*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="E6" s="27">
-        <f>ROUND(Inputs!C85*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!C91*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="F6" s="27">
-        <f>ROUND(Inputs!D85*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!D91*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="G6" s="27">
-        <f>ROUND(Inputs!E85*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!E91*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="H6" s="24">
@@ -10320,7 +10512,7 @@
         <v/>
       </c>
       <c r="I6" s="24">
-        <f>ROUND(Inputs!G85*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!G91*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="J6" s="20">
@@ -10353,19 +10545,19 @@
         </is>
       </c>
       <c r="D7" s="27">
-        <f>ROUND(Inputs!B86*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!B92*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="E7" s="27">
-        <f>ROUND(Inputs!C86*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!C92*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="F7" s="27">
-        <f>ROUND(Inputs!D86*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!D92*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="G7" s="27">
-        <f>ROUND(Inputs!E86*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!E92*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="H7" s="24">
@@ -10373,7 +10565,7 @@
         <v/>
       </c>
       <c r="I7" s="24">
-        <f>ROUND(Inputs!G86*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!G92*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="J7" s="20">
@@ -10406,19 +10598,19 @@
         </is>
       </c>
       <c r="D8" s="27">
-        <f>ROUND(Inputs!B87*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!B93*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="E8" s="27">
-        <f>ROUND(Inputs!C87*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!C93*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="F8" s="27">
-        <f>ROUND(Inputs!D87*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!D93*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="G8" s="27">
-        <f>ROUND(Inputs!E87*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!E93*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="H8" s="24">
@@ -10426,7 +10618,7 @@
         <v/>
       </c>
       <c r="I8" s="24">
-        <f>ROUND(Inputs!G87*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!G93*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="J8" s="20">
@@ -10459,19 +10651,19 @@
         </is>
       </c>
       <c r="D9" s="27">
-        <f>ROUND(Inputs!B84*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!B90*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="E9" s="27">
-        <f>ROUND(Inputs!C84*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!C90*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="F9" s="27">
-        <f>ROUND(Inputs!D84*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!D90*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="G9" s="27">
-        <f>ROUND(Inputs!E84*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!E90*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="H9" s="24">
@@ -10479,7 +10671,7 @@
         <v/>
       </c>
       <c r="I9" s="24">
-        <f>ROUND(Inputs!G84*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!G90*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="J9" s="20">
@@ -10516,19 +10708,19 @@
         </is>
       </c>
       <c r="D10" s="27">
-        <f>ROUND(Inputs!B85*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!B91*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="E10" s="27">
-        <f>ROUND(Inputs!C85*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!C91*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="F10" s="27">
-        <f>ROUND(Inputs!D85*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!D91*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="G10" s="27">
-        <f>ROUND(Inputs!E85*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!E91*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="H10" s="24">
@@ -10536,7 +10728,7 @@
         <v/>
       </c>
       <c r="I10" s="24">
-        <f>ROUND(Inputs!G85*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!G91*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="J10" s="20">
@@ -10569,19 +10761,19 @@
         </is>
       </c>
       <c r="D11" s="27">
-        <f>ROUND(Inputs!B86*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!B92*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="E11" s="27">
-        <f>ROUND(Inputs!C86*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!C92*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="F11" s="27">
-        <f>ROUND(Inputs!D86*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!D92*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="G11" s="27">
-        <f>ROUND(Inputs!E86*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!E92*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="H11" s="24">
@@ -10589,7 +10781,7 @@
         <v/>
       </c>
       <c r="I11" s="24">
-        <f>ROUND(Inputs!G86*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!G92*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="J11" s="20">
@@ -10622,19 +10814,19 @@
         </is>
       </c>
       <c r="D12" s="27">
-        <f>ROUND(Inputs!B87*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!B93*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="E12" s="27">
-        <f>ROUND(Inputs!C87*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!C93*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="F12" s="27">
-        <f>ROUND(Inputs!D87*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!D93*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="G12" s="27">
-        <f>ROUND(Inputs!E87*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!E93*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="H12" s="24">
@@ -10642,7 +10834,7 @@
         <v/>
       </c>
       <c r="I12" s="24">
-        <f>ROUND(Inputs!G87*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!G93*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="J12" s="20">
@@ -10675,19 +10867,19 @@
         </is>
       </c>
       <c r="D13" s="27">
-        <f>ROUND(Inputs!B84*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!B90*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="E13" s="27">
-        <f>ROUND(Inputs!C84*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!C90*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="F13" s="27">
-        <f>ROUND(Inputs!D84*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!D90*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="G13" s="27">
-        <f>ROUND(Inputs!E84*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!E90*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="H13" s="24">
@@ -10695,7 +10887,7 @@
         <v/>
       </c>
       <c r="I13" s="24">
-        <f>ROUND(Inputs!G84*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!G90*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="J13" s="20">
@@ -10732,19 +10924,19 @@
         </is>
       </c>
       <c r="D14" s="27">
-        <f>ROUND(Inputs!B85*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!B91*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="E14" s="27">
-        <f>ROUND(Inputs!C85*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!C91*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="F14" s="27">
-        <f>ROUND(Inputs!D85*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!D91*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="G14" s="27">
-        <f>ROUND(Inputs!E85*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!E91*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="H14" s="24">
@@ -10752,7 +10944,7 @@
         <v/>
       </c>
       <c r="I14" s="24">
-        <f>ROUND(Inputs!G85*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!G91*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="J14" s="20">
@@ -10785,19 +10977,19 @@
         </is>
       </c>
       <c r="D15" s="27">
-        <f>ROUND(Inputs!B86*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!B92*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="E15" s="27">
-        <f>ROUND(Inputs!C86*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!C92*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="F15" s="27">
-        <f>ROUND(Inputs!D86*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!D92*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="G15" s="27">
-        <f>ROUND(Inputs!E86*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!E92*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="H15" s="24">
@@ -10805,7 +10997,7 @@
         <v/>
       </c>
       <c r="I15" s="24">
-        <f>ROUND(Inputs!G86*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!G92*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="J15" s="20">
@@ -10838,19 +11030,19 @@
         </is>
       </c>
       <c r="D16" s="27">
-        <f>ROUND(Inputs!B87*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!B93*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="E16" s="27">
-        <f>ROUND(Inputs!C87*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!C93*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="F16" s="27">
-        <f>ROUND(Inputs!D87*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!D93*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="G16" s="27">
-        <f>ROUND(Inputs!E87*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!E93*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="H16" s="24">
@@ -10858,7 +11050,7 @@
         <v/>
       </c>
       <c r="I16" s="24">
-        <f>ROUND(Inputs!G87*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!G93*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="J16" s="20">
@@ -11921,7 +12113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -12175,16 +12367,16 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Additional line of business after go-live</t>
+          <t>Connector go-live with a partner</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>per line</t>
+          <t>per connector</t>
         </is>
       </c>
       <c r="C12" s="34">
-        <f>ROUND(Days_per_LOB*Blended/Round_To,0)*Round_To</f>
+        <f>ROUND(Conn_Golive_Days*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="D12" s="20">
@@ -12192,28 +12384,28 @@
         <v/>
       </c>
       <c r="E12" s="25">
-        <f>Days_per_LOB</f>
+        <f>Conn_Golive_Days</f>
         <v/>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Product set-up, rating and tax lines, templates, testing.</t>
+          <t>To confirm by management. A delivered connector (SMS gateway, CTPL provider, one insurer, one bank file layout, BIR EIS) taken live; the partner certifies its own side.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>New report or document template</t>
+          <t>Activation of the AML/CFT toolkit</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>per item (typical)</t>
+          <t>one-time</t>
         </is>
       </c>
       <c r="C13" s="34">
-        <f>ROUND(Report_Days*Blended/Round_To,0)*Round_To</f>
+        <f>ROUND(AML_Act_Days*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="D13" s="20">
@@ -12221,171 +12413,353 @@
         <v/>
       </c>
       <c r="E13" s="25">
-        <f>Report_Days</f>
+        <f>AML_Act_Days</f>
         <v/>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Small CR band; firm price after the impact note.</t>
+          <t>To confirm by management. The toolkit is included in the software; this is the set-up effort. The compliance officer confirms the settings and loads the lists.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>On-site day (Metro Manila)</t>
+          <t>Activation of the IC compliance registers</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>per consultant day</t>
+          <t>one-time</t>
         </is>
       </c>
       <c r="C14" s="34">
-        <f>Rate_Onsite</f>
+        <f>ROUND(IC_Act_Days*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="D14" s="20">
         <f>C14/FX</f>
         <v/>
       </c>
-      <c r="E14" s="25" t="inlineStr"/>
+      <c r="E14" s="25">
+        <f>IC_Act_Days</f>
+        <v/>
+      </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Outside Metro Manila: travel, lodging and meals at cost.</t>
+          <t>To confirm by management. Registers included in the software; this is the set-up effort.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="10">
-        <f>"24x7 Severity 1 support, "&amp;Inputs!A28&amp;" tier"</f>
-        <v/>
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Activation of the BIR pack</t>
+        </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>per year, Year 1</t>
+          <t>one-time</t>
         </is>
       </c>
       <c r="C15" s="34">
-        <f>Inputs!L28</f>
+        <f>ROUND(BIR_Act_Days*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="D15" s="20">
         <f>C15/FX</f>
         <v/>
       </c>
+      <c r="E15" s="25">
+        <f>BIR_Act_Days</f>
+        <v/>
+      </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Standard support is business hours (Monday to Friday, 08:00 to 18:00 Philippine time, excluding holidays). This adds round-the-clock response to Severity 1 incidents (production down or a core process stopped for all users).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="10">
-        <f>"24x7 Severity 1 support, "&amp;Inputs!A29&amp;" tier"</f>
-        <v/>
+          <t>To confirm by management. BIR forms, EOPT invoices, EIS and CAS pack included in the software; the tax adviser confirms the treatment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Dealer programme set-up</t>
+        </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>per year, Year 1</t>
+          <t>per programme</t>
         </is>
       </c>
       <c r="C16" s="34">
-        <f>Inputs!L29</f>
+        <f>ROUND(Dealer_Prog_Days*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="D16" s="20">
         <f>C16/FX</f>
         <v/>
       </c>
-      <c r="F16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="10">
-        <f>"24x7 Severity 1 support, "&amp;Inputs!A30&amp;" tier"</f>
-        <v/>
+      <c r="E16" s="25">
+        <f>Dealer_Prog_Days</f>
+        <v/>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>To confirm by management. Dealer programmes are included in the software; this is the set-up of one programme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Client brand pack</t>
+        </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>per year, Year 1</t>
+          <t>per pack</t>
         </is>
       </c>
       <c r="C17" s="34">
-        <f>Inputs!L30</f>
+        <f>ROUND(Brand_Pack_Days*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="D17" s="20">
         <f>C17/FX</f>
         <v/>
       </c>
-      <c r="F17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="10">
-        <f>"24x7 Severity 1 support, "&amp;Inputs!A31&amp;" tier"</f>
-        <v/>
+      <c r="E17" s="25">
+        <f>Brand_Pack_Days</f>
+        <v/>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>To confirm by management. Branding is included in the software; a pack carrying third-party marks needs the owner's written permission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Additional line of business after go-live</t>
+        </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>per year, Year 1</t>
+          <t>per line</t>
         </is>
       </c>
       <c r="C18" s="34">
-        <f>Inputs!L31</f>
+        <f>ROUND(Days_per_LOB*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="D18" s="20">
         <f>C18/FX</f>
         <v/>
       </c>
-      <c r="F18" s="5" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="E18" s="25">
+        <f>Days_per_LOB</f>
+        <v/>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Product set-up, rating and tax lines, templates, testing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>New report or document template</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>per item (typical)</t>
+        </is>
+      </c>
+      <c r="C19" s="34">
+        <f>ROUND(Report_Days*Blended/Round_To,0)*Round_To</f>
+        <v/>
+      </c>
+      <c r="D19" s="20">
+        <f>C19/FX</f>
+        <v/>
+      </c>
+      <c r="E19" s="25">
+        <f>Report_Days</f>
+        <v/>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Small CR band; firm price after the impact note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>On-site day (Metro Manila)</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>per consultant day</t>
+        </is>
+      </c>
+      <c r="C20" s="34">
+        <f>Rate_Onsite</f>
+        <v/>
+      </c>
+      <c r="D20" s="20">
+        <f>C20/FX</f>
+        <v/>
+      </c>
+      <c r="E20" s="25" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Outside Metro Manila: travel, lodging and meals at cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="10">
+        <f>"24x7 Severity 1 support, "&amp;Inputs!A28&amp;" tier"</f>
+        <v/>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>per year, Year 1</t>
+        </is>
+      </c>
+      <c r="C21" s="34">
+        <f>Inputs!L28</f>
+        <v/>
+      </c>
+      <c r="D21" s="20">
+        <f>C21/FX</f>
+        <v/>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Standard support is business hours (Monday to Friday, 08:00 to 18:00 Philippine time, excluding holidays). This adds round-the-clock response to Severity 1 incidents (production down or a core process stopped for all users).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="10">
+        <f>"24x7 Severity 1 support, "&amp;Inputs!A29&amp;" tier"</f>
+        <v/>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>per year, Year 1</t>
+        </is>
+      </c>
+      <c r="C22" s="34">
+        <f>Inputs!L29</f>
+        <v/>
+      </c>
+      <c r="D22" s="20">
+        <f>C22/FX</f>
+        <v/>
+      </c>
+      <c r="F22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="10">
+        <f>"24x7 Severity 1 support, "&amp;Inputs!A30&amp;" tier"</f>
+        <v/>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>per year, Year 1</t>
+        </is>
+      </c>
+      <c r="C23" s="34">
+        <f>Inputs!L30</f>
+        <v/>
+      </c>
+      <c r="D23" s="20">
+        <f>C23/FX</f>
+        <v/>
+      </c>
+      <c r="F23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="10">
+        <f>"24x7 Severity 1 support, "&amp;Inputs!A31&amp;" tier"</f>
+        <v/>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>per year, Year 1</t>
+        </is>
+      </c>
+      <c r="C24" s="34">
+        <f>Inputs!L31</f>
+        <v/>
+      </c>
+      <c r="D24" s="20">
+        <f>C24/FX</f>
+        <v/>
+      </c>
+      <c r="F24" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Included in the standard implementation (no extra charge)</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>Configuration of the company, branches, users and roles, insurers, commission rates, chart of accounts, banks and the included lines of business.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="26" t="inlineStr">
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>Data load using the standard upload templates (about 50 templates in docs/package/05_Delivery/Upload_Templates), with the broker supplying clean data.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="26" t="inlineStr">
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t>Training days included for the tier (train-the-trainer), UAT support, go-live support and 4 weeks of hypercare.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="26" t="inlineStr">
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>Set-up of the environment set of the tier (Dev, UAT and Production; SIT as well for Large and Enterprise) and of Pre-Prod for the go-live rehearsal; hosting is billed separately. Deployment guidance when the broker hosts.</t>
         </is>
       </c>
     </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t>Every module is included in the software price, including the AML/CFT toolkit, the IC compliance registers, the BIR pack, the integration framework with its connectors, dealer programmes and branding. Their activation and each connector go-live are the optional lines above (to confirm by management).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A23:F23"/>
+  <mergeCells count="5">
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A29:F29"/>
   </mergeCells>
   <printOptions gridLines="0"/>
   <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12436,7 +12810,7 @@
     </row>
     <row r="4">
       <c r="A4" s="6">
-        <f>"Example 1: "&amp;Inputs!$B$93&amp;", "&amp;Inputs!$B$94&amp;" users, "&amp;Inputs!$B$95&amp;" lines of business, tier "&amp;INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))&amp;", hosting: "&amp;Inputs!$B$96</f>
+        <f>"Example 1: "&amp;Inputs!$B$99&amp;", "&amp;Inputs!$B$100&amp;" users, "&amp;Inputs!$B$101&amp;" lines of business, tier "&amp;INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))&amp;", hosting: "&amp;Inputs!$B$102</f>
         <v/>
       </c>
       <c r="B4" s="7" t="n"/>
@@ -12503,7 +12877,7 @@
         </is>
       </c>
       <c r="B7" s="20">
-        <f>ROUND((INDEX(Inputs!$G$28:$G$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))+MAX(0,Inputs!$B$95-INDEX(Inputs!$H$28:$H$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1)))*Days_per_LOB)*Blended/Round_To,0)*Round_To</f>
+        <f>ROUND((INDEX(Inputs!$G$28:$G$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))+MAX(0,Inputs!$B$101-INDEX(Inputs!$H$28:$H$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1)))*Days_per_LOB)*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="C7" s="20" t="n">
@@ -12534,7 +12908,7 @@
         </is>
       </c>
       <c r="B8" s="20">
-        <f>MAX(0,MIN(Inputs!$B$94,Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$D$28+MAX(0,MIN(Inputs!$B$94,Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$D$29+MAX(0,MIN(Inputs!$B$94,Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$D$30+MAX(0,MIN(Inputs!$B$94,Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$D$31</f>
+        <f>MAX(0,MIN(Inputs!$B$100,Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$D$28+MAX(0,MIN(Inputs!$B$100,Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$D$29+MAX(0,MIN(Inputs!$B$100,Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$D$30+MAX(0,MIN(Inputs!$B$100,Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$D$31</f>
         <v/>
       </c>
       <c r="C8" s="20" t="n">
@@ -12668,27 +13042,27 @@
     </row>
     <row r="13">
       <c r="A13" s="10">
-        <f>"Subscription ("&amp;MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1)))&amp;" billable users)"</f>
+        <f>"Subscription ("&amp;MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1)))&amp;" billable users)"</f>
         <v/>
       </c>
       <c r="B13" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(1-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(1-1)</f>
         <v/>
       </c>
       <c r="C13" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(2-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(2-1)</f>
         <v/>
       </c>
       <c r="D13" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(3-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(3-1)</f>
         <v/>
       </c>
       <c r="E13" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(4-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(4-1)</f>
         <v/>
       </c>
       <c r="F13" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(5-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(5-1)</f>
         <v/>
       </c>
       <c r="G13" s="34">
@@ -12744,27 +13118,27 @@
     </row>
     <row r="16">
       <c r="A16" s="10">
-        <f>"Hosting, environment set and Pre-Prod: "&amp;Inputs!$B$96</f>
+        <f>"Hosting, environment set and Pre-Prod: "&amp;Inputs!$B$102</f>
         <v/>
       </c>
       <c r="B16" s="20">
-        <f>(SUMIFS(Infrastructure!$J$5:$J$20,Infrastructure!$A$5:$A$20,Inputs!$B$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(1-1)</f>
+        <f>(SUMIFS(Infrastructure!$J$5:$J$20,Infrastructure!$A$5:$A$20,Inputs!$B$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(1-1)</f>
         <v/>
       </c>
       <c r="C16" s="20">
-        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$B$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(2-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$B$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(2-1)</f>
         <v/>
       </c>
       <c r="D16" s="20">
-        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$B$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(3-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$B$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(3-1)</f>
         <v/>
       </c>
       <c r="E16" s="20">
-        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$B$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(4-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$B$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(4-1)</f>
         <v/>
       </c>
       <c r="F16" s="20">
-        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$B$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(5-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$B$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(5-1)</f>
         <v/>
       </c>
       <c r="G16" s="34">
@@ -12783,23 +13157,23 @@
         </is>
       </c>
       <c r="B17" s="20">
-        <f>IF(Inputs!$B$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(1-1),0)</f>
+        <f>IF(Inputs!$B$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(1-1),0)</f>
         <v/>
       </c>
       <c r="C17" s="20">
-        <f>IF(Inputs!$B$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(2-1),0)</f>
+        <f>IF(Inputs!$B$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(2-1),0)</f>
         <v/>
       </c>
       <c r="D17" s="20">
-        <f>IF(Inputs!$B$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(3-1),0)</f>
+        <f>IF(Inputs!$B$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(3-1),0)</f>
         <v/>
       </c>
       <c r="E17" s="20">
-        <f>IF(Inputs!$B$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(4-1),0)</f>
+        <f>IF(Inputs!$B$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(4-1),0)</f>
         <v/>
       </c>
       <c r="F17" s="20">
-        <f>IF(Inputs!$B$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(5-1),0)</f>
+        <f>IF(Inputs!$B$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(5-1),0)</f>
         <v/>
       </c>
       <c r="G17" s="34">
@@ -12818,7 +13192,7 @@
         </is>
       </c>
       <c r="B18" s="20">
-        <f>Inputs!$B$98*Rate_Trainer+ROUND(Mig_Days_Source*Blended/Round_To,0)*Round_To*Inputs!$B$99+ROUND(Int_Std_Days*Blended/Round_To,0)*Round_To*Inputs!$B$100</f>
+        <f>Inputs!$B$104*Rate_Trainer+ROUND(Mig_Days_Source*Blended/Round_To,0)*Round_To*Inputs!$B$105+ROUND(Int_Std_Days*Blended/Round_To,0)*Round_To*Inputs!$B$106</f>
         <v/>
       </c>
       <c r="C18" s="20" t="n">
@@ -13060,7 +13434,7 @@
     </row>
     <row r="27">
       <c r="A27" s="6">
-        <f>"Example 2: "&amp;Inputs!$C$93&amp;", "&amp;Inputs!$C$94&amp;" users, "&amp;Inputs!$C$95&amp;" lines of business, tier "&amp;INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))&amp;", hosting: "&amp;Inputs!$C$96</f>
+        <f>"Example 2: "&amp;Inputs!$C$99&amp;", "&amp;Inputs!$C$100&amp;" users, "&amp;Inputs!$C$101&amp;" lines of business, tier "&amp;INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))&amp;", hosting: "&amp;Inputs!$C$102</f>
         <v/>
       </c>
       <c r="B27" s="7" t="n"/>
@@ -13127,7 +13501,7 @@
         </is>
       </c>
       <c r="B30" s="20">
-        <f>ROUND((INDEX(Inputs!$G$28:$G$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))+MAX(0,Inputs!$C$95-INDEX(Inputs!$H$28:$H$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1)))*Days_per_LOB)*Blended/Round_To,0)*Round_To</f>
+        <f>ROUND((INDEX(Inputs!$G$28:$G$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))+MAX(0,Inputs!$C$101-INDEX(Inputs!$H$28:$H$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1)))*Days_per_LOB)*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="C30" s="20" t="n">
@@ -13158,7 +13532,7 @@
         </is>
       </c>
       <c r="B31" s="20">
-        <f>MAX(0,MIN(Inputs!$C$94,Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$D$28+MAX(0,MIN(Inputs!$C$94,Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$D$29+MAX(0,MIN(Inputs!$C$94,Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$D$30+MAX(0,MIN(Inputs!$C$94,Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$D$31</f>
+        <f>MAX(0,MIN(Inputs!$C$100,Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$D$28+MAX(0,MIN(Inputs!$C$100,Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$D$29+MAX(0,MIN(Inputs!$C$100,Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$D$30+MAX(0,MIN(Inputs!$C$100,Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$D$31</f>
         <v/>
       </c>
       <c r="C31" s="20" t="n">
@@ -13292,27 +13666,27 @@
     </row>
     <row r="36">
       <c r="A36" s="10">
-        <f>"Subscription ("&amp;MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1)))&amp;" billable users)"</f>
+        <f>"Subscription ("&amp;MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1)))&amp;" billable users)"</f>
         <v/>
       </c>
       <c r="B36" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(1-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(1-1)</f>
         <v/>
       </c>
       <c r="C36" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(2-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(2-1)</f>
         <v/>
       </c>
       <c r="D36" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(3-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(3-1)</f>
         <v/>
       </c>
       <c r="E36" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(4-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(4-1)</f>
         <v/>
       </c>
       <c r="F36" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(5-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(5-1)</f>
         <v/>
       </c>
       <c r="G36" s="34">
@@ -13368,27 +13742,27 @@
     </row>
     <row r="39">
       <c r="A39" s="10">
-        <f>"Hosting, environment set and Pre-Prod: "&amp;Inputs!$C$96</f>
+        <f>"Hosting, environment set and Pre-Prod: "&amp;Inputs!$C$102</f>
         <v/>
       </c>
       <c r="B39" s="20">
-        <f>(SUMIFS(Infrastructure!$J$5:$J$20,Infrastructure!$A$5:$A$20,Inputs!$C$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(1-1)</f>
+        <f>(SUMIFS(Infrastructure!$J$5:$J$20,Infrastructure!$A$5:$A$20,Inputs!$C$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(1-1)</f>
         <v/>
       </c>
       <c r="C39" s="20">
-        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$C$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(2-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$C$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(2-1)</f>
         <v/>
       </c>
       <c r="D39" s="20">
-        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$C$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(3-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$C$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(3-1)</f>
         <v/>
       </c>
       <c r="E39" s="20">
-        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$C$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(4-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$C$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(4-1)</f>
         <v/>
       </c>
       <c r="F39" s="20">
-        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$C$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(5-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$C$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(5-1)</f>
         <v/>
       </c>
       <c r="G39" s="34">
@@ -13407,23 +13781,23 @@
         </is>
       </c>
       <c r="B40" s="20">
-        <f>IF(Inputs!$C$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(1-1),0)</f>
+        <f>IF(Inputs!$C$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(1-1),0)</f>
         <v/>
       </c>
       <c r="C40" s="20">
-        <f>IF(Inputs!$C$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(2-1),0)</f>
+        <f>IF(Inputs!$C$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(2-1),0)</f>
         <v/>
       </c>
       <c r="D40" s="20">
-        <f>IF(Inputs!$C$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(3-1),0)</f>
+        <f>IF(Inputs!$C$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(3-1),0)</f>
         <v/>
       </c>
       <c r="E40" s="20">
-        <f>IF(Inputs!$C$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(4-1),0)</f>
+        <f>IF(Inputs!$C$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(4-1),0)</f>
         <v/>
       </c>
       <c r="F40" s="20">
-        <f>IF(Inputs!$C$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(5-1),0)</f>
+        <f>IF(Inputs!$C$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(5-1),0)</f>
         <v/>
       </c>
       <c r="G40" s="34">
@@ -13442,7 +13816,7 @@
         </is>
       </c>
       <c r="B41" s="20">
-        <f>Inputs!$C$98*Rate_Trainer+ROUND(Mig_Days_Source*Blended/Round_To,0)*Round_To*Inputs!$C$99+ROUND(Int_Std_Days*Blended/Round_To,0)*Round_To*Inputs!$C$100</f>
+        <f>Inputs!$C$104*Rate_Trainer+ROUND(Mig_Days_Source*Blended/Round_To,0)*Round_To*Inputs!$C$105+ROUND(Int_Std_Days*Blended/Round_To,0)*Round_To*Inputs!$C$106</f>
         <v/>
       </c>
       <c r="C41" s="20" t="n">
@@ -13684,7 +14058,7 @@
     </row>
     <row r="50">
       <c r="A50" s="6">
-        <f>"Example 3: "&amp;Inputs!$D$93&amp;", "&amp;Inputs!$D$94&amp;" users, "&amp;Inputs!$D$95&amp;" lines of business, tier "&amp;INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))&amp;", hosting: "&amp;Inputs!$D$96</f>
+        <f>"Example 3: "&amp;Inputs!$D$99&amp;", "&amp;Inputs!$D$100&amp;" users, "&amp;Inputs!$D$101&amp;" lines of business, tier "&amp;INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))&amp;", hosting: "&amp;Inputs!$D$102</f>
         <v/>
       </c>
       <c r="B50" s="7" t="n"/>
@@ -13751,7 +14125,7 @@
         </is>
       </c>
       <c r="B53" s="20">
-        <f>ROUND((INDEX(Inputs!$G$28:$G$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))+MAX(0,Inputs!$D$95-INDEX(Inputs!$H$28:$H$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1)))*Days_per_LOB)*Blended/Round_To,0)*Round_To</f>
+        <f>ROUND((INDEX(Inputs!$G$28:$G$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))+MAX(0,Inputs!$D$101-INDEX(Inputs!$H$28:$H$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1)))*Days_per_LOB)*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="C53" s="20" t="n">
@@ -13782,7 +14156,7 @@
         </is>
       </c>
       <c r="B54" s="20">
-        <f>MAX(0,MIN(Inputs!$D$94,Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$D$28+MAX(0,MIN(Inputs!$D$94,Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$D$29+MAX(0,MIN(Inputs!$D$94,Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$D$30+MAX(0,MIN(Inputs!$D$94,Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$D$31</f>
+        <f>MAX(0,MIN(Inputs!$D$100,Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$D$28+MAX(0,MIN(Inputs!$D$100,Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$D$29+MAX(0,MIN(Inputs!$D$100,Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$D$30+MAX(0,MIN(Inputs!$D$100,Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$D$31</f>
         <v/>
       </c>
       <c r="C54" s="20" t="n">
@@ -13916,27 +14290,27 @@
     </row>
     <row r="59">
       <c r="A59" s="10">
-        <f>"Subscription ("&amp;MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1)))&amp;" billable users)"</f>
+        <f>"Subscription ("&amp;MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1)))&amp;" billable users)"</f>
         <v/>
       </c>
       <c r="B59" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(1-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(1-1)</f>
         <v/>
       </c>
       <c r="C59" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(2-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(2-1)</f>
         <v/>
       </c>
       <c r="D59" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(3-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(3-1)</f>
         <v/>
       </c>
       <c r="E59" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(4-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(4-1)</f>
         <v/>
       </c>
       <c r="F59" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$94,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(5-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(5-1)</f>
         <v/>
       </c>
       <c r="G59" s="34">
@@ -13992,27 +14366,27 @@
     </row>
     <row r="62">
       <c r="A62" s="10">
-        <f>"Hosting, environment set and Pre-Prod: "&amp;Inputs!$D$96</f>
+        <f>"Hosting, environment set and Pre-Prod: "&amp;Inputs!$D$102</f>
         <v/>
       </c>
       <c r="B62" s="20">
-        <f>(SUMIFS(Infrastructure!$J$5:$J$20,Infrastructure!$A$5:$A$20,Inputs!$D$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(1-1)</f>
+        <f>(SUMIFS(Infrastructure!$J$5:$J$20,Infrastructure!$A$5:$A$20,Inputs!$D$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(1-1)</f>
         <v/>
       </c>
       <c r="C62" s="20">
-        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$D$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(2-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$D$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(2-1)</f>
         <v/>
       </c>
       <c r="D62" s="20">
-        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$D$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(3-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$D$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(3-1)</f>
         <v/>
       </c>
       <c r="E62" s="20">
-        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$D$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(4-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$D$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(4-1)</f>
         <v/>
       </c>
       <c r="F62" s="20">
-        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$D$96,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(5-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$D$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(5-1)</f>
         <v/>
       </c>
       <c r="G62" s="34">
@@ -14031,23 +14405,23 @@
         </is>
       </c>
       <c r="B63" s="20">
-        <f>IF(Inputs!$D$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(1-1),0)</f>
+        <f>IF(Inputs!$D$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(1-1),0)</f>
         <v/>
       </c>
       <c r="C63" s="20">
-        <f>IF(Inputs!$D$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(2-1),0)</f>
+        <f>IF(Inputs!$D$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(2-1),0)</f>
         <v/>
       </c>
       <c r="D63" s="20">
-        <f>IF(Inputs!$D$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(3-1),0)</f>
+        <f>IF(Inputs!$D$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(3-1),0)</f>
         <v/>
       </c>
       <c r="E63" s="20">
-        <f>IF(Inputs!$D$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(4-1),0)</f>
+        <f>IF(Inputs!$D$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(4-1),0)</f>
         <v/>
       </c>
       <c r="F63" s="20">
-        <f>IF(Inputs!$D$97="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$94,Inputs!$B$28:$B$31,1))*(1+Esc)^(5-1),0)</f>
+        <f>IF(Inputs!$D$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(5-1),0)</f>
         <v/>
       </c>
       <c r="G63" s="34">
@@ -14066,7 +14440,7 @@
         </is>
       </c>
       <c r="B64" s="20">
-        <f>Inputs!$D$98*Rate_Trainer+ROUND(Mig_Days_Source*Blended/Round_To,0)*Round_To*Inputs!$D$99+ROUND(Int_Std_Days*Blended/Round_To,0)*Round_To*Inputs!$D$100</f>
+        <f>Inputs!$D$104*Rate_Trainer+ROUND(Mig_Days_Source*Blended/Round_To,0)*Round_To*Inputs!$D$105+ROUND(Int_Std_Days*Blended/Round_To,0)*Round_To*Inputs!$D$106</f>
         <v/>
       </c>
       <c r="C64" s="20" t="n">

--- a/docs/package/02_Commercials/BrokerVerse_Commercials_and_Pricing.xlsx
+++ b/docs/package/02_Commercials/BrokerVerse_Commercials_and_Pricing.xlsx
@@ -62,14 +62,24 @@
     <definedName name="BIR_Act_Days">Inputs!$B$65</definedName>
     <definedName name="Dealer_Prog_Days">Inputs!$B$66</definedName>
     <definedName name="Brand_Pack_Days">Inputs!$B$67</definedName>
-    <definedName name="NP_Small_USD">Inputs!$B$81</definedName>
-    <definedName name="NP_Med_USD">Inputs!$B$82</definedName>
-    <definedName name="PreProd_Factor">Inputs!$B$83</definedName>
-    <definedName name="PreProd_GoLive_Months">Inputs!$B$84</definedName>
-    <definedName name="PreProd_Rel_Months">Inputs!$B$85</definedName>
-    <definedName name="Major_Rel_Year">Inputs!$B$86</definedName>
-    <definedName name="Azure_Factor">Inputs!$B$94</definedName>
-    <definedName name="Local_Factor">Inputs!$B$95</definedName>
+    <definedName name="AMLC_Val_Days">Inputs!$B$68</definedName>
+    <definedName name="IC_Form_Days">Inputs!$B$69</definedName>
+    <definedName name="EOPT_Rev_Days">Inputs!$B$70</definedName>
+    <definedName name="CAS_Reg_Days">Inputs!$B$71</definedName>
+    <definedName name="EIS_Enrol_Days">Inputs!$B$72</definedName>
+    <definedName name="CTPL_Cert_Days">Inputs!$B$73</definedName>
+    <definedName name="Insurer_Onb_Days">Inputs!$B$74</definedName>
+    <definedName name="Bank_Cert_Days">Inputs!$B$75</definedName>
+    <definedName name="SMS_Act_Days">Inputs!$B$76</definedName>
+    <definedName name="Screen_Prov_Days">Inputs!$B$77</definedName>
+    <definedName name="NP_Small_USD">Inputs!$B$91</definedName>
+    <definedName name="NP_Med_USD">Inputs!$B$92</definedName>
+    <definedName name="PreProd_Factor">Inputs!$B$93</definedName>
+    <definedName name="PreProd_GoLive_Months">Inputs!$B$94</definedName>
+    <definedName name="PreProd_Rel_Months">Inputs!$B$95</definedName>
+    <definedName name="Major_Rel_Year">Inputs!$B$96</definedName>
+    <definedName name="Azure_Factor">Inputs!$B$104</definedName>
+    <definedName name="Local_Factor">Inputs!$B$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -661,7 +671,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>iorta TechNXT. Prepared 03 October 2026. Prices in PHP, exclusive of 12% VAT. For discussion with prospective broker customers.</t>
+          <t>iorta TechNXT. Prepared 03 October 2026, revised 04 October 2026 (optional modules and partner services confirmed). Prices in PHP, exclusive of 12% VAT. For discussion with prospective broker customers.</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N106"/>
+  <dimension ref="A1:N116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4867,7 +4877,7 @@
     <row r="62">
       <c r="A62" s="10" t="inlineStr">
         <is>
-          <t>Go-live of a delivered connector with one partner (to confirm by management)</t>
+          <t>Go-live of a delivered connector with one partner</t>
         </is>
       </c>
       <c r="B62" s="14" t="n">
@@ -4880,7 +4890,7 @@
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>Assumption: SMS gateway, CTPL provider, one insurer API mapping, one bank file layout or the BIR EIS: configuration, credentials check, live test, support of the partner acceptance. To confirm by management.</t>
+          <t>Estimate: SMS gateway, CTPL provider, one insurer API mapping, one bank file layout or the BIR EIS: configuration, credentials check, live test, support of the partner acceptance. Optional service confirmed by management on 04 October 2026.</t>
         </is>
       </c>
       <c r="E62" s="8" t="n"/>
@@ -4897,7 +4907,7 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>Activation of the AML/CFT toolkit (to confirm by management)</t>
+          <t>Activation of the AML/CFT toolkit</t>
         </is>
       </c>
       <c r="B63" s="14" t="n">
@@ -4910,7 +4920,7 @@
       </c>
       <c r="D63" s="15" t="inlineStr">
         <is>
-          <t>Assumption: risk factors and rules workshop with the compliance officer, settings, first list loads, provider set-up, AMLC test file. To confirm by management.</t>
+          <t>Estimate: risk factors and rules workshop with the compliance officer, settings, first list loads, provider set-up, AMLC test file. Optional service confirmed by management on 04 October 2026.</t>
         </is>
       </c>
       <c r="E63" s="8" t="n"/>
@@ -4927,7 +4937,7 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>Activation of the IC compliance registers (to confirm by management)</t>
+          <t>Activation of the IC compliance registers</t>
         </is>
       </c>
       <c r="B64" s="14" t="n">
@@ -4940,7 +4950,7 @@
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>Assumption: licence and fit and proper register load, insurer certificates, complaints and breach settings, IC statement account mapping to the broker chart. To confirm by management.</t>
+          <t>Estimate: licence and fit and proper register load, insurer certificates, complaints and breach settings, IC statement account mapping to the broker chart. Optional service confirmed by management on 04 October 2026.</t>
         </is>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -4957,7 +4967,7 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>Activation of the BIR pack (to confirm by management)</t>
+          <t>Activation of the BIR pack</t>
         </is>
       </c>
       <c r="B65" s="14" t="n">
@@ -4970,7 +4980,7 @@
       </c>
       <c r="D65" s="15" t="inlineStr">
         <is>
-          <t>Assumption: BIR and EOPT invoice settings with the tax adviser, ATC mapping, DAT file dry run, CAS books pack. To confirm by management.</t>
+          <t>Estimate: BIR and EOPT invoice settings with the tax adviser, ATC mapping, DAT file dry run, CAS books pack. Optional service confirmed by management on 04 October 2026.</t>
         </is>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -4987,7 +4997,7 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>Set-up of one dealer programme (to confirm by management)</t>
+          <t>Set-up of one dealer programme</t>
         </is>
       </c>
       <c r="B66" s="14" t="n">
@@ -5000,7 +5010,7 @@
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>Assumption: channels, rates, subsidy, bank letter and the first upload. To confirm by management.</t>
+          <t>Estimate: channels, rates, subsidy, bank letter and the first upload. Optional service confirmed by management on 04 October 2026.</t>
         </is>
       </c>
       <c r="E66" s="8" t="n"/>
@@ -5017,7 +5027,7 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>Client brand pack (to confirm by management)</t>
+          <t>Client brand pack</t>
         </is>
       </c>
       <c r="B67" s="14" t="n">
@@ -5030,7 +5040,7 @@
       </c>
       <c r="D67" s="15" t="inlineStr">
         <is>
-          <t>Assumption: theme, sign-in picture, document and e-mail branding, e-signature mapping, exported pack. To confirm by management.</t>
+          <t>Estimate: theme, sign-in picture, document and e-mail branding, e-signature mapping, exported pack. Optional service confirmed by management on 04 October 2026.</t>
         </is>
       </c>
       <c r="E67" s="8" t="n"/>
@@ -5044,57 +5054,87 @@
       <c r="M67" s="8" t="n"/>
       <c r="N67" s="9" t="n"/>
     </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>AMLC reporting file validation and portal test</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="D68" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: CTR and STR layout, institution and transaction codes confirmed with the AMLC, test file accepted in the AMLC portal. Optional service confirmed by management on 04 October 2026.</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="n"/>
+      <c r="F68" s="8" t="n"/>
+      <c r="G68" s="8" t="n"/>
+      <c r="H68" s="8" t="n"/>
+      <c r="I68" s="8" t="n"/>
+      <c r="J68" s="8" t="n"/>
+      <c r="K68" s="8" t="n"/>
+      <c r="L68" s="8" t="n"/>
+      <c r="M68" s="8" t="n"/>
+      <c r="N68" s="9" t="n"/>
+    </row>
     <row r="69">
-      <c r="A69" s="6" t="inlineStr">
-        <is>
-          <t>Infrastructure: AWS reference cost per month of the Production environment (USD)</t>
-        </is>
-      </c>
-      <c r="B69" s="7" t="n"/>
-      <c r="C69" s="7" t="n"/>
-      <c r="D69" s="7" t="n"/>
-      <c r="E69" s="7" t="n"/>
-      <c r="F69" s="7" t="n"/>
-      <c r="G69" s="7" t="n"/>
-      <c r="H69" s="7" t="n"/>
-      <c r="I69" s="7" t="n"/>
-      <c r="J69" s="7" t="n"/>
-      <c r="K69" s="7" t="n"/>
-      <c r="L69" s="7" t="n"/>
-      <c r="M69" s="7" t="n"/>
-      <c r="N69" s="7" t="n"/>
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>IC annual statement form alignment</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="D69" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: the accountant working paper mapped to the IC form set in force for the year. Optional service confirmed by management on 04 October 2026.</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="n"/>
+      <c r="F69" s="8" t="n"/>
+      <c r="G69" s="8" t="n"/>
+      <c r="H69" s="8" t="n"/>
+      <c r="I69" s="8" t="n"/>
+      <c r="J69" s="8" t="n"/>
+      <c r="K69" s="8" t="n"/>
+      <c r="L69" s="8" t="n"/>
+      <c r="M69" s="8" t="n"/>
+      <c r="N69" s="9" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>Small</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>Enterprise</t>
-        </is>
-      </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>Basis</t>
-        </is>
-      </c>
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>EOPT invoicing review with the broker tax adviser</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: registered invoice documents, supplementary wording, VAT treatment, ATP or CAS. Optional service confirmed by management on 04 October 2026.</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="n"/>
+      <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
       <c r="H70" s="8" t="n"/>
       <c r="I70" s="8" t="n"/>
@@ -5107,26 +5147,24 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>Application containers (API, web, scheduler)</t>
-        </is>
-      </c>
-      <c r="B71" s="16" t="n">
-        <v>90</v>
-      </c>
-      <c r="C71" s="16" t="n">
-        <v>135</v>
-      </c>
-      <c r="D71" s="16" t="n">
-        <v>180</v>
-      </c>
-      <c r="E71" s="16" t="n">
-        <v>360</v>
-      </c>
-      <c r="F71" s="15" t="inlineStr">
-        <is>
-          <t>Estimate: 2/3/4/8 containers of 1 vCPU, 2 GB (Fargate, Singapore).</t>
-        </is>
-      </c>
+          <t>BIR CAS registration support</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="D71" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: books, system description, Permit to Use filing prepared with the broker. Optional service confirmed by management on 04 October 2026.</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="n"/>
+      <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
       <c r="H71" s="8" t="n"/>
       <c r="I71" s="8" t="n"/>
@@ -5139,26 +5177,24 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>Managed PostgreSQL 16 (instance and storage)</t>
-        </is>
-      </c>
-      <c r="B72" s="16" t="n">
-        <v>85</v>
-      </c>
-      <c r="C72" s="16" t="n">
-        <v>320</v>
-      </c>
-      <c r="D72" s="16" t="n">
-        <v>640</v>
-      </c>
-      <c r="E72" s="16" t="n">
-        <v>1280</v>
-      </c>
-      <c r="F72" s="15" t="inlineStr">
-        <is>
-          <t>Estimate: db.t4g.medium single-AZ / db.m7g.large Multi-AZ / m7g.xlarge Multi-AZ / m7g.2xlarge Multi-AZ (S20). Large and Enterprise: high availability.</t>
-        </is>
-      </c>
+          <t>BIR EIS enrolment and certification</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: enrolment, signing certificate, final field list, production endpoint and certification of the connector. Optional service confirmed by management on 04 October 2026.</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="n"/>
+      <c r="F72" s="8" t="n"/>
       <c r="G72" s="8" t="n"/>
       <c r="H72" s="8" t="n"/>
       <c r="I72" s="8" t="n"/>
@@ -5171,26 +5207,24 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>Object storage and backups (documents, snapshots)</t>
-        </is>
-      </c>
-      <c r="B73" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="C73" s="16" t="n">
-        <v>40</v>
-      </c>
-      <c r="D73" s="16" t="n">
-        <v>90</v>
-      </c>
-      <c r="E73" s="16" t="n">
-        <v>180</v>
-      </c>
-      <c r="F73" s="15" t="inlineStr">
-        <is>
-          <t>Estimate: S3 and snapshot storage, growing with policies and uploads.</t>
-        </is>
-      </c>
+          <t>CTPL authentication and LTO interface certification</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: acceptance of the live requests by the accredited provider, COC series, LTO interface. Optional service confirmed by management on 04 October 2026.</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="n"/>
+      <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
       <c r="H73" s="8" t="n"/>
       <c r="I73" s="8" t="n"/>
@@ -5203,26 +5237,24 @@
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>Network (load balancer, CDN, data transfer)</t>
-        </is>
-      </c>
-      <c r="B74" s="16" t="n">
-        <v>45</v>
-      </c>
-      <c r="C74" s="16" t="n">
-        <v>70</v>
-      </c>
-      <c r="D74" s="16" t="n">
-        <v>120</v>
-      </c>
-      <c r="E74" s="16" t="n">
-        <v>220</v>
-      </c>
-      <c r="F74" s="15" t="inlineStr">
-        <is>
-          <t>Estimate.</t>
-        </is>
-      </c>
+          <t>Insurer API onboarding, per insurer</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: endpoint, credentials, field mapping and live test with one insurer. Optional service confirmed by management on 04 October 2026.</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="n"/>
+      <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="n"/>
       <c r="H74" s="8" t="n"/>
       <c r="I74" s="8" t="n"/>
@@ -5235,26 +5267,24 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>Security and monitoring (WAF, logs, alarms, secrets, keys)</t>
-        </is>
-      </c>
-      <c r="B75" s="16" t="n">
-        <v>35</v>
-      </c>
-      <c r="C75" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="D75" s="16" t="n">
-        <v>110</v>
-      </c>
-      <c r="E75" s="16" t="n">
-        <v>200</v>
-      </c>
-      <c r="F75" s="15" t="inlineStr">
-        <is>
-          <t>Estimate.</t>
-        </is>
-      </c>
+          <t>Bank payment file certification, per bank</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="D75" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: layout validated against the bank specification and a test file accepted. Optional service confirmed by management on 04 October 2026.</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="n"/>
+      <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
       <c r="H75" s="8" t="n"/>
       <c r="I75" s="8" t="n"/>
@@ -5267,26 +5297,24 @@
     <row r="76">
       <c r="A76" s="10" t="inlineStr">
         <is>
-          <t>Disaster recovery copy (cross-region backups)</t>
-        </is>
-      </c>
-      <c r="B76" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C76" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="16" t="n">
-        <v>400</v>
-      </c>
-      <c r="F76" s="15" t="inlineStr">
-        <is>
-          <t>Estimate: Enterprise only; optional for others. Not part of Pre-Prod.</t>
-        </is>
-      </c>
+          <t>SMS or Viber gateway activation</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="D76" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: sender name or short code, live credentials, templates and consent check tested. Optional service confirmed by management on 04 October 2026.</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="n"/>
+      <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
       <c r="H76" s="8" t="n"/>
       <c r="I76" s="8" t="n"/>
@@ -5297,32 +5325,39 @@
       <c r="N76" s="9" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="18" t="inlineStr">
-        <is>
-          <t>Production reference cost per month (USD)</t>
-        </is>
-      </c>
-      <c r="B77" s="21">
-        <f>SUM(B71:B76)</f>
-        <v/>
-      </c>
-      <c r="C77" s="21">
-        <f>SUM(C71:C76)</f>
-        <v/>
-      </c>
-      <c r="D77" s="21">
-        <f>SUM(D71:D76)</f>
-        <v/>
-      </c>
-      <c r="E77" s="21">
-        <f>SUM(E71:E76)</f>
-        <v/>
-      </c>
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>Screening list provider onboarding</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: provider contract data, API key, adapter test and first screening run. Optional service confirmed by management on 04 October 2026.</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="n"/>
+      <c r="F77" s="8" t="n"/>
+      <c r="G77" s="8" t="n"/>
+      <c r="H77" s="8" t="n"/>
+      <c r="I77" s="8" t="n"/>
+      <c r="J77" s="8" t="n"/>
+      <c r="K77" s="8" t="n"/>
+      <c r="L77" s="8" t="n"/>
+      <c r="M77" s="8" t="n"/>
+      <c r="N77" s="9" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>Infrastructure: non-production environment sizes and Pre-Prod use</t>
+          <t>Infrastructure: AWS reference cost per month of the Production environment (USD)</t>
         </is>
       </c>
       <c r="B79" s="7" t="n"/>
@@ -5342,26 +5377,34 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Driver</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Unit</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>Enterprise</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="E80" s="8" t="n"/>
-      <c r="F80" s="8" t="n"/>
       <c r="G80" s="8" t="n"/>
       <c r="H80" s="8" t="n"/>
       <c r="I80" s="8" t="n"/>
@@ -5374,24 +5417,26 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>Non-production environment, small: cloud cost per month</t>
+          <t>Application containers (API, web, scheduler)</t>
         </is>
       </c>
       <c r="B81" s="16" t="n">
-        <v>150</v>
-      </c>
-      <c r="C81" s="10" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D81" s="15" t="inlineStr">
-        <is>
-          <t>Estimate: 1 container of 1 vCPU, 2 GB; PostgreSQL db.t4g.medium single-AZ, 50 GB; file store; backups 7 to 14 days. Dev in every tier; UAT of Small and Medium brokers.</t>
-        </is>
-      </c>
-      <c r="E81" s="8" t="n"/>
-      <c r="F81" s="8" t="n"/>
+        <v>90</v>
+      </c>
+      <c r="C81" s="16" t="n">
+        <v>135</v>
+      </c>
+      <c r="D81" s="16" t="n">
+        <v>180</v>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>360</v>
+      </c>
+      <c r="F81" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: 2/3/4/8 containers of 1 vCPU, 2 GB (Fargate, Singapore).</t>
+        </is>
+      </c>
       <c r="G81" s="8" t="n"/>
       <c r="H81" s="8" t="n"/>
       <c r="I81" s="8" t="n"/>
@@ -5404,24 +5449,26 @@
     <row r="82">
       <c r="A82" s="10" t="inlineStr">
         <is>
-          <t>Non-production environment, medium: cloud cost per month</t>
+          <t>Managed PostgreSQL 16 (instance and storage)</t>
         </is>
       </c>
       <c r="B82" s="16" t="n">
-        <v>300</v>
-      </c>
-      <c r="C82" s="10" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D82" s="15" t="inlineStr">
-        <is>
-          <t>Estimate: 2 containers of 1 vCPU, 2 GB (the second for the UAT performance test); db.t4g.large single-AZ, 100 GB; file store; load balancer. SIT and UAT of Large and Enterprise brokers.</t>
-        </is>
-      </c>
-      <c r="E82" s="8" t="n"/>
-      <c r="F82" s="8" t="n"/>
+        <v>85</v>
+      </c>
+      <c r="C82" s="16" t="n">
+        <v>320</v>
+      </c>
+      <c r="D82" s="16" t="n">
+        <v>640</v>
+      </c>
+      <c r="E82" s="16" t="n">
+        <v>1280</v>
+      </c>
+      <c r="F82" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: db.t4g.medium single-AZ / db.m7g.large Multi-AZ / m7g.xlarge Multi-AZ / m7g.2xlarge Multi-AZ (S20). Large and Enterprise: high availability.</t>
+        </is>
+      </c>
       <c r="G82" s="8" t="n"/>
       <c r="H82" s="8" t="n"/>
       <c r="I82" s="8" t="n"/>
@@ -5434,24 +5481,26 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>Pre-Prod cloud cost relative to Production (without the DR copy)</t>
-        </is>
-      </c>
-      <c r="B83" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C83" s="10" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D83" s="15" t="inlineStr">
-        <is>
-          <t>Assumption: Pre-Prod is restored from a production backup and runs at production topology and size, so the rehearsal measures real timings.</t>
-        </is>
-      </c>
-      <c r="E83" s="8" t="n"/>
-      <c r="F83" s="8" t="n"/>
+          <t>Object storage and backups (documents, snapshots)</t>
+        </is>
+      </c>
+      <c r="B83" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="C83" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="D83" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="E83" s="16" t="n">
+        <v>180</v>
+      </c>
+      <c r="F83" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: S3 and snapshot storage, growing with policies and uploads.</t>
+        </is>
+      </c>
       <c r="G83" s="8" t="n"/>
       <c r="H83" s="8" t="n"/>
       <c r="I83" s="8" t="n"/>
@@ -5464,24 +5513,26 @@
     <row r="84">
       <c r="A84" s="10" t="inlineStr">
         <is>
-          <t>Pre-Prod months of use around go-live</t>
-        </is>
-      </c>
-      <c r="B84" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C84" s="10" t="inlineStr">
-        <is>
-          <t>months</t>
-        </is>
-      </c>
-      <c r="D84" s="15" t="inlineStr">
-        <is>
-          <t>Assumption: created before the cutover rehearsal and removed after hypercare (1 to 2 months). Billed per month of use.</t>
-        </is>
-      </c>
-      <c r="E84" s="8" t="n"/>
-      <c r="F84" s="8" t="n"/>
+          <t>Network (load balancer, CDN, data transfer)</t>
+        </is>
+      </c>
+      <c r="B84" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="C84" s="16" t="n">
+        <v>70</v>
+      </c>
+      <c r="D84" s="16" t="n">
+        <v>120</v>
+      </c>
+      <c r="E84" s="16" t="n">
+        <v>220</v>
+      </c>
+      <c r="F84" s="15" t="inlineStr">
+        <is>
+          <t>Estimate.</t>
+        </is>
+      </c>
       <c r="G84" s="8" t="n"/>
       <c r="H84" s="8" t="n"/>
       <c r="I84" s="8" t="n"/>
@@ -5494,24 +5545,26 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>Pre-Prod months of use per major release</t>
-        </is>
-      </c>
-      <c r="B85" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C85" s="10" t="inlineStr">
-        <is>
-          <t>months</t>
-        </is>
-      </c>
-      <c r="D85" s="15" t="inlineStr">
-        <is>
-          <t>Assumption: created from a production backup for the release rehearsal and removed after the release.</t>
-        </is>
-      </c>
-      <c r="E85" s="8" t="n"/>
-      <c r="F85" s="8" t="n"/>
+          <t>Security and monitoring (WAF, logs, alarms, secrets, keys)</t>
+        </is>
+      </c>
+      <c r="B85" s="16" t="n">
+        <v>35</v>
+      </c>
+      <c r="C85" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="D85" s="16" t="n">
+        <v>110</v>
+      </c>
+      <c r="E85" s="16" t="n">
+        <v>200</v>
+      </c>
+      <c r="F85" s="15" t="inlineStr">
+        <is>
+          <t>Estimate.</t>
+        </is>
+      </c>
       <c r="G85" s="8" t="n"/>
       <c r="H85" s="8" t="n"/>
       <c r="I85" s="8" t="n"/>
@@ -5524,24 +5577,26 @@
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t>Major releases per year (yearly hosting view only)</t>
-        </is>
-      </c>
-      <c r="B86" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C86" s="10" t="inlineStr">
-        <is>
-          <t>releases</t>
-        </is>
-      </c>
-      <c r="D86" s="15" t="inlineStr">
-        <is>
-          <t>Assumption for budgeting. Major releases are announced at least 6 months ahead (Release Notes and Roadmap); the invoice follows the actual months of use.</t>
-        </is>
-      </c>
-      <c r="E86" s="8" t="n"/>
-      <c r="F86" s="8" t="n"/>
+          <t>Disaster recovery copy (cross-region backups)</t>
+        </is>
+      </c>
+      <c r="B86" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="16" t="n">
+        <v>400</v>
+      </c>
+      <c r="F86" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: Enterprise only; optional for others. Not part of Pre-Prod.</t>
+        </is>
+      </c>
       <c r="G86" s="8" t="n"/>
       <c r="H86" s="8" t="n"/>
       <c r="I86" s="8" t="n"/>
@@ -5551,107 +5606,74 @@
       <c r="M86" s="8" t="n"/>
       <c r="N86" s="9" t="n"/>
     </row>
-    <row r="88">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>Infrastructure: environment set by tier, AWS reference cost per month (USD)</t>
-        </is>
-      </c>
-      <c r="B88" s="7" t="n"/>
-      <c r="C88" s="7" t="n"/>
-      <c r="D88" s="7" t="n"/>
-      <c r="E88" s="7" t="n"/>
-      <c r="F88" s="7" t="n"/>
-      <c r="G88" s="7" t="n"/>
-      <c r="H88" s="7" t="n"/>
-      <c r="I88" s="7" t="n"/>
-      <c r="J88" s="7" t="n"/>
-      <c r="K88" s="7" t="n"/>
-      <c r="L88" s="7" t="n"/>
-      <c r="M88" s="7" t="n"/>
-      <c r="N88" s="7" t="n"/>
-    </row>
-    <row r="89" ht="30" customHeight="1">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>Tier</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>Dev</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>SIT</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>UAT</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>Production</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="inlineStr">
-        <is>
-          <t>Standing environments</t>
-        </is>
-      </c>
-      <c r="G89" s="3" t="inlineStr">
-        <is>
-          <t>Pre-Prod per month of use</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>Environment set and basis</t>
-        </is>
-      </c>
-      <c r="I89" s="8" t="n"/>
-      <c r="J89" s="8" t="n"/>
-      <c r="K89" s="8" t="n"/>
-      <c r="L89" s="8" t="n"/>
-      <c r="M89" s="8" t="n"/>
-      <c r="N89" s="9" t="n"/>
+    <row r="87">
+      <c r="A87" s="18" t="inlineStr">
+        <is>
+          <t>Production reference cost per month (USD)</t>
+        </is>
+      </c>
+      <c r="B87" s="21">
+        <f>SUM(B81:B86)</f>
+        <v/>
+      </c>
+      <c r="C87" s="21">
+        <f>SUM(C81:C86)</f>
+        <v/>
+      </c>
+      <c r="D87" s="21">
+        <f>SUM(D81:D86)</f>
+        <v/>
+      </c>
+      <c r="E87" s="21">
+        <f>SUM(E81:E86)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>Infrastructure: non-production environment sizes and Pre-Prod use</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="n"/>
+      <c r="C89" s="7" t="n"/>
+      <c r="D89" s="7" t="n"/>
+      <c r="E89" s="7" t="n"/>
+      <c r="F89" s="7" t="n"/>
+      <c r="G89" s="7" t="n"/>
+      <c r="H89" s="7" t="n"/>
+      <c r="I89" s="7" t="n"/>
+      <c r="J89" s="7" t="n"/>
+      <c r="K89" s="7" t="n"/>
+      <c r="L89" s="7" t="n"/>
+      <c r="M89" s="7" t="n"/>
+      <c r="N89" s="7" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="18">
-        <f>A28</f>
-        <v/>
-      </c>
-      <c r="B90" s="20">
-        <f>NP_Small_USD</f>
-        <v/>
-      </c>
-      <c r="C90" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" s="20">
-        <f>NP_Small_USD</f>
-        <v/>
-      </c>
-      <c r="E90" s="20">
-        <f>B77</f>
-        <v/>
-      </c>
-      <c r="F90" s="24">
-        <f>SUM(B90:E90)</f>
-        <v/>
-      </c>
-      <c r="G90" s="21">
-        <f>SUM(B71:B75)*PreProd_Factor</f>
-        <v/>
-      </c>
-      <c r="H90" s="5" t="inlineStr">
-        <is>
-          <t>Dev, UAT, Production, temporary Pre-Prod. Integration and SIT in Dev, then promoted to UAT for testing.</t>
-        </is>
-      </c>
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="n"/>
+      <c r="F90" s="8" t="n"/>
+      <c r="G90" s="8" t="n"/>
+      <c r="H90" s="8" t="n"/>
       <c r="I90" s="8" t="n"/>
       <c r="J90" s="8" t="n"/>
       <c r="K90" s="8" t="n"/>
@@ -5660,38 +5682,28 @@
       <c r="N90" s="9" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="18">
-        <f>A29</f>
-        <v/>
-      </c>
-      <c r="B91" s="20">
-        <f>NP_Small_USD</f>
-        <v/>
-      </c>
-      <c r="C91" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" s="20">
-        <f>NP_Small_USD</f>
-        <v/>
-      </c>
-      <c r="E91" s="20">
-        <f>C77</f>
-        <v/>
-      </c>
-      <c r="F91" s="24">
-        <f>SUM(B91:E91)</f>
-        <v/>
-      </c>
-      <c r="G91" s="21">
-        <f>SUM(C71:C75)*PreProd_Factor</f>
-        <v/>
-      </c>
-      <c r="H91" s="5" t="inlineStr">
-        <is>
-          <t>Dev, UAT, Production, temporary Pre-Prod. As Small.</t>
-        </is>
-      </c>
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>Non-production environment, small: cloud cost per month</t>
+        </is>
+      </c>
+      <c r="B91" s="16" t="n">
+        <v>150</v>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D91" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: 1 container of 1 vCPU, 2 GB; PostgreSQL db.t4g.medium single-AZ, 50 GB; file store; backups 7 to 14 days. Dev in every tier; UAT of Small and Medium brokers.</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="n"/>
+      <c r="F91" s="8" t="n"/>
+      <c r="G91" s="8" t="n"/>
+      <c r="H91" s="8" t="n"/>
       <c r="I91" s="8" t="n"/>
       <c r="J91" s="8" t="n"/>
       <c r="K91" s="8" t="n"/>
@@ -5700,39 +5712,28 @@
       <c r="N91" s="9" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="18">
-        <f>A30</f>
-        <v/>
-      </c>
-      <c r="B92" s="20">
-        <f>NP_Small_USD</f>
-        <v/>
-      </c>
-      <c r="C92" s="20">
-        <f>NP_Med_USD</f>
-        <v/>
-      </c>
-      <c r="D92" s="20">
-        <f>NP_Med_USD</f>
-        <v/>
-      </c>
-      <c r="E92" s="20">
-        <f>D77</f>
-        <v/>
-      </c>
-      <c r="F92" s="24">
-        <f>SUM(B92:E92)</f>
-        <v/>
-      </c>
-      <c r="G92" s="21">
-        <f>SUM(D71:D75)*PreProd_Factor</f>
-        <v/>
-      </c>
-      <c r="H92" s="5" t="inlineStr">
-        <is>
-          <t>Dev, SIT, UAT, Production with high availability, temporary Pre-Prod. SIT and UAT are separate.</t>
-        </is>
-      </c>
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>Non-production environment, medium: cloud cost per month</t>
+        </is>
+      </c>
+      <c r="B92" s="16" t="n">
+        <v>300</v>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D92" s="15" t="inlineStr">
+        <is>
+          <t>Estimate: 2 containers of 1 vCPU, 2 GB (the second for the UAT performance test); db.t4g.large single-AZ, 100 GB; file store; load balancer. SIT and UAT of Large and Enterprise brokers.</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="n"/>
+      <c r="F92" s="8" t="n"/>
+      <c r="G92" s="8" t="n"/>
+      <c r="H92" s="8" t="n"/>
       <c r="I92" s="8" t="n"/>
       <c r="J92" s="8" t="n"/>
       <c r="K92" s="8" t="n"/>
@@ -5741,39 +5742,28 @@
       <c r="N92" s="9" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="18">
-        <f>A31</f>
-        <v/>
-      </c>
-      <c r="B93" s="20">
-        <f>NP_Small_USD</f>
-        <v/>
-      </c>
-      <c r="C93" s="20">
-        <f>NP_Med_USD</f>
-        <v/>
-      </c>
-      <c r="D93" s="20">
-        <f>NP_Med_USD</f>
-        <v/>
-      </c>
-      <c r="E93" s="20">
-        <f>E77</f>
-        <v/>
-      </c>
-      <c r="F93" s="24">
-        <f>SUM(B93:E93)</f>
-        <v/>
-      </c>
-      <c r="G93" s="21">
-        <f>SUM(E71:E75)*PreProd_Factor</f>
-        <v/>
-      </c>
-      <c r="H93" s="5" t="inlineStr">
-        <is>
-          <t>As Large, with the cross-region DR copy in Production.</t>
-        </is>
-      </c>
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>Pre-Prod cloud cost relative to Production (without the DR copy)</t>
+        </is>
+      </c>
+      <c r="B93" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D93" s="15" t="inlineStr">
+        <is>
+          <t>Assumption: Pre-Prod is restored from a production backup and runs at production topology and size, so the rehearsal measures real timings.</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="n"/>
+      <c r="F93" s="8" t="n"/>
+      <c r="G93" s="8" t="n"/>
+      <c r="H93" s="8" t="n"/>
       <c r="I93" s="8" t="n"/>
       <c r="J93" s="8" t="n"/>
       <c r="K93" s="8" t="n"/>
@@ -5784,17 +5774,24 @@
     <row r="94">
       <c r="A94" s="10" t="inlineStr">
         <is>
-          <t>Azure cost relative to AWS</t>
-        </is>
-      </c>
-      <c r="B94" s="11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="F94" s="15" t="inlineStr">
-        <is>
-          <t>Assumption: comparable list prices in Southeast Asia (D4s v5 Linux about USD 158 a month, S21); +5% for managed PostgreSQL and WAF differences.</t>
-        </is>
-      </c>
+          <t>Pre-Prod months of use around go-live</t>
+        </is>
+      </c>
+      <c r="B94" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="D94" s="15" t="inlineStr">
+        <is>
+          <t>Assumption: created before the cutover rehearsal and removed after hypercare (1 to 2 months). Billed per month of use.</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="n"/>
+      <c r="F94" s="8" t="n"/>
       <c r="G94" s="8" t="n"/>
       <c r="H94" s="8" t="n"/>
       <c r="I94" s="8" t="n"/>
@@ -5807,17 +5804,24 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>Local partner cloud cost relative to AWS</t>
-        </is>
-      </c>
-      <c r="B95" s="11" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F95" s="15" t="inlineStr">
-        <is>
-          <t>Assumption: Philippine data-centre or partner cloud priced in PHP; lower compute and bandwidth, database run as managed VM. Confirm with a partner quotation.</t>
-        </is>
-      </c>
+          <t>Pre-Prod months of use per major release</t>
+        </is>
+      </c>
+      <c r="B95" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" s="10" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="D95" s="15" t="inlineStr">
+        <is>
+          <t>Assumption: created from a production backup for the release rehearsal and removed after the release.</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="n"/>
+      <c r="F95" s="8" t="n"/>
       <c r="G95" s="8" t="n"/>
       <c r="H95" s="8" t="n"/>
       <c r="I95" s="8" t="n"/>
@@ -5827,90 +5831,97 @@
       <c r="M95" s="8" t="n"/>
       <c r="N95" s="9" t="n"/>
     </row>
-    <row r="97">
-      <c r="A97" s="6" t="inlineStr">
-        <is>
-          <t>Sample quote scenarios (used by Sample Quotes)</t>
-        </is>
-      </c>
-      <c r="B97" s="7" t="n"/>
-      <c r="C97" s="7" t="n"/>
-      <c r="D97" s="7" t="n"/>
-      <c r="E97" s="7" t="n"/>
-      <c r="F97" s="7" t="n"/>
-      <c r="G97" s="7" t="n"/>
-      <c r="H97" s="7" t="n"/>
-      <c r="I97" s="7" t="n"/>
-      <c r="J97" s="7" t="n"/>
-      <c r="K97" s="7" t="n"/>
-      <c r="L97" s="7" t="n"/>
-      <c r="M97" s="7" t="n"/>
-      <c r="N97" s="7" t="n"/>
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>Major releases per year (yearly hosting view only)</t>
+        </is>
+      </c>
+      <c r="B96" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
+        <is>
+          <t>releases</t>
+        </is>
+      </c>
+      <c r="D96" s="15" t="inlineStr">
+        <is>
+          <t>Assumption for budgeting. Major releases are announced at least 6 months ahead (Release Notes and Roadmap); the invoice follows the actual months of use.</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="n"/>
+      <c r="F96" s="8" t="n"/>
+      <c r="G96" s="8" t="n"/>
+      <c r="H96" s="8" t="n"/>
+      <c r="I96" s="8" t="n"/>
+      <c r="J96" s="8" t="n"/>
+      <c r="K96" s="8" t="n"/>
+      <c r="L96" s="8" t="n"/>
+      <c r="M96" s="8" t="n"/>
+      <c r="N96" s="9" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>Driver</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>Example 1</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t>Example 2</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>Example 3</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr"/>
-      <c r="F98" s="3" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="G98" s="8" t="n"/>
-      <c r="H98" s="8" t="n"/>
-      <c r="I98" s="8" t="n"/>
-      <c r="J98" s="8" t="n"/>
-      <c r="K98" s="8" t="n"/>
-      <c r="L98" s="8" t="n"/>
-      <c r="M98" s="8" t="n"/>
-      <c r="N98" s="9" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="10" t="inlineStr">
-        <is>
-          <t>Broker profile</t>
-        </is>
-      </c>
-      <c r="B99" s="12" t="inlineStr">
-        <is>
-          <t>Small broker</t>
-        </is>
-      </c>
-      <c r="C99" s="12" t="inlineStr">
-        <is>
-          <t>Medium broker</t>
-        </is>
-      </c>
-      <c r="D99" s="12" t="inlineStr">
-        <is>
-          <t>Large broker</t>
-        </is>
-      </c>
-      <c r="F99" s="10" t="inlineStr">
-        <is>
-          <t>Label only.</t>
-        </is>
-      </c>
-      <c r="G99" s="8" t="n"/>
-      <c r="H99" s="8" t="n"/>
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>Infrastructure: environment set by tier, AWS reference cost per month (USD)</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="n"/>
+      <c r="C98" s="7" t="n"/>
+      <c r="D98" s="7" t="n"/>
+      <c r="E98" s="7" t="n"/>
+      <c r="F98" s="7" t="n"/>
+      <c r="G98" s="7" t="n"/>
+      <c r="H98" s="7" t="n"/>
+      <c r="I98" s="7" t="n"/>
+      <c r="J98" s="7" t="n"/>
+      <c r="K98" s="7" t="n"/>
+      <c r="L98" s="7" t="n"/>
+      <c r="M98" s="7" t="n"/>
+      <c r="N98" s="7" t="n"/>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>SIT</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>UAT</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>Standing environments</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>Pre-Prod per month of use</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>Environment set and basis</t>
+        </is>
+      </c>
       <c r="I99" s="8" t="n"/>
       <c r="J99" s="8" t="n"/>
       <c r="K99" s="8" t="n"/>
@@ -5919,27 +5930,38 @@
       <c r="N99" s="9" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="10" t="inlineStr">
-        <is>
-          <t>Named users</t>
-        </is>
-      </c>
-      <c r="B100" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C100" s="14" t="n">
-        <v>60</v>
-      </c>
-      <c r="D100" s="14" t="n">
-        <v>180</v>
-      </c>
-      <c r="F100" s="10" t="inlineStr">
-        <is>
-          <t>Tier follows from the user count.</t>
-        </is>
-      </c>
-      <c r="G100" s="8" t="n"/>
-      <c r="H100" s="8" t="n"/>
+      <c r="A100" s="18">
+        <f>A28</f>
+        <v/>
+      </c>
+      <c r="B100" s="20">
+        <f>NP_Small_USD</f>
+        <v/>
+      </c>
+      <c r="C100" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="20">
+        <f>NP_Small_USD</f>
+        <v/>
+      </c>
+      <c r="E100" s="20">
+        <f>B87</f>
+        <v/>
+      </c>
+      <c r="F100" s="24">
+        <f>SUM(B100:E100)</f>
+        <v/>
+      </c>
+      <c r="G100" s="21">
+        <f>SUM(B81:B85)*PreProd_Factor</f>
+        <v/>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>Dev, UAT, Production, temporary Pre-Prod. Integration and SIT in Dev, then promoted to UAT for testing.</t>
+        </is>
+      </c>
       <c r="I100" s="8" t="n"/>
       <c r="J100" s="8" t="n"/>
       <c r="K100" s="8" t="n"/>
@@ -5948,27 +5970,38 @@
       <c r="N100" s="9" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="10" t="inlineStr">
-        <is>
-          <t>Lines of business</t>
-        </is>
-      </c>
-      <c r="B101" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C101" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="D101" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="F101" s="10" t="inlineStr">
-        <is>
-          <t>Motor, fire, marine, casualty, engineering, bonds and so on.</t>
-        </is>
-      </c>
-      <c r="G101" s="8" t="n"/>
-      <c r="H101" s="8" t="n"/>
+      <c r="A101" s="18">
+        <f>A29</f>
+        <v/>
+      </c>
+      <c r="B101" s="20">
+        <f>NP_Small_USD</f>
+        <v/>
+      </c>
+      <c r="C101" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="20">
+        <f>NP_Small_USD</f>
+        <v/>
+      </c>
+      <c r="E101" s="20">
+        <f>C87</f>
+        <v/>
+      </c>
+      <c r="F101" s="24">
+        <f>SUM(B101:E101)</f>
+        <v/>
+      </c>
+      <c r="G101" s="21">
+        <f>SUM(C81:C85)*PreProd_Factor</f>
+        <v/>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>Dev, UAT, Production, temporary Pre-Prod. As Small.</t>
+        </is>
+      </c>
       <c r="I101" s="8" t="n"/>
       <c r="J101" s="8" t="n"/>
       <c r="K101" s="8" t="n"/>
@@ -5977,33 +6010,39 @@
       <c r="N101" s="9" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="10" t="inlineStr">
-        <is>
-          <t>Infrastructure provider (AWS, Azure, Local partner, Customer)</t>
-        </is>
-      </c>
-      <c r="B102" s="12" t="inlineStr">
-        <is>
-          <t>AWS</t>
-        </is>
-      </c>
-      <c r="C102" s="12" t="inlineStr">
-        <is>
-          <t>Azure</t>
-        </is>
-      </c>
-      <c r="D102" s="12" t="inlineStr">
-        <is>
-          <t>Local partner</t>
-        </is>
-      </c>
-      <c r="F102" s="10" t="inlineStr">
-        <is>
-          <t>"Customer" means the broker hosts itself: no infrastructure fee.</t>
-        </is>
-      </c>
-      <c r="G102" s="8" t="n"/>
-      <c r="H102" s="8" t="n"/>
+      <c r="A102" s="18">
+        <f>A30</f>
+        <v/>
+      </c>
+      <c r="B102" s="20">
+        <f>NP_Small_USD</f>
+        <v/>
+      </c>
+      <c r="C102" s="20">
+        <f>NP_Med_USD</f>
+        <v/>
+      </c>
+      <c r="D102" s="20">
+        <f>NP_Med_USD</f>
+        <v/>
+      </c>
+      <c r="E102" s="20">
+        <f>D87</f>
+        <v/>
+      </c>
+      <c r="F102" s="24">
+        <f>SUM(B102:E102)</f>
+        <v/>
+      </c>
+      <c r="G102" s="21">
+        <f>SUM(D81:D85)*PreProd_Factor</f>
+        <v/>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>Dev, SIT, UAT, Production with high availability, temporary Pre-Prod. SIT and UAT are separate.</t>
+        </is>
+      </c>
       <c r="I102" s="8" t="n"/>
       <c r="J102" s="8" t="n"/>
       <c r="K102" s="8" t="n"/>
@@ -6012,33 +6051,39 @@
       <c r="N102" s="9" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="10" t="inlineStr">
-        <is>
-          <t>24x7 Severity 1 support (Yes/No)</t>
-        </is>
-      </c>
-      <c r="B103" s="12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C103" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D103" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F103" s="10" t="inlineStr">
-        <is>
-          <t>Optional.</t>
-        </is>
-      </c>
-      <c r="G103" s="8" t="n"/>
-      <c r="H103" s="8" t="n"/>
+      <c r="A103" s="18">
+        <f>A31</f>
+        <v/>
+      </c>
+      <c r="B103" s="20">
+        <f>NP_Small_USD</f>
+        <v/>
+      </c>
+      <c r="C103" s="20">
+        <f>NP_Med_USD</f>
+        <v/>
+      </c>
+      <c r="D103" s="20">
+        <f>NP_Med_USD</f>
+        <v/>
+      </c>
+      <c r="E103" s="20">
+        <f>E87</f>
+        <v/>
+      </c>
+      <c r="F103" s="24">
+        <f>SUM(B103:E103)</f>
+        <v/>
+      </c>
+      <c r="G103" s="21">
+        <f>SUM(E81:E85)*PreProd_Factor</f>
+        <v/>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>As Large, with the cross-region DR copy in Production.</t>
+        </is>
+      </c>
       <c r="I103" s="8" t="n"/>
       <c r="J103" s="8" t="n"/>
       <c r="K103" s="8" t="n"/>
@@ -6049,21 +6094,15 @@
     <row r="104">
       <c r="A104" s="10" t="inlineStr">
         <is>
-          <t>Extra training days</t>
-        </is>
-      </c>
-      <c r="B104" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C104" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D104" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="F104" s="10" t="inlineStr">
-        <is>
-          <t>Beyond the days included for the tier.</t>
+          <t>Azure cost relative to AWS</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F104" s="15" t="inlineStr">
+        <is>
+          <t>Assumption: comparable list prices in Southeast Asia (D4s v5 Linux about USD 158 a month, S21); +5% for managed PostgreSQL and WAF differences.</t>
         </is>
       </c>
       <c r="G104" s="8" t="n"/>
@@ -6078,21 +6117,15 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>Extra legacy data sources to migrate</t>
-        </is>
-      </c>
-      <c r="B105" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C105" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D105" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F105" s="10" t="inlineStr">
-        <is>
-          <t>Beyond the standard templates.</t>
+          <t>Local partner cloud cost relative to AWS</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F105" s="15" t="inlineStr">
+        <is>
+          <t>Assumption: Philippine data-centre or partner cloud priced in PHP; lower compute and bandwidth, database run as managed VM. Confirm with a partner quotation.</t>
         </is>
       </c>
       <c r="G105" s="8" t="n"/>
@@ -6104,117 +6137,404 @@
       <c r="M105" s="8" t="n"/>
       <c r="N105" s="9" t="n"/>
     </row>
-    <row r="106">
-      <c r="A106" s="10" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>Sample quote scenarios (used by Sample Quotes)</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="n"/>
+      <c r="C107" s="7" t="n"/>
+      <c r="D107" s="7" t="n"/>
+      <c r="E107" s="7" t="n"/>
+      <c r="F107" s="7" t="n"/>
+      <c r="G107" s="7" t="n"/>
+      <c r="H107" s="7" t="n"/>
+      <c r="I107" s="7" t="n"/>
+      <c r="J107" s="7" t="n"/>
+      <c r="K107" s="7" t="n"/>
+      <c r="L107" s="7" t="n"/>
+      <c r="M107" s="7" t="n"/>
+      <c r="N107" s="7" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>Example 1</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>Example 2</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>Example 3</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr"/>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="G108" s="8" t="n"/>
+      <c r="H108" s="8" t="n"/>
+      <c r="I108" s="8" t="n"/>
+      <c r="J108" s="8" t="n"/>
+      <c r="K108" s="8" t="n"/>
+      <c r="L108" s="8" t="n"/>
+      <c r="M108" s="8" t="n"/>
+      <c r="N108" s="9" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>Broker profile</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>Small broker</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>Medium broker</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>Large broker</t>
+        </is>
+      </c>
+      <c r="F109" s="10" t="inlineStr">
+        <is>
+          <t>Label only.</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="n"/>
+      <c r="H109" s="8" t="n"/>
+      <c r="I109" s="8" t="n"/>
+      <c r="J109" s="8" t="n"/>
+      <c r="K109" s="8" t="n"/>
+      <c r="L109" s="8" t="n"/>
+      <c r="M109" s="8" t="n"/>
+      <c r="N109" s="9" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>Named users</t>
+        </is>
+      </c>
+      <c r="B110" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="C110" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="D110" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="F110" s="10" t="inlineStr">
+        <is>
+          <t>Tier follows from the user count.</t>
+        </is>
+      </c>
+      <c r="G110" s="8" t="n"/>
+      <c r="H110" s="8" t="n"/>
+      <c r="I110" s="8" t="n"/>
+      <c r="J110" s="8" t="n"/>
+      <c r="K110" s="8" t="n"/>
+      <c r="L110" s="8" t="n"/>
+      <c r="M110" s="8" t="n"/>
+      <c r="N110" s="9" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>Lines of business</t>
+        </is>
+      </c>
+      <c r="B111" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C111" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="D111" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F111" s="10" t="inlineStr">
+        <is>
+          <t>Motor, fire, marine, casualty, engineering, bonds and so on.</t>
+        </is>
+      </c>
+      <c r="G111" s="8" t="n"/>
+      <c r="H111" s="8" t="n"/>
+      <c r="I111" s="8" t="n"/>
+      <c r="J111" s="8" t="n"/>
+      <c r="K111" s="8" t="n"/>
+      <c r="L111" s="8" t="n"/>
+      <c r="M111" s="8" t="n"/>
+      <c r="N111" s="9" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>Infrastructure provider (AWS, Azure, Local partner, Customer)</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="inlineStr">
+        <is>
+          <t>Azure</t>
+        </is>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>Local partner</t>
+        </is>
+      </c>
+      <c r="F112" s="10" t="inlineStr">
+        <is>
+          <t>"Customer" means the broker hosts itself: no infrastructure fee.</t>
+        </is>
+      </c>
+      <c r="G112" s="8" t="n"/>
+      <c r="H112" s="8" t="n"/>
+      <c r="I112" s="8" t="n"/>
+      <c r="J112" s="8" t="n"/>
+      <c r="K112" s="8" t="n"/>
+      <c r="L112" s="8" t="n"/>
+      <c r="M112" s="8" t="n"/>
+      <c r="N112" s="9" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>24x7 Severity 1 support (Yes/No)</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D113" s="12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F113" s="10" t="inlineStr">
+        <is>
+          <t>Optional.</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="n"/>
+      <c r="H113" s="8" t="n"/>
+      <c r="I113" s="8" t="n"/>
+      <c r="J113" s="8" t="n"/>
+      <c r="K113" s="8" t="n"/>
+      <c r="L113" s="8" t="n"/>
+      <c r="M113" s="8" t="n"/>
+      <c r="N113" s="9" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>Extra training days</t>
+        </is>
+      </c>
+      <c r="B114" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D114" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F114" s="10" t="inlineStr">
+        <is>
+          <t>Beyond the days included for the tier.</t>
+        </is>
+      </c>
+      <c r="G114" s="8" t="n"/>
+      <c r="H114" s="8" t="n"/>
+      <c r="I114" s="8" t="n"/>
+      <c r="J114" s="8" t="n"/>
+      <c r="K114" s="8" t="n"/>
+      <c r="L114" s="8" t="n"/>
+      <c r="M114" s="8" t="n"/>
+      <c r="N114" s="9" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>Extra legacy data sources to migrate</t>
+        </is>
+      </c>
+      <c r="B115" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F115" s="10" t="inlineStr">
+        <is>
+          <t>Beyond the standard templates.</t>
+        </is>
+      </c>
+      <c r="G115" s="8" t="n"/>
+      <c r="H115" s="8" t="n"/>
+      <c r="I115" s="8" t="n"/>
+      <c r="J115" s="8" t="n"/>
+      <c r="K115" s="8" t="n"/>
+      <c r="L115" s="8" t="n"/>
+      <c r="M115" s="8" t="n"/>
+      <c r="N115" s="9" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="10" t="inlineStr">
         <is>
           <t>Additional standard integrations</t>
         </is>
       </c>
-      <c r="B106" s="14" t="n">
+      <c r="B116" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="C106" s="14" t="n">
+      <c r="C116" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D106" s="14" t="n">
+      <c r="D116" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F106" s="10" t="inlineStr">
+      <c r="F116" s="10" t="inlineStr">
         <is>
           <t>One-time.</t>
         </is>
       </c>
-      <c r="G106" s="8" t="n"/>
-      <c r="H106" s="8" t="n"/>
-      <c r="I106" s="8" t="n"/>
-      <c r="J106" s="8" t="n"/>
-      <c r="K106" s="8" t="n"/>
-      <c r="L106" s="8" t="n"/>
-      <c r="M106" s="8" t="n"/>
-      <c r="N106" s="9" t="n"/>
+      <c r="G116" s="8" t="n"/>
+      <c r="H116" s="8" t="n"/>
+      <c r="I116" s="8" t="n"/>
+      <c r="J116" s="8" t="n"/>
+      <c r="K116" s="8" t="n"/>
+      <c r="L116" s="8" t="n"/>
+      <c r="M116" s="8" t="n"/>
+      <c r="N116" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="74">
-    <mergeCell ref="E36:N36"/>
+  <mergeCells count="84">
     <mergeCell ref="D59:N59"/>
-    <mergeCell ref="D50:N50"/>
-    <mergeCell ref="F104:N104"/>
+    <mergeCell ref="F86:N86"/>
+    <mergeCell ref="F80:N80"/>
     <mergeCell ref="D60:N60"/>
-    <mergeCell ref="F76:N76"/>
-    <mergeCell ref="F95:N95"/>
-    <mergeCell ref="D19:N19"/>
-    <mergeCell ref="D63:N63"/>
-    <mergeCell ref="F94:N94"/>
-    <mergeCell ref="D10:N10"/>
-    <mergeCell ref="F101:N101"/>
-    <mergeCell ref="F70:N70"/>
-    <mergeCell ref="D81:N81"/>
-    <mergeCell ref="D46:N46"/>
-    <mergeCell ref="D84:N84"/>
-    <mergeCell ref="F75:N75"/>
-    <mergeCell ref="F106:N106"/>
-    <mergeCell ref="D80:N80"/>
-    <mergeCell ref="E41:N41"/>
-    <mergeCell ref="D65:N65"/>
     <mergeCell ref="D45:N45"/>
-    <mergeCell ref="F100:N100"/>
-    <mergeCell ref="F72:N72"/>
-    <mergeCell ref="E37:N37"/>
     <mergeCell ref="D6:N6"/>
-    <mergeCell ref="D52:N52"/>
-    <mergeCell ref="H92:N92"/>
-    <mergeCell ref="D86:N86"/>
-    <mergeCell ref="D11:N11"/>
-    <mergeCell ref="D49:N49"/>
-    <mergeCell ref="D57:N57"/>
-    <mergeCell ref="H91:N91"/>
-    <mergeCell ref="F102:N102"/>
-    <mergeCell ref="F71:N71"/>
-    <mergeCell ref="D13:N13"/>
+    <mergeCell ref="F81:N81"/>
+    <mergeCell ref="D95:N95"/>
     <mergeCell ref="F105:N105"/>
+    <mergeCell ref="D70:N70"/>
     <mergeCell ref="E42:N42"/>
     <mergeCell ref="D48:N48"/>
+    <mergeCell ref="D7:N7"/>
+    <mergeCell ref="D72:N72"/>
+    <mergeCell ref="D62:N62"/>
+    <mergeCell ref="D56:N56"/>
+    <mergeCell ref="D71:N71"/>
+    <mergeCell ref="D58:N58"/>
+    <mergeCell ref="D64:N64"/>
+    <mergeCell ref="D73:N73"/>
+    <mergeCell ref="D51:N51"/>
+    <mergeCell ref="F83:N83"/>
+    <mergeCell ref="D50:N50"/>
+    <mergeCell ref="F85:N85"/>
+    <mergeCell ref="D19:N19"/>
+    <mergeCell ref="D90:N90"/>
+    <mergeCell ref="F109:N109"/>
+    <mergeCell ref="E41:N41"/>
+    <mergeCell ref="D77:N77"/>
+    <mergeCell ref="D11:N11"/>
+    <mergeCell ref="F111:N111"/>
+    <mergeCell ref="D13:N13"/>
+    <mergeCell ref="D61:N61"/>
+    <mergeCell ref="D75:N75"/>
+    <mergeCell ref="D53:N53"/>
+    <mergeCell ref="D47:N47"/>
+    <mergeCell ref="E35:N35"/>
+    <mergeCell ref="A32:N32"/>
+    <mergeCell ref="D9:N9"/>
+    <mergeCell ref="D15:N15"/>
+    <mergeCell ref="H100:N100"/>
+    <mergeCell ref="E36:N36"/>
+    <mergeCell ref="F114:N114"/>
+    <mergeCell ref="D63:N63"/>
+    <mergeCell ref="D10:N10"/>
+    <mergeCell ref="F110:N110"/>
+    <mergeCell ref="D65:N65"/>
+    <mergeCell ref="E37:N37"/>
+    <mergeCell ref="D52:N52"/>
+    <mergeCell ref="F115:N115"/>
+    <mergeCell ref="D49:N49"/>
+    <mergeCell ref="D76:N76"/>
+    <mergeCell ref="H103:N103"/>
     <mergeCell ref="D17:N17"/>
-    <mergeCell ref="D61:N61"/>
-    <mergeCell ref="D53:N53"/>
+    <mergeCell ref="D91:N91"/>
     <mergeCell ref="D66:N66"/>
-    <mergeCell ref="H93:N93"/>
+    <mergeCell ref="D93:N93"/>
+    <mergeCell ref="D12:N12"/>
+    <mergeCell ref="F112:N112"/>
+    <mergeCell ref="D92:N92"/>
+    <mergeCell ref="D67:N67"/>
+    <mergeCell ref="D5:N5"/>
+    <mergeCell ref="D14:N14"/>
+    <mergeCell ref="D94:N94"/>
+    <mergeCell ref="H99:N99"/>
+    <mergeCell ref="D69:N69"/>
+    <mergeCell ref="F104:N104"/>
+    <mergeCell ref="F113:N113"/>
+    <mergeCell ref="H101:N101"/>
+    <mergeCell ref="D46:N46"/>
+    <mergeCell ref="D96:N96"/>
+    <mergeCell ref="D57:N57"/>
+    <mergeCell ref="H102:N102"/>
+    <mergeCell ref="F82:N82"/>
     <mergeCell ref="E39:N39"/>
     <mergeCell ref="D16:N16"/>
-    <mergeCell ref="D47:N47"/>
-    <mergeCell ref="F98:N98"/>
-    <mergeCell ref="D7:N7"/>
-    <mergeCell ref="E35:N35"/>
     <mergeCell ref="E38:N38"/>
-    <mergeCell ref="D62:N62"/>
-    <mergeCell ref="A32:N32"/>
-    <mergeCell ref="F73:N73"/>
     <mergeCell ref="D18:N18"/>
-    <mergeCell ref="D56:N56"/>
-    <mergeCell ref="H89:N89"/>
-    <mergeCell ref="D9:N9"/>
-    <mergeCell ref="D12:N12"/>
-    <mergeCell ref="D58:N58"/>
+    <mergeCell ref="F116:N116"/>
     <mergeCell ref="D8:N8"/>
-    <mergeCell ref="D83:N83"/>
-    <mergeCell ref="F103:N103"/>
-    <mergeCell ref="D64:N64"/>
-    <mergeCell ref="D15:N15"/>
-    <mergeCell ref="D82:N82"/>
-    <mergeCell ref="F99:N99"/>
-    <mergeCell ref="D67:N67"/>
-    <mergeCell ref="D5:N5"/>
-    <mergeCell ref="D51:N51"/>
-    <mergeCell ref="F74:N74"/>
-    <mergeCell ref="D14:N14"/>
-    <mergeCell ref="D85:N85"/>
-    <mergeCell ref="H90:N90"/>
+    <mergeCell ref="D74:N74"/>
+    <mergeCell ref="F108:N108"/>
+    <mergeCell ref="D68:N68"/>
+    <mergeCell ref="F84:N84"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="B102:D102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B112:D112" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"AWS,Azure,Local partner,Customer"</formula1>
     </dataValidation>
-    <dataValidation sqref="B103:D103" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B113:D113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10435,19 +10755,19 @@
         </is>
       </c>
       <c r="D5" s="27">
-        <f>ROUND(Inputs!B90*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!B100*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="E5" s="27">
-        <f>ROUND(Inputs!C90*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!C100*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="F5" s="27">
-        <f>ROUND(Inputs!D90*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!D100*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="G5" s="27">
-        <f>ROUND(Inputs!E90*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!E100*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="H5" s="24">
@@ -10455,7 +10775,7 @@
         <v/>
       </c>
       <c r="I5" s="24">
-        <f>ROUND(Inputs!G90*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!G100*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="J5" s="20">
@@ -10492,19 +10812,19 @@
         </is>
       </c>
       <c r="D6" s="27">
-        <f>ROUND(Inputs!B91*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!B101*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="E6" s="27">
-        <f>ROUND(Inputs!C91*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!C101*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="F6" s="27">
-        <f>ROUND(Inputs!D91*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!D101*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="G6" s="27">
-        <f>ROUND(Inputs!E91*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!E101*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="H6" s="24">
@@ -10512,7 +10832,7 @@
         <v/>
       </c>
       <c r="I6" s="24">
-        <f>ROUND(Inputs!G91*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!G101*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="J6" s="20">
@@ -10545,19 +10865,19 @@
         </is>
       </c>
       <c r="D7" s="27">
-        <f>ROUND(Inputs!B92*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!B102*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="E7" s="27">
-        <f>ROUND(Inputs!C92*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!C102*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="F7" s="27">
-        <f>ROUND(Inputs!D92*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!D102*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="G7" s="27">
-        <f>ROUND(Inputs!E92*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!E102*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="H7" s="24">
@@ -10565,7 +10885,7 @@
         <v/>
       </c>
       <c r="I7" s="24">
-        <f>ROUND(Inputs!G92*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!G102*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="J7" s="20">
@@ -10598,19 +10918,19 @@
         </is>
       </c>
       <c r="D8" s="27">
-        <f>ROUND(Inputs!B93*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!B103*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="E8" s="27">
-        <f>ROUND(Inputs!C93*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!C103*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="F8" s="27">
-        <f>ROUND(Inputs!D93*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!D103*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="G8" s="27">
-        <f>ROUND(Inputs!E93*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!E103*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="H8" s="24">
@@ -10618,7 +10938,7 @@
         <v/>
       </c>
       <c r="I8" s="24">
-        <f>ROUND(Inputs!G93*1*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!G103*1*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="J8" s="20">
@@ -10651,19 +10971,19 @@
         </is>
       </c>
       <c r="D9" s="27">
-        <f>ROUND(Inputs!B90*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!B100*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="E9" s="27">
-        <f>ROUND(Inputs!C90*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!C100*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="F9" s="27">
-        <f>ROUND(Inputs!D90*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!D100*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="G9" s="27">
-        <f>ROUND(Inputs!E90*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!E100*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="H9" s="24">
@@ -10671,7 +10991,7 @@
         <v/>
       </c>
       <c r="I9" s="24">
-        <f>ROUND(Inputs!G90*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!G100*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="J9" s="20">
@@ -10708,19 +11028,19 @@
         </is>
       </c>
       <c r="D10" s="27">
-        <f>ROUND(Inputs!B91*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!B101*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="E10" s="27">
-        <f>ROUND(Inputs!C91*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!C101*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="F10" s="27">
-        <f>ROUND(Inputs!D91*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!D101*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="G10" s="27">
-        <f>ROUND(Inputs!E91*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!E101*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="H10" s="24">
@@ -10728,7 +11048,7 @@
         <v/>
       </c>
       <c r="I10" s="24">
-        <f>ROUND(Inputs!G91*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!G101*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="J10" s="20">
@@ -10761,19 +11081,19 @@
         </is>
       </c>
       <c r="D11" s="27">
-        <f>ROUND(Inputs!B92*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!B102*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="E11" s="27">
-        <f>ROUND(Inputs!C92*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!C102*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="F11" s="27">
-        <f>ROUND(Inputs!D92*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!D102*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="G11" s="27">
-        <f>ROUND(Inputs!E92*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!E102*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="H11" s="24">
@@ -10781,7 +11101,7 @@
         <v/>
       </c>
       <c r="I11" s="24">
-        <f>ROUND(Inputs!G92*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!G102*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="J11" s="20">
@@ -10814,19 +11134,19 @@
         </is>
       </c>
       <c r="D12" s="27">
-        <f>ROUND(Inputs!B93*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!B103*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="E12" s="27">
-        <f>ROUND(Inputs!C93*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!C103*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="F12" s="27">
-        <f>ROUND(Inputs!D93*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!D103*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="G12" s="27">
-        <f>ROUND(Inputs!E93*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!E103*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="H12" s="24">
@@ -10834,7 +11154,7 @@
         <v/>
       </c>
       <c r="I12" s="24">
-        <f>ROUND(Inputs!G93*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!G103*Azure_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="J12" s="20">
@@ -10867,19 +11187,19 @@
         </is>
       </c>
       <c r="D13" s="27">
-        <f>ROUND(Inputs!B90*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!B100*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="E13" s="27">
-        <f>ROUND(Inputs!C90*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!C100*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="F13" s="27">
-        <f>ROUND(Inputs!D90*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!D100*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="G13" s="27">
-        <f>ROUND(Inputs!E90*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!E100*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="H13" s="24">
@@ -10887,7 +11207,7 @@
         <v/>
       </c>
       <c r="I13" s="24">
-        <f>ROUND(Inputs!G90*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!G100*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="J13" s="20">
@@ -10924,19 +11244,19 @@
         </is>
       </c>
       <c r="D14" s="27">
-        <f>ROUND(Inputs!B91*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!B101*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="E14" s="27">
-        <f>ROUND(Inputs!C91*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!C101*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="F14" s="27">
-        <f>ROUND(Inputs!D91*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!D101*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="G14" s="27">
-        <f>ROUND(Inputs!E91*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!E101*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="H14" s="24">
@@ -10944,7 +11264,7 @@
         <v/>
       </c>
       <c r="I14" s="24">
-        <f>ROUND(Inputs!G91*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!G101*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="J14" s="20">
@@ -10977,19 +11297,19 @@
         </is>
       </c>
       <c r="D15" s="27">
-        <f>ROUND(Inputs!B92*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!B102*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="E15" s="27">
-        <f>ROUND(Inputs!C92*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!C102*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="F15" s="27">
-        <f>ROUND(Inputs!D92*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!D102*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="G15" s="27">
-        <f>ROUND(Inputs!E92*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!E102*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="H15" s="24">
@@ -10997,7 +11317,7 @@
         <v/>
       </c>
       <c r="I15" s="24">
-        <f>ROUND(Inputs!G92*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!G102*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="J15" s="20">
@@ -11030,19 +11350,19 @@
         </is>
       </c>
       <c r="D16" s="27">
-        <f>ROUND(Inputs!B93*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!B103*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="E16" s="27">
-        <f>ROUND(Inputs!C93*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!C103*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="F16" s="27">
-        <f>ROUND(Inputs!D93*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!D103*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="G16" s="27">
-        <f>ROUND(Inputs!E93*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!E103*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="H16" s="24">
@@ -11050,7 +11370,7 @@
         <v/>
       </c>
       <c r="I16" s="24">
-        <f>ROUND(Inputs!G93*Local_Factor*FX*(1+Infra_Margin),-3)</f>
+        <f>ROUND(Inputs!G103*Local_Factor*FX*(1+Infra_Margin),-3)</f>
         <v/>
       </c>
       <c r="J16" s="20">
@@ -12113,7 +12433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -12367,16 +12687,16 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Connector go-live with a partner</t>
+          <t>Additional line of business after go-live</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>per connector</t>
+          <t>per line</t>
         </is>
       </c>
       <c r="C12" s="34">
-        <f>ROUND(Conn_Golive_Days*Blended/Round_To,0)*Round_To</f>
+        <f>ROUND(Days_per_LOB*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="D12" s="20">
@@ -12384,28 +12704,28 @@
         <v/>
       </c>
       <c r="E12" s="25">
-        <f>Conn_Golive_Days</f>
+        <f>Days_per_LOB</f>
         <v/>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>To confirm by management. A delivered connector (SMS gateway, CTPL provider, one insurer, one bank file layout, BIR EIS) taken live; the partner certifies its own side.</t>
+          <t>Product set-up, rating and tax lines, templates, testing.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Activation of the AML/CFT toolkit</t>
+          <t>New report or document template</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>one-time</t>
+          <t>per item (typical)</t>
         </is>
       </c>
       <c r="C13" s="34">
-        <f>ROUND(AML_Act_Days*Blended/Round_To,0)*Round_To</f>
+        <f>ROUND(Report_Days*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="D13" s="20">
@@ -12413,144 +12733,98 @@
         <v/>
       </c>
       <c r="E13" s="25">
-        <f>AML_Act_Days</f>
+        <f>Report_Days</f>
         <v/>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>To confirm by management. The toolkit is included in the software; this is the set-up effort. The compliance officer confirms the settings and loads the lists.</t>
+          <t>Small CR band; firm price after the impact note.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Activation of the IC compliance registers</t>
+          <t>On-site day (Metro Manila)</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>one-time</t>
+          <t>per consultant day</t>
         </is>
       </c>
       <c r="C14" s="34">
-        <f>ROUND(IC_Act_Days*Blended/Round_To,0)*Round_To</f>
+        <f>Rate_Onsite</f>
         <v/>
       </c>
       <c r="D14" s="20">
         <f>C14/FX</f>
         <v/>
       </c>
-      <c r="E14" s="25">
-        <f>IC_Act_Days</f>
-        <v/>
-      </c>
+      <c r="E14" s="25" t="inlineStr"/>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>To confirm by management. Registers included in the software; this is the set-up effort.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Activation of the BIR pack</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>one-time</t>
-        </is>
-      </c>
-      <c r="C15" s="34">
-        <f>ROUND(BIR_Act_Days*Blended/Round_To,0)*Round_To</f>
-        <v/>
-      </c>
-      <c r="D15" s="20">
-        <f>C15/FX</f>
-        <v/>
-      </c>
-      <c r="E15" s="25">
-        <f>BIR_Act_Days</f>
-        <v/>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>To confirm by management. BIR forms, EOPT invoices, EIS and CAS pack included in the software; the tax adviser confirms the treatment.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>Dealer programme set-up</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>per programme</t>
-        </is>
-      </c>
-      <c r="C16" s="34">
-        <f>ROUND(Dealer_Prog_Days*Blended/Round_To,0)*Round_To</f>
-        <v/>
-      </c>
-      <c r="D16" s="20">
-        <f>C16/FX</f>
-        <v/>
-      </c>
-      <c r="E16" s="25">
-        <f>Dealer_Prog_Days</f>
-        <v/>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>To confirm by management. Dealer programmes are included in the software; this is the set-up of one programme.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Client brand pack</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>per pack</t>
-        </is>
-      </c>
-      <c r="C17" s="34">
-        <f>ROUND(Brand_Pack_Days*Blended/Round_To,0)*Round_To</f>
-        <v/>
-      </c>
-      <c r="D17" s="20">
-        <f>C17/FX</f>
-        <v/>
-      </c>
-      <c r="E17" s="25">
-        <f>Brand_Pack_Days</f>
-        <v/>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>To confirm by management. Branding is included in the software; a pack carrying third-party marks needs the owner's written permission.</t>
+          <t>Outside Metro Manila: travel, lodging and meals at cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Optional modules and partner services (confirmed by management on 04 October 2026): man-days x blended rate, rounded to PHP 10,000; the regulator's or partner's own fees are not included</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Price (PHP)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Price (USD)</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Man-days</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Scope</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Additional line of business after go-live</t>
+          <t>Connector go-live with a partner</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>per line</t>
+          <t>per connector</t>
         </is>
       </c>
       <c r="C18" s="34">
-        <f>ROUND(Days_per_LOB*Blended/Round_To,0)*Round_To</f>
+        <f>ROUND(Conn_Golive_Days*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="D18" s="20">
@@ -12558,28 +12832,28 @@
         <v/>
       </c>
       <c r="E18" s="25">
-        <f>Days_per_LOB</f>
+        <f>Conn_Golive_Days</f>
         <v/>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Product set-up, rating and tax lines, templates, testing.</t>
+          <t>A delivered connector (SMS gateway, CTPL provider, one insurer, one bank file layout, BIR EIS) taken live: configuration, credential check, live test, support of the partner acceptance; the partner certifies its own side.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>New report or document template</t>
+          <t>Activation of the AML/CFT toolkit</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>per item (typical)</t>
+          <t>one-time</t>
         </is>
       </c>
       <c r="C19" s="34">
-        <f>ROUND(Report_Days*Blended/Round_To,0)*Round_To</f>
+        <f>ROUND(AML_Act_Days*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="D19" s="20">
@@ -12587,179 +12861,571 @@
         <v/>
       </c>
       <c r="E19" s="25">
-        <f>Report_Days</f>
+        <f>AML_Act_Days</f>
         <v/>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Small CR band; firm price after the impact note.</t>
+          <t>The toolkit is included in the software; this is the set-up effort: risk factors and rules workshop, settings, first list loads, provider set-up, AMLC test file. The compliance officer confirms the settings and loads the lists.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>On-site day (Metro Manila)</t>
+          <t>Activation of the IC compliance registers</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>per consultant day</t>
+          <t>one-time</t>
         </is>
       </c>
       <c r="C20" s="34">
-        <f>Rate_Onsite</f>
+        <f>ROUND(IC_Act_Days*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="D20" s="20">
         <f>C20/FX</f>
         <v/>
       </c>
-      <c r="E20" s="25" t="inlineStr"/>
+      <c r="E20" s="25">
+        <f>IC_Act_Days</f>
+        <v/>
+      </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Outside Metro Manila: travel, lodging and meals at cost.</t>
+          <t>Registers included in the software; this is the set-up effort: licence and fit and proper register load, insurer certificates, complaints and breach settings, IC statement account mapping.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="10">
-        <f>"24x7 Severity 1 support, "&amp;Inputs!A28&amp;" tier"</f>
-        <v/>
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Activation of the BIR pack</t>
+        </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>per year, Year 1</t>
+          <t>one-time</t>
         </is>
       </c>
       <c r="C21" s="34">
-        <f>Inputs!L28</f>
+        <f>ROUND(BIR_Act_Days*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="D21" s="20">
         <f>C21/FX</f>
         <v/>
       </c>
+      <c r="E21" s="25">
+        <f>BIR_Act_Days</f>
+        <v/>
+      </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Standard support is business hours (Monday to Friday, 08:00 to 18:00 Philippine time, excluding holidays). This adds round-the-clock response to Severity 1 incidents (production down or a core process stopped for all users).</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="10">
-        <f>"24x7 Severity 1 support, "&amp;Inputs!A29&amp;" tier"</f>
-        <v/>
+          <t>BIR forms, EOPT invoices, EIS and CAS pack included in the software; this is the set-up effort: BIR and EOPT invoice settings, ATC mapping, DAT file dry run, CAS books pack. The tax adviser confirms the treatment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Dealer programme set-up</t>
+        </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>per year, Year 1</t>
+          <t>per programme</t>
         </is>
       </c>
       <c r="C22" s="34">
-        <f>Inputs!L29</f>
+        <f>ROUND(Dealer_Prog_Days*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="D22" s="20">
         <f>C22/FX</f>
         <v/>
       </c>
-      <c r="F22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="10">
-        <f>"24x7 Severity 1 support, "&amp;Inputs!A30&amp;" tier"</f>
-        <v/>
+      <c r="E22" s="25">
+        <f>Dealer_Prog_Days</f>
+        <v/>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Dealer programmes are included in the software; this is the set-up of one programme: channels, rates, subsidy, bank letter and the first upload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Client brand pack</t>
+        </is>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>per year, Year 1</t>
+          <t>per pack</t>
         </is>
       </c>
       <c r="C23" s="34">
-        <f>Inputs!L30</f>
+        <f>ROUND(Brand_Pack_Days*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="D23" s="20">
         <f>C23/FX</f>
         <v/>
       </c>
-      <c r="F23" s="5" t="inlineStr"/>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="10">
-        <f>"24x7 Severity 1 support, "&amp;Inputs!A31&amp;" tier"</f>
-        <v/>
+      <c r="E23" s="25">
+        <f>Brand_Pack_Days</f>
+        <v/>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Branding is included in the software; this is one pack: theme, sign-in picture, document and e-mail branding, e-signature mapping, exported pack. A pack carrying third-party marks needs the owner's written permission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>AMLC reporting file validation and portal test</t>
+        </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>per year, Year 1</t>
+          <t>one-time</t>
         </is>
       </c>
       <c r="C24" s="34">
-        <f>Inputs!L31</f>
+        <f>ROUND(AMLC_Val_Days*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="D24" s="20">
         <f>C24/FX</f>
         <v/>
       </c>
-      <c r="F24" s="5" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="E24" s="25">
+        <f>AMLC_Val_Days</f>
+        <v/>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>CTR and STR layout, institution and transaction codes confirmed with the AMLC, test file accepted in the AMLC portal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>IC annual statement form alignment</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>one-time</t>
+        </is>
+      </c>
+      <c r="C25" s="34">
+        <f>ROUND(IC_Form_Days*Blended/Round_To,0)*Round_To</f>
+        <v/>
+      </c>
+      <c r="D25" s="20">
+        <f>C25/FX</f>
+        <v/>
+      </c>
+      <c r="E25" s="25">
+        <f>IC_Form_Days</f>
+        <v/>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>The accountant working paper mapped to the IC form set in force for the year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>EOPT invoicing review with the broker tax adviser</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>one-time</t>
+        </is>
+      </c>
+      <c r="C26" s="34">
+        <f>ROUND(EOPT_Rev_Days*Blended/Round_To,0)*Round_To</f>
+        <v/>
+      </c>
+      <c r="D26" s="20">
+        <f>C26/FX</f>
+        <v/>
+      </c>
+      <c r="E26" s="25">
+        <f>EOPT_Rev_Days</f>
+        <v/>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Registered invoice documents, supplementary wording, VAT treatment of each commission stream, ATP or CAS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>BIR CAS registration support</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>one-time</t>
+        </is>
+      </c>
+      <c r="C27" s="34">
+        <f>ROUND(CAS_Reg_Days*Blended/Round_To,0)*Round_To</f>
+        <v/>
+      </c>
+      <c r="D27" s="20">
+        <f>C27/FX</f>
+        <v/>
+      </c>
+      <c r="E27" s="25">
+        <f>CAS_Reg_Days</f>
+        <v/>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Books, system description and the Permit to Use filing prepared with the broker; the broker files.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>BIR EIS enrolment and certification</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>one-time</t>
+        </is>
+      </c>
+      <c r="C28" s="34">
+        <f>ROUND(EIS_Enrol_Days*Blended/Round_To,0)*Round_To</f>
+        <v/>
+      </c>
+      <c r="D28" s="20">
+        <f>C28/FX</f>
+        <v/>
+      </c>
+      <c r="E28" s="25">
+        <f>EIS_Enrol_Days</f>
+        <v/>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>EIS enrolment, signing certificate, final field list, production endpoint and certification of the connector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>CTPL authentication and LTO interface certification</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>one-time</t>
+        </is>
+      </c>
+      <c r="C29" s="34">
+        <f>ROUND(CTPL_Cert_Days*Blended/Round_To,0)*Round_To</f>
+        <v/>
+      </c>
+      <c r="D29" s="20">
+        <f>C29/FX</f>
+        <v/>
+      </c>
+      <c r="E29" s="25">
+        <f>CTPL_Cert_Days</f>
+        <v/>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Acceptance of the live requests by the accredited provider, COC series, LTO interface where the provider does not transmit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Insurer API onboarding, per insurer</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>per insurer</t>
+        </is>
+      </c>
+      <c r="C30" s="34">
+        <f>ROUND(Insurer_Onb_Days*Blended/Round_To,0)*Round_To</f>
+        <v/>
+      </c>
+      <c r="D30" s="20">
+        <f>C30/FX</f>
+        <v/>
+      </c>
+      <c r="E30" s="25">
+        <f>Insurer_Onb_Days</f>
+        <v/>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Endpoint, credentials, field mapping and live test with one insurer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Bank payment file certification, per bank</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>per bank</t>
+        </is>
+      </c>
+      <c r="C31" s="34">
+        <f>ROUND(Bank_Cert_Days*Blended/Round_To,0)*Round_To</f>
+        <v/>
+      </c>
+      <c r="D31" s="20">
+        <f>C31/FX</f>
+        <v/>
+      </c>
+      <c r="E31" s="25">
+        <f>Bank_Cert_Days</f>
+        <v/>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Layout validated against the bank specification and a test file accepted by the bank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>SMS or Viber gateway activation</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>one-time</t>
+        </is>
+      </c>
+      <c r="C32" s="34">
+        <f>ROUND(SMS_Act_Days*Blended/Round_To,0)*Round_To</f>
+        <v/>
+      </c>
+      <c r="D32" s="20">
+        <f>C32/FX</f>
+        <v/>
+      </c>
+      <c r="E32" s="25">
+        <f>SMS_Act_Days</f>
+        <v/>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>Sender name or short code, live credentials, templates and consent check tested with the gateway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Screening list provider onboarding</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>one-time</t>
+        </is>
+      </c>
+      <c r="C33" s="34">
+        <f>ROUND(Screen_Prov_Days*Blended/Round_To,0)*Round_To</f>
+        <v/>
+      </c>
+      <c r="D33" s="20">
+        <f>C33/FX</f>
+        <v/>
+      </c>
+      <c r="E33" s="25">
+        <f>Screen_Prov_Days</f>
+        <v/>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Provider contract data, API key, adapter test and first screening run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>24x7 Severity 1 support</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="10">
+        <f>"24x7 Severity 1 support, "&amp;Inputs!A28&amp;" tier"</f>
+        <v/>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>per year, Year 1</t>
+        </is>
+      </c>
+      <c r="C36" s="34">
+        <f>Inputs!L28</f>
+        <v/>
+      </c>
+      <c r="D36" s="20">
+        <f>C36/FX</f>
+        <v/>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Standard support is business hours (Monday to Friday, 08:00 to 18:00 Philippine time, excluding holidays). This adds round-the-clock response to Severity 1 incidents (production down or a core process stopped for all users).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="10">
+        <f>"24x7 Severity 1 support, "&amp;Inputs!A29&amp;" tier"</f>
+        <v/>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>per year, Year 1</t>
+        </is>
+      </c>
+      <c r="C37" s="34">
+        <f>Inputs!L29</f>
+        <v/>
+      </c>
+      <c r="D37" s="20">
+        <f>C37/FX</f>
+        <v/>
+      </c>
+      <c r="F37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="10">
+        <f>"24x7 Severity 1 support, "&amp;Inputs!A30&amp;" tier"</f>
+        <v/>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>per year, Year 1</t>
+        </is>
+      </c>
+      <c r="C38" s="34">
+        <f>Inputs!L30</f>
+        <v/>
+      </c>
+      <c r="D38" s="20">
+        <f>C38/FX</f>
+        <v/>
+      </c>
+      <c r="F38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="10">
+        <f>"24x7 Severity 1 support, "&amp;Inputs!A31&amp;" tier"</f>
+        <v/>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>per year, Year 1</t>
+        </is>
+      </c>
+      <c r="C39" s="34">
+        <f>Inputs!L31</f>
+        <v/>
+      </c>
+      <c r="D39" s="20">
+        <f>C39/FX</f>
+        <v/>
+      </c>
+      <c r="F39" s="5" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>Included in the standard implementation (no extra charge)</t>
         </is>
       </c>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="26" t="inlineStr">
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="7" t="n"/>
+      <c r="E41" s="7" t="n"/>
+      <c r="F41" s="7" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="26" t="inlineStr">
         <is>
           <t>Configuration of the company, branches, users and roles, insurers, commission rates, chart of accounts, banks and the included lines of business.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="26" t="inlineStr">
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="26" t="inlineStr">
         <is>
           <t>Data load using the standard upload templates (about 50 templates in docs/package/05_Delivery/Upload_Templates), with the broker supplying clean data.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="26" t="inlineStr">
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="26" t="inlineStr">
         <is>
           <t>Training days included for the tier (train-the-trainer), UAT support, go-live support and 4 weeks of hypercare.</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="26" t="inlineStr">
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="26" t="inlineStr">
         <is>
           <t>Set-up of the environment set of the tier (Dev, UAT and Production; SIT as well for Large and Enterprise) and of Pre-Prod for the go-live rehearsal; hosting is billed separately. Deployment guidance when the broker hosts.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="26" t="inlineStr">
-        <is>
-          <t>Every module is included in the software price, including the AML/CFT toolkit, the IC compliance registers, the BIR pack, the integration framework with its connectors, dealer programmes and branding. Their activation and each connector go-live are the optional lines above (to confirm by management).</t>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>Every module is included in the software price, including the AML/CFT toolkit, the IC compliance registers, the BIR pack, the integration framework with its connectors, dealer programmes and branding. Their activation, each connector go-live and the regulator and partner services are the optional modules and partner services above, confirmed by management on 04 October 2026 as add-on items; no package total changes.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A43:F43"/>
   </mergeCells>
   <printOptions gridLines="0"/>
   <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12810,7 +13476,7 @@
     </row>
     <row r="4">
       <c r="A4" s="6">
-        <f>"Example 1: "&amp;Inputs!$B$99&amp;", "&amp;Inputs!$B$100&amp;" users, "&amp;Inputs!$B$101&amp;" lines of business, tier "&amp;INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))&amp;", hosting: "&amp;Inputs!$B$102</f>
+        <f>"Example 1: "&amp;Inputs!$B$109&amp;", "&amp;Inputs!$B$110&amp;" users, "&amp;Inputs!$B$111&amp;" lines of business, tier "&amp;INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))&amp;", hosting: "&amp;Inputs!$B$112</f>
         <v/>
       </c>
       <c r="B4" s="7" t="n"/>
@@ -12877,7 +13543,7 @@
         </is>
       </c>
       <c r="B7" s="20">
-        <f>ROUND((INDEX(Inputs!$G$28:$G$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))+MAX(0,Inputs!$B$101-INDEX(Inputs!$H$28:$H$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1)))*Days_per_LOB)*Blended/Round_To,0)*Round_To</f>
+        <f>ROUND((INDEX(Inputs!$G$28:$G$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))+MAX(0,Inputs!$B$111-INDEX(Inputs!$H$28:$H$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1)))*Days_per_LOB)*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="C7" s="20" t="n">
@@ -12908,7 +13574,7 @@
         </is>
       </c>
       <c r="B8" s="20">
-        <f>MAX(0,MIN(Inputs!$B$100,Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$D$28+MAX(0,MIN(Inputs!$B$100,Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$D$29+MAX(0,MIN(Inputs!$B$100,Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$D$30+MAX(0,MIN(Inputs!$B$100,Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$D$31</f>
+        <f>MAX(0,MIN(Inputs!$B$110,Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$D$28+MAX(0,MIN(Inputs!$B$110,Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$D$29+MAX(0,MIN(Inputs!$B$110,Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$D$30+MAX(0,MIN(Inputs!$B$110,Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$D$31</f>
         <v/>
       </c>
       <c r="C8" s="20" t="n">
@@ -13042,27 +13708,27 @@
     </row>
     <row r="13">
       <c r="A13" s="10">
-        <f>"Subscription ("&amp;MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1)))&amp;" billable users)"</f>
+        <f>"Subscription ("&amp;MAX(Inputs!$B$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1)))&amp;" billable users)"</f>
         <v/>
       </c>
       <c r="B13" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(1-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$B$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(1-1)</f>
         <v/>
       </c>
       <c r="C13" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(2-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$B$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(2-1)</f>
         <v/>
       </c>
       <c r="D13" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(3-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$B$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(3-1)</f>
         <v/>
       </c>
       <c r="E13" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(4-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$B$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(4-1)</f>
         <v/>
       </c>
       <c r="F13" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(5-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$B$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$B$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$B$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$B$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(5-1)</f>
         <v/>
       </c>
       <c r="G13" s="34">
@@ -13118,27 +13784,27 @@
     </row>
     <row r="16">
       <c r="A16" s="10">
-        <f>"Hosting, environment set and Pre-Prod: "&amp;Inputs!$B$102</f>
+        <f>"Hosting, environment set and Pre-Prod: "&amp;Inputs!$B$112</f>
         <v/>
       </c>
       <c r="B16" s="20">
-        <f>(SUMIFS(Infrastructure!$J$5:$J$20,Infrastructure!$A$5:$A$20,Inputs!$B$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(1-1)</f>
+        <f>(SUMIFS(Infrastructure!$J$5:$J$20,Infrastructure!$A$5:$A$20,Inputs!$B$112,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(1-1)</f>
         <v/>
       </c>
       <c r="C16" s="20">
-        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$B$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(2-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$B$112,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(2-1)</f>
         <v/>
       </c>
       <c r="D16" s="20">
-        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$B$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(3-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$B$112,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(3-1)</f>
         <v/>
       </c>
       <c r="E16" s="20">
-        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$B$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(4-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$B$112,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(4-1)</f>
         <v/>
       </c>
       <c r="F16" s="20">
-        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$B$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(5-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$B$112,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(5-1)</f>
         <v/>
       </c>
       <c r="G16" s="34">
@@ -13157,23 +13823,23 @@
         </is>
       </c>
       <c r="B17" s="20">
-        <f>IF(Inputs!$B$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(1-1),0)</f>
+        <f>IF(Inputs!$B$113="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))*(1+Esc)^(1-1),0)</f>
         <v/>
       </c>
       <c r="C17" s="20">
-        <f>IF(Inputs!$B$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(2-1),0)</f>
+        <f>IF(Inputs!$B$113="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))*(1+Esc)^(2-1),0)</f>
         <v/>
       </c>
       <c r="D17" s="20">
-        <f>IF(Inputs!$B$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(3-1),0)</f>
+        <f>IF(Inputs!$B$113="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))*(1+Esc)^(3-1),0)</f>
         <v/>
       </c>
       <c r="E17" s="20">
-        <f>IF(Inputs!$B$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(4-1),0)</f>
+        <f>IF(Inputs!$B$113="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))*(1+Esc)^(4-1),0)</f>
         <v/>
       </c>
       <c r="F17" s="20">
-        <f>IF(Inputs!$B$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(5-1),0)</f>
+        <f>IF(Inputs!$B$113="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$B$110,Inputs!$B$28:$B$31,1))*(1+Esc)^(5-1),0)</f>
         <v/>
       </c>
       <c r="G17" s="34">
@@ -13192,7 +13858,7 @@
         </is>
       </c>
       <c r="B18" s="20">
-        <f>Inputs!$B$104*Rate_Trainer+ROUND(Mig_Days_Source*Blended/Round_To,0)*Round_To*Inputs!$B$105+ROUND(Int_Std_Days*Blended/Round_To,0)*Round_To*Inputs!$B$106</f>
+        <f>Inputs!$B$114*Rate_Trainer+ROUND(Mig_Days_Source*Blended/Round_To,0)*Round_To*Inputs!$B$115+ROUND(Int_Std_Days*Blended/Round_To,0)*Round_To*Inputs!$B$116</f>
         <v/>
       </c>
       <c r="C18" s="20" t="n">
@@ -13434,7 +14100,7 @@
     </row>
     <row r="27">
       <c r="A27" s="6">
-        <f>"Example 2: "&amp;Inputs!$C$99&amp;", "&amp;Inputs!$C$100&amp;" users, "&amp;Inputs!$C$101&amp;" lines of business, tier "&amp;INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))&amp;", hosting: "&amp;Inputs!$C$102</f>
+        <f>"Example 2: "&amp;Inputs!$C$109&amp;", "&amp;Inputs!$C$110&amp;" users, "&amp;Inputs!$C$111&amp;" lines of business, tier "&amp;INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))&amp;", hosting: "&amp;Inputs!$C$112</f>
         <v/>
       </c>
       <c r="B27" s="7" t="n"/>
@@ -13501,7 +14167,7 @@
         </is>
       </c>
       <c r="B30" s="20">
-        <f>ROUND((INDEX(Inputs!$G$28:$G$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))+MAX(0,Inputs!$C$101-INDEX(Inputs!$H$28:$H$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1)))*Days_per_LOB)*Blended/Round_To,0)*Round_To</f>
+        <f>ROUND((INDEX(Inputs!$G$28:$G$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))+MAX(0,Inputs!$C$111-INDEX(Inputs!$H$28:$H$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1)))*Days_per_LOB)*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="C30" s="20" t="n">
@@ -13532,7 +14198,7 @@
         </is>
       </c>
       <c r="B31" s="20">
-        <f>MAX(0,MIN(Inputs!$C$100,Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$D$28+MAX(0,MIN(Inputs!$C$100,Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$D$29+MAX(0,MIN(Inputs!$C$100,Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$D$30+MAX(0,MIN(Inputs!$C$100,Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$D$31</f>
+        <f>MAX(0,MIN(Inputs!$C$110,Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$D$28+MAX(0,MIN(Inputs!$C$110,Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$D$29+MAX(0,MIN(Inputs!$C$110,Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$D$30+MAX(0,MIN(Inputs!$C$110,Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$D$31</f>
         <v/>
       </c>
       <c r="C31" s="20" t="n">
@@ -13666,27 +14332,27 @@
     </row>
     <row r="36">
       <c r="A36" s="10">
-        <f>"Subscription ("&amp;MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1)))&amp;" billable users)"</f>
+        <f>"Subscription ("&amp;MAX(Inputs!$C$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1)))&amp;" billable users)"</f>
         <v/>
       </c>
       <c r="B36" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(1-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$C$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(1-1)</f>
         <v/>
       </c>
       <c r="C36" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(2-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$C$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(2-1)</f>
         <v/>
       </c>
       <c r="D36" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(3-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$C$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(3-1)</f>
         <v/>
       </c>
       <c r="E36" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(4-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$C$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(4-1)</f>
         <v/>
       </c>
       <c r="F36" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(5-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$C$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$C$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$C$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$C$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(5-1)</f>
         <v/>
       </c>
       <c r="G36" s="34">
@@ -13742,27 +14408,27 @@
     </row>
     <row r="39">
       <c r="A39" s="10">
-        <f>"Hosting, environment set and Pre-Prod: "&amp;Inputs!$C$102</f>
+        <f>"Hosting, environment set and Pre-Prod: "&amp;Inputs!$C$112</f>
         <v/>
       </c>
       <c r="B39" s="20">
-        <f>(SUMIFS(Infrastructure!$J$5:$J$20,Infrastructure!$A$5:$A$20,Inputs!$C$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(1-1)</f>
+        <f>(SUMIFS(Infrastructure!$J$5:$J$20,Infrastructure!$A$5:$A$20,Inputs!$C$112,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(1-1)</f>
         <v/>
       </c>
       <c r="C39" s="20">
-        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$C$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(2-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$C$112,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(2-1)</f>
         <v/>
       </c>
       <c r="D39" s="20">
-        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$C$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(3-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$C$112,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(3-1)</f>
         <v/>
       </c>
       <c r="E39" s="20">
-        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$C$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(4-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$C$112,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(4-1)</f>
         <v/>
       </c>
       <c r="F39" s="20">
-        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$C$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(5-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$C$112,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(5-1)</f>
         <v/>
       </c>
       <c r="G39" s="34">
@@ -13781,23 +14447,23 @@
         </is>
       </c>
       <c r="B40" s="20">
-        <f>IF(Inputs!$C$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(1-1),0)</f>
+        <f>IF(Inputs!$C$113="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))*(1+Esc)^(1-1),0)</f>
         <v/>
       </c>
       <c r="C40" s="20">
-        <f>IF(Inputs!$C$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(2-1),0)</f>
+        <f>IF(Inputs!$C$113="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))*(1+Esc)^(2-1),0)</f>
         <v/>
       </c>
       <c r="D40" s="20">
-        <f>IF(Inputs!$C$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(3-1),0)</f>
+        <f>IF(Inputs!$C$113="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))*(1+Esc)^(3-1),0)</f>
         <v/>
       </c>
       <c r="E40" s="20">
-        <f>IF(Inputs!$C$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(4-1),0)</f>
+        <f>IF(Inputs!$C$113="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))*(1+Esc)^(4-1),0)</f>
         <v/>
       </c>
       <c r="F40" s="20">
-        <f>IF(Inputs!$C$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(5-1),0)</f>
+        <f>IF(Inputs!$C$113="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$C$110,Inputs!$B$28:$B$31,1))*(1+Esc)^(5-1),0)</f>
         <v/>
       </c>
       <c r="G40" s="34">
@@ -13816,7 +14482,7 @@
         </is>
       </c>
       <c r="B41" s="20">
-        <f>Inputs!$C$104*Rate_Trainer+ROUND(Mig_Days_Source*Blended/Round_To,0)*Round_To*Inputs!$C$105+ROUND(Int_Std_Days*Blended/Round_To,0)*Round_To*Inputs!$C$106</f>
+        <f>Inputs!$C$114*Rate_Trainer+ROUND(Mig_Days_Source*Blended/Round_To,0)*Round_To*Inputs!$C$115+ROUND(Int_Std_Days*Blended/Round_To,0)*Round_To*Inputs!$C$116</f>
         <v/>
       </c>
       <c r="C41" s="20" t="n">
@@ -14058,7 +14724,7 @@
     </row>
     <row r="50">
       <c r="A50" s="6">
-        <f>"Example 3: "&amp;Inputs!$D$99&amp;", "&amp;Inputs!$D$100&amp;" users, "&amp;Inputs!$D$101&amp;" lines of business, tier "&amp;INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))&amp;", hosting: "&amp;Inputs!$D$102</f>
+        <f>"Example 3: "&amp;Inputs!$D$109&amp;", "&amp;Inputs!$D$110&amp;" users, "&amp;Inputs!$D$111&amp;" lines of business, tier "&amp;INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))&amp;", hosting: "&amp;Inputs!$D$112</f>
         <v/>
       </c>
       <c r="B50" s="7" t="n"/>
@@ -14125,7 +14791,7 @@
         </is>
       </c>
       <c r="B53" s="20">
-        <f>ROUND((INDEX(Inputs!$G$28:$G$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))+MAX(0,Inputs!$D$101-INDEX(Inputs!$H$28:$H$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1)))*Days_per_LOB)*Blended/Round_To,0)*Round_To</f>
+        <f>ROUND((INDEX(Inputs!$G$28:$G$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))+MAX(0,Inputs!$D$111-INDEX(Inputs!$H$28:$H$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1)))*Days_per_LOB)*Blended/Round_To,0)*Round_To</f>
         <v/>
       </c>
       <c r="C53" s="20" t="n">
@@ -14156,7 +14822,7 @@
         </is>
       </c>
       <c r="B54" s="20">
-        <f>MAX(0,MIN(Inputs!$D$100,Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$D$28+MAX(0,MIN(Inputs!$D$100,Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$D$29+MAX(0,MIN(Inputs!$D$100,Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$D$30+MAX(0,MIN(Inputs!$D$100,Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$D$31</f>
+        <f>MAX(0,MIN(Inputs!$D$110,Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$D$28+MAX(0,MIN(Inputs!$D$110,Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$D$29+MAX(0,MIN(Inputs!$D$110,Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$D$30+MAX(0,MIN(Inputs!$D$110,Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$D$31</f>
         <v/>
       </c>
       <c r="C54" s="20" t="n">
@@ -14290,27 +14956,27 @@
     </row>
     <row r="59">
       <c r="A59" s="10">
-        <f>"Subscription ("&amp;MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1)))&amp;" billable users)"</f>
+        <f>"Subscription ("&amp;MAX(Inputs!$D$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1)))&amp;" billable users)"</f>
         <v/>
       </c>
       <c r="B59" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(1-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$D$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(1-1)</f>
         <v/>
       </c>
       <c r="C59" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(2-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$D$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(2-1)</f>
         <v/>
       </c>
       <c r="D59" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(3-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$D$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(3-1)</f>
         <v/>
       </c>
       <c r="E59" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(4-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$D$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(4-1)</f>
         <v/>
       </c>
       <c r="F59" s="20">
-        <f>(MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$100,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(5-1)</f>
+        <f>(MAX(0,MIN(MAX(Inputs!$D$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))),Inputs!$C$28)-Inputs!$B$28+1)*Inputs!$E$28+MAX(0,MIN(MAX(Inputs!$D$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))),Inputs!$C$29)-Inputs!$B$29+1)*Inputs!$E$29+MAX(0,MIN(MAX(Inputs!$D$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))),Inputs!$C$30)-Inputs!$B$30+1)*Inputs!$E$30+MAX(0,MIN(MAX(Inputs!$D$110,INDEX(Inputs!$F$28:$F$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))),Inputs!$C$31)-Inputs!$B$31+1)*Inputs!$E$31)*12*(1+Esc)^(5-1)</f>
         <v/>
       </c>
       <c r="G59" s="34">
@@ -14366,27 +15032,27 @@
     </row>
     <row r="62">
       <c r="A62" s="10">
-        <f>"Hosting, environment set and Pre-Prod: "&amp;Inputs!$D$102</f>
+        <f>"Hosting, environment set and Pre-Prod: "&amp;Inputs!$D$112</f>
         <v/>
       </c>
       <c r="B62" s="20">
-        <f>(SUMIFS(Infrastructure!$J$5:$J$20,Infrastructure!$A$5:$A$20,Inputs!$D$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(1-1)</f>
+        <f>(SUMIFS(Infrastructure!$J$5:$J$20,Infrastructure!$A$5:$A$20,Inputs!$D$112,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(1-1)</f>
         <v/>
       </c>
       <c r="C62" s="20">
-        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$D$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(2-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$D$112,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(2-1)</f>
         <v/>
       </c>
       <c r="D62" s="20">
-        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$D$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(3-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$D$112,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(3-1)</f>
         <v/>
       </c>
       <c r="E62" s="20">
-        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$D$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(4-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$D$112,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(4-1)</f>
         <v/>
       </c>
       <c r="F62" s="20">
-        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$D$102,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(5-1)</f>
+        <f>(SUMIFS(Infrastructure!$K$5:$K$20,Infrastructure!$A$5:$A$20,Inputs!$D$112,Infrastructure!$B$5:$B$20,INDEX(Inputs!$A$28:$A$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))))*(1+Infra_Esc)^(5-1)</f>
         <v/>
       </c>
       <c r="G62" s="34">
@@ -14405,23 +15071,23 @@
         </is>
       </c>
       <c r="B63" s="20">
-        <f>IF(Inputs!$D$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(1-1),0)</f>
+        <f>IF(Inputs!$D$113="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))*(1+Esc)^(1-1),0)</f>
         <v/>
       </c>
       <c r="C63" s="20">
-        <f>IF(Inputs!$D$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(2-1),0)</f>
+        <f>IF(Inputs!$D$113="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))*(1+Esc)^(2-1),0)</f>
         <v/>
       </c>
       <c r="D63" s="20">
-        <f>IF(Inputs!$D$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(3-1),0)</f>
+        <f>IF(Inputs!$D$113="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))*(1+Esc)^(3-1),0)</f>
         <v/>
       </c>
       <c r="E63" s="20">
-        <f>IF(Inputs!$D$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(4-1),0)</f>
+        <f>IF(Inputs!$D$113="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))*(1+Esc)^(4-1),0)</f>
         <v/>
       </c>
       <c r="F63" s="20">
-        <f>IF(Inputs!$D$103="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$100,Inputs!$B$28:$B$31,1))*(1+Esc)^(5-1),0)</f>
+        <f>IF(Inputs!$D$113="Yes",INDEX(Inputs!$L$28:$L$31,MATCH(Inputs!$D$110,Inputs!$B$28:$B$31,1))*(1+Esc)^(5-1),0)</f>
         <v/>
       </c>
       <c r="G63" s="34">
@@ -14440,7 +15106,7 @@
         </is>
       </c>
       <c r="B64" s="20">
-        <f>Inputs!$D$104*Rate_Trainer+ROUND(Mig_Days_Source*Blended/Round_To,0)*Round_To*Inputs!$D$105+ROUND(Int_Std_Days*Blended/Round_To,0)*Round_To*Inputs!$D$106</f>
+        <f>Inputs!$D$114*Rate_Trainer+ROUND(Mig_Days_Source*Blended/Round_To,0)*Round_To*Inputs!$D$115+ROUND(Int_Std_Days*Blended/Round_To,0)*Round_To*Inputs!$D$116</f>
         <v/>
       </c>
       <c r="C64" s="20" t="n">

--- a/docs/package/02_Commercials/BrokerVerse_Commercials_and_Pricing.xlsx
+++ b/docs/package/02_Commercials/BrokerVerse_Commercials_and_Pricing.xlsx
@@ -12982,7 +12982,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Branding is included in the software; this is one pack: theme, sign-in picture, document and e-mail branding, e-signature mapping, exported pack. A pack carrying third-party marks needs the owner's written permission.</t>
+          <t>Branding is included in the software; this is one pack: theme, sign-in picture, document and e-mail branding, e-signature mapping, exported pack. A client pack carries the marks of a client of iorta TechNXT and is applied only in that client's environments, under the client's contract with iorta TechNXT, which covers the use of its marks there.</t>
         </is>
       </c>
     </row>
